--- a/Proyectos/Diseno-Estructural/DISENO-VIGAS-VIGUETAS-FINAL-v2.xlsx
+++ b/Proyectos/Diseno-Estructural/DISENO-VIGAS-VIGUETAS-FINAL-v2.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Despiece y Longitudes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1397,20 +1397,20 @@
       </c>
       <c r="D18" s="7">
         <f>MAX(E68:E72,H68:H72)</f>
-        <v/>
+        <v>1.023571884</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>1.20 / 1.40</t>
         </is>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="7" t="str">
         <f>IF(D18&gt;1.4,"Extrema",IF(D18&gt;1.2,"Si","No"))</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="G18" s="8">
         <f>IF(D18&gt;1.4,0.8,IF(D18&gt;1.2,0.9,1))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J18" s="32" t="inlineStr">
         <is>
@@ -1431,20 +1431,20 @@
       </c>
       <c r="D19" s="7">
         <f>MAX(C42/C40,C43/C41)</f>
-        <v/>
+        <v>0.1657285804</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="7" t="str">
         <f>IF(AND(C42/C40&gt;0.15,C43/C41&gt;0.15),"Si","No")</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="G19" s="8">
         <f>IF(AND(C42/C40&gt;0.15,C43/C41&gt;0.15),0.9,1)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1460,19 +1460,19 @@
       </c>
       <c r="D20" s="7">
         <f>C45</f>
-        <v/>
+        <v>27.03</v>
       </c>
       <c r="E20" s="7">
         <f>0.5*C40*C41</f>
-        <v/>
-      </c>
-      <c r="F20" s="7">
+        <v>292.617</v>
+      </c>
+      <c r="F20" s="7" t="str">
         <f>IF(C45&gt;0.5*C40*C41,"Si","No")</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="G20" s="8">
         <f>IF(C45&gt;0.5*C40*C41,0.9,1)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="G23" s="9">
         <f>MIN(G18:G22)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="33">
@@ -1603,20 +1603,20 @@
       </c>
       <c r="D27" s="7">
         <f>MIN(G52:G55)</f>
-        <v/>
+        <v>1.064936106</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>0.70 / 0.60</t>
         </is>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="7" t="str">
         <f>IF(D27&lt;0.6,"Extrema",IF(D27&lt;0.7,"Si","No"))</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="G27" s="8">
         <f>IF(D27&lt;0.6,0.8,IF(D27&lt;0.7,0.9,1))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="33">
@@ -1632,20 +1632,20 @@
       </c>
       <c r="D28" s="7">
         <f>MAX(H60:H63)</f>
-        <v/>
+        <v>1.323326017</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="7" t="str">
         <f>IF(D28&gt;1.5,"Si","No")</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="G28" s="8">
         <f>IF(D28&gt;1.5,0.9,1)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G32" s="9">
         <f>MIN(G27:G31)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="34" ht="31.5" customHeight="1" s="33">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C36" s="9">
         <f>IF(E35="Si",1,0.75)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="38" ht="31.5" customHeight="1" s="33">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C44" s="7">
         <f>C40*C41</f>
-        <v/>
+        <v>585.234</v>
       </c>
     </row>
     <row r="45">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C46" s="10">
         <f>C13*G32*G23*C36</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="47" ht="57.95" customHeight="1" s="33">
@@ -1938,18 +1938,18 @@
       </c>
       <c r="D52" s="7">
         <f>SUM(C52:C56)</f>
-        <v/>
+        <v>15128.72</v>
       </c>
       <c r="E52" s="7" t="n">
         <v>0.022</v>
       </c>
       <c r="F52" s="7">
         <f>D52/E52</f>
-        <v/>
+        <v>687669.0909</v>
       </c>
       <c r="G52" s="7">
         <f>F52/F53</f>
-        <v/>
+        <v>1.410636191</v>
       </c>
     </row>
     <row r="53">
@@ -1961,18 +1961,18 @@
       </c>
       <c r="D53" s="7">
         <f>SUM(C53:C56)</f>
-        <v/>
+        <v>14137.17</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>0.029</v>
       </c>
       <c r="F53" s="7">
         <f>D53/E53</f>
-        <v/>
+        <v>487488.6207</v>
       </c>
       <c r="G53" s="7">
         <f>F53/F54</f>
-        <v/>
+        <v>1.087083105</v>
       </c>
     </row>
     <row r="54">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="D54" s="7">
         <f>SUM(C54:C56)</f>
-        <v/>
+        <v>11659.37</v>
       </c>
       <c r="E54" s="7" t="n">
         <v>0.026</v>
       </c>
       <c r="F54" s="7">
         <f>D54/E54</f>
-        <v/>
+        <v>448437.3077</v>
       </c>
       <c r="G54" s="7">
         <f>F54/F55</f>
-        <v/>
+        <v>1.064936106</v>
       </c>
     </row>
     <row r="55">
@@ -2007,18 +2007,18 @@
       </c>
       <c r="D55" s="7">
         <f>SUM(C55:C56)</f>
-        <v/>
+        <v>8000.77</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>0.019</v>
       </c>
       <c r="F55" s="7">
         <f>D55/E55</f>
-        <v/>
+        <v>421093.1579</v>
       </c>
       <c r="G55" s="7">
         <f>F55/F56</f>
-        <v/>
+        <v>1.870865889</v>
       </c>
     </row>
     <row r="56">
@@ -2030,14 +2030,14 @@
       </c>
       <c r="D56" s="7">
         <f>SUM(C56:C56)</f>
-        <v/>
+        <v>3151.11</v>
       </c>
       <c r="E56" s="7" t="n">
         <v>0.014</v>
       </c>
       <c r="F56" s="7">
         <f>D56/E56</f>
-        <v/>
+        <v>225079.2857</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2093,11 +2093,11 @@
       </c>
       <c r="E60" s="7">
         <f>C60/C61</f>
-        <v/>
+        <v>0.7556716842</v>
       </c>
       <c r="H60" s="7">
         <f>E60</f>
-        <v/>
+        <v>0.7556716842</v>
       </c>
     </row>
     <row r="61">
@@ -2109,15 +2109,15 @@
       </c>
       <c r="D61" s="7">
         <f>C61/C60</f>
-        <v/>
+        <v>1.323326017</v>
       </c>
       <c r="E61" s="7">
         <f>C61/C62</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H61" s="7">
         <f>MAX(D61,E61)</f>
-        <v/>
+        <v>1.323326017</v>
       </c>
     </row>
     <row r="62">
@@ -2129,15 +2129,15 @@
       </c>
       <c r="D62" s="7">
         <f>C62/C61</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E62" s="7">
         <f>C62/C63</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H62" s="7">
         <f>MAX(D62,E62)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D63" s="7">
         <f>C63/C62</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="H63" s="7">
         <f>D63</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E68" s="7">
         <f>C68/((C68+D68)/2)</f>
-        <v/>
+        <v>1.023571884</v>
       </c>
       <c r="F68" s="7" t="n">
         <v>0.02097</v>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="H68" s="7">
         <f>F68/((F68+G68)/2)</f>
-        <v/>
+        <v>1.013288234</v>
       </c>
     </row>
     <row r="69">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E69" s="7">
         <f>C69/((C69+D69)/2)</f>
-        <v/>
+        <v>1.022820801</v>
       </c>
       <c r="F69" s="7" t="n">
         <v>0.04338</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="H69" s="7">
         <f>F69/((F69+G69)/2)</f>
-        <v/>
+        <v>1.014143776</v>
       </c>
     </row>
     <row r="70">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="E70" s="7">
         <f>C70/((C70+D70)/2)</f>
-        <v/>
+        <v>1.022321985</v>
       </c>
       <c r="F70" s="7" t="n">
         <v>0.0625</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="H70" s="7">
         <f>F70/((F70+G70)/2)</f>
-        <v/>
+        <v>1.014363386</v>
       </c>
     </row>
     <row r="71">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E71" s="7">
         <f>C71/((C71+D71)/2)</f>
-        <v/>
+        <v>1.022007838</v>
       </c>
       <c r="F71" s="7" t="n">
         <v>0.07592</v>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="H71" s="7">
         <f>F71/((F71+G71)/2)</f>
-        <v/>
+        <v>1.014498564</v>
       </c>
     </row>
     <row r="72">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E72" s="7">
         <f>C72/((C72+D72)/2)</f>
-        <v/>
+        <v>1.021769631</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>0.08278000000000001</v>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H72" s="7">
         <f>F72/((F72+G72)/2)</f>
-        <v/>
+        <v>1.014522949</v>
       </c>
     </row>
   </sheetData>
@@ -2796,127 +2796,127 @@
       </c>
       <c r="K14" s="79">
         <f>F14*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L14" s="80">
         <f>G14*1000000/(0.9*(E14*1000)*K14^2)</f>
-        <v/>
+        <v>0.3282627711</v>
       </c>
       <c r="M14" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L14/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.0007870436534</v>
       </c>
       <c r="N14" s="82">
         <f>M14*(E14*1000)*K14</f>
-        <v/>
+        <v>80.88054104</v>
       </c>
       <c r="O14" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E14*1000)*K14</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P14" s="82">
         <f>MAX(N14,O14)</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="Q14" s="83">
         <f>ROUNDUP(P14/$B$9,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="R14" s="82">
         <f>Q14*$B$9</f>
-        <v/>
+        <v>398</v>
       </c>
       <c r="S14" s="79">
         <f>R14*$B$6/(0.85*$B$5*(E14*1000))</f>
-        <v/>
+        <v>23.41176471</v>
       </c>
       <c r="T14" s="79">
         <f>0.9*R14*$B$6*(K14-S14/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U14" s="84">
+        <v>49.77351244</v>
+      </c>
+      <c r="U14" s="84" t="str">
         <f>IF(AND(T14&gt;=G14,P14&lt;=0.025*(E14*1000)*K14,P14&gt;=O14),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V14" s="80">
         <f>H14*1000000/(0.9*(E14*1000)*K14^2)</f>
-        <v/>
+        <v>0.126254912</v>
       </c>
       <c r="W14" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V14/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.0003014085253</v>
       </c>
       <c r="X14" s="82">
         <f>W14*(E14*1000)*K14</f>
-        <v/>
+        <v>30.97424711</v>
       </c>
       <c r="Y14" s="82">
         <f>MAX(X14,O14)</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="Z14" s="83">
         <f>ROUNDUP(Y14/$B$9,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA14" s="82">
         <f>Z14*$B$9</f>
-        <v/>
+        <v>398</v>
       </c>
       <c r="AB14" s="79">
         <f>0.9*AA14*$B$6*(K14-(AA14*$B$6/(0.85*$B$5*(E14*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC14" s="84">
+        <v>49.77351244</v>
+      </c>
+      <c r="AC14" s="84" t="str">
         <f>IF(AB14&gt;=H14,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD14" s="79">
         <f>0.17*SQRT($B$5)*(E14*1000)*K14/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE14" s="79">
         <f>MAX(I14/0.75-AD14,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF14" s="83">
         <f>IF(AE14&gt;0,MIN($B$11*$B$6*K14/(AE14*1000),MIN(K14/4,6*$B$8,150)),MIN(K14/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG14" s="79">
         <f>0.66*SQRT($B$5)*(E14*1000)*K14/1000</f>
-        <v/>
-      </c>
-      <c r="AH14" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH14" s="84" t="str">
         <f>IF(AE14&lt;=AG14,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI14" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E14*1000)*(F14*1000))^2/(2*((E14*1000)+(F14*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ14" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ14" s="85" t="str">
         <f>IF(J14&gt;AI14,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK14" s="80">
         <f>IF(J14&gt;AI14,J14*1000000/(0.75*2*0.85*((E14*1000-2*$B$7)*(F14*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL14" s="79">
         <f>1.25*R14*$B$6*(K14-(1.25*R14*$B$6/(0.85*$B$5*(E14*1000)))/2)/1000000</f>
-        <v/>
+        <v>68.51839235</v>
       </c>
       <c r="AM14" s="79">
         <f>1.25*AA14*$B$6*(K14-(1.25*AA14*$B$6/(0.85*$B$5*(E14*1000)))/2)/1000000</f>
-        <v/>
+        <v>68.51839235</v>
       </c>
       <c r="AN14" s="79">
         <f>(AL14+AM14)/B14</f>
-        <v/>
+        <v>54.81471388</v>
       </c>
       <c r="AO14" s="79">
         <f>MAX(I14,AN14)</f>
-        <v/>
+        <v>54.81471388</v>
       </c>
     </row>
     <row r="15">
@@ -2956,127 +2956,127 @@
       </c>
       <c r="K15" s="79">
         <f>F15*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L15" s="80">
         <f>G15*1000000/(0.9*(E15*1000)*K15^2)</f>
-        <v/>
+        <v>0.2177897232</v>
       </c>
       <c r="M15" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L15/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.0005209414896</v>
       </c>
       <c r="N15" s="82">
         <f>M15*(E15*1000)*K15</f>
-        <v/>
+        <v>53.53455218</v>
       </c>
       <c r="O15" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E15*1000)*K15</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P15" s="82">
         <f>MAX(N15,O15)</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="Q15" s="83">
         <f>ROUNDUP(P15/$B$9,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="R15" s="82">
         <f>Q15*$B$9</f>
-        <v/>
+        <v>398</v>
       </c>
       <c r="S15" s="79">
         <f>R15*$B$6/(0.85*$B$5*(E15*1000))</f>
-        <v/>
+        <v>23.41176471</v>
       </c>
       <c r="T15" s="79">
         <f>0.9*R15*$B$6*(K15-S15/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U15" s="84">
+        <v>49.77351244</v>
+      </c>
+      <c r="U15" s="84" t="str">
         <f>IF(AND(T15&gt;=G15,P15&lt;=0.025*(E15*1000)*K15,P15&gt;=O15),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V15" s="80">
         <f>H15*1000000/(0.9*(E15*1000)*K15^2)</f>
-        <v/>
+        <v>0.07259657439</v>
       </c>
       <c r="W15" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V15/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.0001731134124</v>
       </c>
       <c r="X15" s="82">
         <f>W15*(E15*1000)*K15</f>
-        <v/>
+        <v>17.78999983</v>
       </c>
       <c r="Y15" s="82">
         <f>MAX(X15,O15)</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="Z15" s="83">
         <f>ROUNDUP(Y15/$B$9,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA15" s="82">
         <f>Z15*$B$9</f>
-        <v/>
+        <v>398</v>
       </c>
       <c r="AB15" s="79">
         <f>0.9*AA15*$B$6*(K15-(AA15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC15" s="84">
+        <v>49.77351244</v>
+      </c>
+      <c r="AC15" s="84" t="str">
         <f>IF(AB15&gt;=H15,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD15" s="79">
         <f>0.17*SQRT($B$5)*(E15*1000)*K15/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE15" s="79">
         <f>MAX(I15/0.75-AD15,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF15" s="83">
         <f>IF(AE15&gt;0,MIN($B$11*$B$6*K15/(AE15*1000),MIN(K15/4,6*$B$8,150)),MIN(K15/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG15" s="79">
         <f>0.66*SQRT($B$5)*(E15*1000)*K15/1000</f>
-        <v/>
-      </c>
-      <c r="AH15" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH15" s="84" t="str">
         <f>IF(AE15&lt;=AG15,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI15" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E15*1000)*(F15*1000))^2/(2*((E15*1000)+(F15*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ15" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ15" s="85" t="str">
         <f>IF(J15&gt;AI15,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK15" s="80">
         <f>IF(J15&gt;AI15,J15*1000000/(0.75*2*0.85*((E15*1000-2*$B$7)*(F15*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL15" s="79">
         <f>1.25*R15*$B$6*(K15-(1.25*R15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v/>
+        <v>68.51839235</v>
       </c>
       <c r="AM15" s="79">
         <f>1.25*AA15*$B$6*(K15-(1.25*AA15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v/>
+        <v>68.51839235</v>
       </c>
       <c r="AN15" s="79">
         <f>(AL15+AM15)/B15</f>
-        <v/>
+        <v>52.70645566</v>
       </c>
       <c r="AO15" s="79">
         <f>MAX(I15,AN15)</f>
-        <v/>
+        <v>52.70645566</v>
       </c>
     </row>
     <row r="16">
@@ -3116,127 +3116,127 @@
       </c>
       <c r="K16" s="79">
         <f>F16*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L16" s="80">
         <f>G16*1000000/(0.9*(E16*1000)*K16^2)</f>
-        <v/>
+        <v>3.749770886</v>
       </c>
       <c r="M16" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L16/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.009770311012</v>
       </c>
       <c r="N16" s="82">
         <f>M16*(E16*1000)*K16</f>
-        <v/>
+        <v>1004.046011</v>
       </c>
       <c r="O16" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E16*1000)*K16</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P16" s="82">
         <f>MAX(N16,O16)</f>
-        <v/>
+        <v>1004.046011</v>
       </c>
       <c r="Q16" s="83">
         <f>ROUNDUP(P16/$B$9,0)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="R16" s="82">
         <f>Q16*$B$9</f>
-        <v/>
+        <v>1194</v>
       </c>
       <c r="S16" s="79">
         <f>R16*$B$6/(0.85*$B$5*(E16*1000))</f>
-        <v/>
+        <v>70.23529412</v>
       </c>
       <c r="T16" s="79">
         <f>0.9*R16*$B$6*(K16-S16/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U16" s="84">
+        <v>138.7540587</v>
+      </c>
+      <c r="U16" s="84" t="str">
         <f>IF(AND(T16&gt;=G16,P16&lt;=0.025*(E16*1000)*K16,P16&gt;=O16),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V16" s="80">
         <f>H16*1000000/(0.9*(E16*1000)*K16^2)</f>
-        <v/>
+        <v>3.244751238</v>
       </c>
       <c r="W16" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V16/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.008339207425</v>
       </c>
       <c r="X16" s="82">
         <f>W16*(E16*1000)*K16</f>
-        <v/>
+        <v>856.978651</v>
       </c>
       <c r="Y16" s="82">
         <f>MAX(X16,O16)</f>
-        <v/>
+        <v>856.978651</v>
       </c>
       <c r="Z16" s="83">
         <f>ROUNDUP(Y16/$B$9,0)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="AA16" s="82">
         <f>Z16*$B$9</f>
-        <v/>
+        <v>995</v>
       </c>
       <c r="AB16" s="79">
         <f>0.9*AA16*$B$6*(K16-(AA16*$B$6/(0.85*$B$5*(E16*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC16" s="84">
+        <v>117.829732</v>
+      </c>
+      <c r="AC16" s="84" t="str">
         <f>IF(AB16&gt;=H16,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD16" s="79">
         <f>0.17*SQRT($B$5)*(E16*1000)*K16/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE16" s="79">
         <f>MAX(I16/0.75-AD16,0)</f>
-        <v/>
+        <v>25.29051795</v>
       </c>
       <c r="AF16" s="83">
         <f>IF(AE16&gt;0,MIN($B$11*$B$6*K16/(AE16*1000),MIN(K16/4,6*$B$8,150)),MIN(K16/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG16" s="79">
         <f>0.66*SQRT($B$5)*(E16*1000)*K16/1000</f>
-        <v/>
-      </c>
-      <c r="AH16" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH16" s="84" t="str">
         <f>IF(AE16&lt;=AG16,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI16" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E16*1000)*(F16*1000))^2/(2*((E16*1000)+(F16*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ16" s="85" t="str">
         <f>IF(J16&gt;AI16,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK16" s="80">
         <f>IF(J16&gt;AI16,J16*1000000/(0.75*2*0.85*((E16*1000-2*$B$7)*(F16*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL16" s="79">
         <f>1.25*R16*$B$6*(K16-(1.25*R16*$B$6/(0.85*$B$5*(E16*1000)))/2)/1000000</f>
-        <v/>
+        <v>187.2105962</v>
       </c>
       <c r="AM16" s="79">
         <f>1.25*AA16*$B$6*(K16-(1.25*AA16*$B$6/(0.85*$B$5*(E16*1000)))/2)/1000000</f>
-        <v/>
+        <v>159.8306178</v>
       </c>
       <c r="AN16" s="79">
         <f>(AL16+AM16)/B16</f>
-        <v/>
+        <v>130.9589487</v>
       </c>
       <c r="AO16" s="79">
         <f>MAX(I16,AN16)</f>
-        <v/>
+        <v>130.9589487</v>
       </c>
     </row>
     <row r="17">
@@ -3276,127 +3276,127 @@
       </c>
       <c r="K17" s="79">
         <f>F17*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L17" s="80">
         <f>G17*1000000/(0.9*(E17*1000)*K17^2)</f>
-        <v/>
+        <v>3.345755167</v>
       </c>
       <c r="M17" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L17/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.008622017764</v>
       </c>
       <c r="N17" s="82">
         <f>M17*(E17*1000)*K17</f>
-        <v/>
+        <v>886.0416556</v>
       </c>
       <c r="O17" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E17*1000)*K17</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P17" s="82">
         <f>MAX(N17,O17)</f>
-        <v/>
+        <v>886.0416556</v>
       </c>
       <c r="Q17" s="83">
         <f>ROUNDUP(P17/$B$9,0)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="R17" s="82">
         <f>Q17*$B$9</f>
-        <v/>
+        <v>995</v>
       </c>
       <c r="S17" s="79">
         <f>R17*$B$6/(0.85*$B$5*(E17*1000))</f>
-        <v/>
+        <v>58.52941176</v>
       </c>
       <c r="T17" s="79">
         <f>0.9*R17*$B$6*(K17-S17/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U17" s="84">
+        <v>117.829732</v>
+      </c>
+      <c r="U17" s="84" t="str">
         <f>IF(AND(T17&gt;=G17,P17&lt;=0.025*(E17*1000)*K17,P17&gt;=O17),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V17" s="80">
         <f>H17*1000000/(0.9*(E17*1000)*K17^2)</f>
-        <v/>
+        <v>2.828110028</v>
       </c>
       <c r="W17" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V17/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.007189699199</v>
       </c>
       <c r="X17" s="82">
         <f>W17*(E17*1000)*K17</f>
-        <v/>
+        <v>738.8494382</v>
       </c>
       <c r="Y17" s="82">
         <f>MAX(X17,O17)</f>
-        <v/>
+        <v>738.8494382</v>
       </c>
       <c r="Z17" s="83">
         <f>ROUNDUP(Y17/$B$9,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AA17" s="82">
         <f>Z17*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="AB17" s="79">
         <f>0.9*AA17*$B$6*(K17-(AA17*$B$6/(0.85*$B$5*(E17*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC17" s="84">
+        <v>96.02486534</v>
+      </c>
+      <c r="AC17" s="84" t="str">
         <f>IF(AB17&gt;=H17,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD17" s="79">
         <f>0.17*SQRT($B$5)*(E17*1000)*K17/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE17" s="79">
         <f>MAX(I17/0.75-AD17,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF17" s="83">
         <f>IF(AE17&gt;0,MIN($B$11*$B$6*K17/(AE17*1000),MIN(K17/4,6*$B$8,150)),MIN(K17/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG17" s="79">
         <f>0.66*SQRT($B$5)*(E17*1000)*K17/1000</f>
-        <v/>
-      </c>
-      <c r="AH17" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH17" s="84" t="str">
         <f>IF(AE17&lt;=AG17,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI17" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E17*1000)*(F17*1000))^2/(2*((E17*1000)+(F17*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ17" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ17" s="85" t="str">
         <f>IF(J17&gt;AI17,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK17" s="80">
         <f>IF(J17&gt;AI17,J17*1000000/(0.75*2*0.85*((E17*1000-2*$B$7)*(F17*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL17" s="79">
         <f>1.25*R17*$B$6*(K17-(1.25*R17*$B$6/(0.85*$B$5*(E17*1000)))/2)/1000000</f>
-        <v/>
+        <v>159.8306178</v>
       </c>
       <c r="AM17" s="79">
         <f>1.25*AA17*$B$6*(K17-(1.25*AA17*$B$6/(0.85*$B$5*(E17*1000)))/2)/1000000</f>
-        <v/>
+        <v>130.9219244</v>
       </c>
       <c r="AN17" s="79">
         <f>(AL17+AM17)/B17</f>
-        <v/>
+        <v>77.53401126</v>
       </c>
       <c r="AO17" s="79">
         <f>MAX(I17,AN17)</f>
-        <v/>
+        <v>77.53401126</v>
       </c>
     </row>
     <row r="18">
@@ -3436,127 +3436,127 @@
       </c>
       <c r="K18" s="79">
         <f>F18*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L18" s="80">
         <f>G18*1000000/(0.9*(E18*1000)*K18^2)</f>
-        <v/>
+        <v>0.7890931999</v>
       </c>
       <c r="M18" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L18/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.00191101673</v>
       </c>
       <c r="N18" s="82">
         <f>M18*(E18*1000)*K18</f>
-        <v/>
+        <v>196.3856342</v>
       </c>
       <c r="O18" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E18*1000)*K18</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P18" s="82">
         <f>MAX(N18,O18)</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="Q18" s="83">
         <f>ROUNDUP(P18/$B$9,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="R18" s="82">
         <f>Q18*$B$9</f>
-        <v/>
+        <v>398</v>
       </c>
       <c r="S18" s="79">
         <f>R18*$B$6/(0.85*$B$5*(E18*1000))</f>
-        <v/>
+        <v>23.41176471</v>
       </c>
       <c r="T18" s="79">
         <f>0.9*R18*$B$6*(K18-S18/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U18" s="84">
+        <v>49.77351244</v>
+      </c>
+      <c r="U18" s="84" t="str">
         <f>IF(AND(T18&gt;=G18,P18&lt;=0.025*(E18*1000)*K18,P18&gt;=O18),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V18" s="80">
         <f>H18*1000000/(0.9*(E18*1000)*K18^2)</f>
-        <v/>
+        <v>0.5208015119</v>
       </c>
       <c r="W18" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V18/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.001253875997</v>
       </c>
       <c r="X18" s="82">
         <f>W18*(E18*1000)*K18</f>
-        <v/>
+        <v>128.8545668</v>
       </c>
       <c r="Y18" s="82">
         <f>MAX(X18,O18)</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="Z18" s="83">
         <f>ROUNDUP(Y18/$B$9,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="AA18" s="82">
         <f>Z18*$B$9</f>
-        <v/>
+        <v>398</v>
       </c>
       <c r="AB18" s="79">
         <f>0.9*AA18*$B$6*(K18-(AA18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC18" s="84">
+        <v>49.77351244</v>
+      </c>
+      <c r="AC18" s="84" t="str">
         <f>IF(AB18&gt;=H18,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD18" s="79">
         <f>0.17*SQRT($B$5)*(E18*1000)*K18/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE18" s="79">
         <f>MAX(I18/0.75-AD18,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF18" s="83">
         <f>IF(AE18&gt;0,MIN($B$11*$B$6*K18/(AE18*1000),MIN(K18/4,6*$B$8,150)),MIN(K18/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG18" s="79">
         <f>0.66*SQRT($B$5)*(E18*1000)*K18/1000</f>
-        <v/>
-      </c>
-      <c r="AH18" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH18" s="84" t="str">
         <f>IF(AE18&lt;=AG18,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI18" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E18*1000)*(F18*1000))^2/(2*((E18*1000)+(F18*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ18" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ18" s="85" t="str">
         <f>IF(J18&gt;AI18,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK18" s="80">
         <f>IF(J18&gt;AI18,J18*1000000/(0.75*2*0.85*((E18*1000-2*$B$7)*(F18*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL18" s="79">
         <f>1.25*R18*$B$6*(K18-(1.25*R18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v/>
+        <v>68.51839235</v>
       </c>
       <c r="AM18" s="79">
         <f>1.25*AA18*$B$6*(K18-(1.25*AA18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v/>
+        <v>68.51839235</v>
       </c>
       <c r="AN18" s="79">
         <f>(AL18+AM18)/B18</f>
-        <v/>
+        <v>36.54314259</v>
       </c>
       <c r="AO18" s="79">
         <f>MAX(I18,AN18)</f>
-        <v/>
+        <v>36.54314259</v>
       </c>
     </row>
     <row r="19">
@@ -3596,127 +3596,127 @@
       </c>
       <c r="K19" s="79">
         <f>F19*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L19" s="80">
         <f>G19*1000000/(0.9*(E19*1000)*K19^2)</f>
-        <v/>
+        <v>3.595108619</v>
       </c>
       <c r="M19" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L19/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.009327439421</v>
       </c>
       <c r="N19" s="82">
         <f>M19*(E19*1000)*K19</f>
-        <v/>
+        <v>958.5343121</v>
       </c>
       <c r="O19" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E19*1000)*K19</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P19" s="82">
         <f>MAX(N19,O19)</f>
-        <v/>
+        <v>958.5343121</v>
       </c>
       <c r="Q19" s="83">
         <f>ROUNDUP(P19/$B$9,0)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="R19" s="82">
         <f>Q19*$B$9</f>
-        <v/>
+        <v>995</v>
       </c>
       <c r="S19" s="79">
         <f>R19*$B$6/(0.85*$B$5*(E19*1000))</f>
-        <v/>
+        <v>58.52941176</v>
       </c>
       <c r="T19" s="79">
         <f>0.9*R19*$B$6*(K19-S19/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U19" s="84">
+        <v>117.829732</v>
+      </c>
+      <c r="U19" s="84" t="str">
         <f>IF(AND(T19&gt;=G19,P19&lt;=0.025*(E19*1000)*K19,P19&gt;=O19),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V19" s="80">
         <f>H19*1000000/(0.9*(E19*1000)*K19^2)</f>
-        <v/>
+        <v>2.55981834</v>
       </c>
       <c r="W19" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V19/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.006463414983</v>
       </c>
       <c r="X19" s="82">
         <f>W19*(E19*1000)*K19</f>
-        <v/>
+        <v>664.2128408</v>
       </c>
       <c r="Y19" s="82">
         <f>MAX(X19,O19)</f>
-        <v/>
+        <v>664.2128408</v>
       </c>
       <c r="Z19" s="83">
         <f>ROUNDUP(Y19/$B$9,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AA19" s="82">
         <f>Z19*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="AB19" s="79">
         <f>0.9*AA19*$B$6*(K19-(AA19*$B$6/(0.85*$B$5*(E19*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC19" s="84">
+        <v>96.02486534</v>
+      </c>
+      <c r="AC19" s="84" t="str">
         <f>IF(AB19&gt;=H19,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD19" s="79">
         <f>0.17*SQRT($B$5)*(E19*1000)*K19/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE19" s="79">
         <f>MAX(I19/0.75-AD19,0)</f>
-        <v/>
+        <v>5.557184616</v>
       </c>
       <c r="AF19" s="83">
         <f>IF(AE19&gt;0,MIN($B$11*$B$6*K19/(AE19*1000),MIN(K19/4,6*$B$8,150)),MIN(K19/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG19" s="79">
         <f>0.66*SQRT($B$5)*(E19*1000)*K19/1000</f>
-        <v/>
-      </c>
-      <c r="AH19" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH19" s="84" t="str">
         <f>IF(AE19&lt;=AG19,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI19" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E19*1000)*(F19*1000))^2/(2*((E19*1000)+(F19*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ19" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ19" s="85" t="str">
         <f>IF(J19&gt;AI19,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>SI - disenar</v>
       </c>
       <c r="AK19" s="80">
         <f>IF(J19&gt;AI19,J19*1000000/(0.75*2*0.85*((E19*1000-2*$B$7)*(F19*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0.1830277566</v>
       </c>
       <c r="AL19" s="79">
         <f>1.25*R19*$B$6*(K19-(1.25*R19*$B$6/(0.85*$B$5*(E19*1000)))/2)/1000000</f>
-        <v/>
+        <v>159.8306178</v>
       </c>
       <c r="AM19" s="79">
         <f>1.25*AA19*$B$6*(K19-(1.25*AA19*$B$6/(0.85*$B$5*(E19*1000)))/2)/1000000</f>
-        <v/>
+        <v>130.9219244</v>
       </c>
       <c r="AN19" s="79">
         <f>(AL19+AM19)/B19</f>
-        <v/>
+        <v>76.31300321</v>
       </c>
       <c r="AO19" s="79">
         <f>MAX(I19,AN19)</f>
-        <v/>
+        <v>76.31300321</v>
       </c>
     </row>
     <row r="20">
@@ -3756,127 +3756,127 @@
       </c>
       <c r="K20" s="79">
         <f>F20*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L20" s="80">
         <f>G20*1000000/(0.9*(E20*1000)*K20^2)</f>
-        <v/>
+        <v>3.336286049</v>
       </c>
       <c r="M20" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L20/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.008595433615</v>
       </c>
       <c r="N20" s="82">
         <f>M20*(E20*1000)*K20</f>
-        <v/>
+        <v>883.3097355</v>
       </c>
       <c r="O20" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E20*1000)*K20</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P20" s="82">
         <f>MAX(N20,O20)</f>
-        <v/>
+        <v>883.3097355</v>
       </c>
       <c r="Q20" s="83">
         <f>ROUNDUP(P20/$B$9,0)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="R20" s="82">
         <f>Q20*$B$9</f>
-        <v/>
+        <v>995</v>
       </c>
       <c r="S20" s="79">
         <f>R20*$B$6/(0.85*$B$5*(E20*1000))</f>
-        <v/>
+        <v>58.52941176</v>
       </c>
       <c r="T20" s="79">
         <f>0.9*R20*$B$6*(K20-S20/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U20" s="84">
+        <v>117.829732</v>
+      </c>
+      <c r="U20" s="84" t="str">
         <f>IF(AND(T20&gt;=G20,P20&lt;=0.025*(E20*1000)*K20,P20&gt;=O20),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V20" s="80">
         <f>H20*1000000/(0.9*(E20*1000)*K20^2)</f>
-        <v/>
+        <v>2.342028617</v>
       </c>
       <c r="W20" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V20/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.00588148049</v>
       </c>
       <c r="X20" s="82">
         <f>W20*(E20*1000)*K20</f>
-        <v/>
+        <v>604.4103425</v>
       </c>
       <c r="Y20" s="82">
         <f>MAX(X20,O20)</f>
-        <v/>
+        <v>604.4103425</v>
       </c>
       <c r="Z20" s="83">
         <f>ROUNDUP(Y20/$B$9,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AA20" s="82">
         <f>Z20*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="AB20" s="79">
         <f>0.9*AA20*$B$6*(K20-(AA20*$B$6/(0.85*$B$5*(E20*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC20" s="84">
+        <v>96.02486534</v>
+      </c>
+      <c r="AC20" s="84" t="str">
         <f>IF(AB20&gt;=H20,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD20" s="79">
         <f>0.17*SQRT($B$5)*(E20*1000)*K20/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE20" s="79">
         <f>MAX(I20/0.75-AD20,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF20" s="83">
         <f>IF(AE20&gt;0,MIN($B$11*$B$6*K20/(AE20*1000),MIN(K20/4,6*$B$8,150)),MIN(K20/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG20" s="79">
         <f>0.66*SQRT($B$5)*(E20*1000)*K20/1000</f>
-        <v/>
-      </c>
-      <c r="AH20" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH20" s="84" t="str">
         <f>IF(AE20&lt;=AG20,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI20" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E20*1000)*(F20*1000))^2/(2*((E20*1000)+(F20*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ20" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ20" s="85" t="str">
         <f>IF(J20&gt;AI20,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>SI - disenar</v>
       </c>
       <c r="AK20" s="80">
         <f>IF(J20&gt;AI20,J20*1000000/(0.75*2*0.85*((E20*1000-2*$B$7)*(F20*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0.1724174518</v>
       </c>
       <c r="AL20" s="79">
         <f>1.25*R20*$B$6*(K20-(1.25*R20*$B$6/(0.85*$B$5*(E20*1000)))/2)/1000000</f>
-        <v/>
+        <v>159.8306178</v>
       </c>
       <c r="AM20" s="79">
         <f>1.25*AA20*$B$6*(K20-(1.25*AA20*$B$6/(0.85*$B$5*(E20*1000)))/2)/1000000</f>
-        <v/>
+        <v>130.9219244</v>
       </c>
       <c r="AN20" s="79">
         <f>(AL20+AM20)/B20</f>
-        <v/>
+        <v>76.31300321</v>
       </c>
       <c r="AO20" s="79">
         <f>MAX(I20,AN20)</f>
-        <v/>
+        <v>76.31300321</v>
       </c>
     </row>
     <row r="21">
@@ -3916,127 +3916,127 @@
       </c>
       <c r="K21" s="79">
         <f>F21*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L21" s="80">
         <f>G21*1000000/(0.9*(E21*1000)*K21^2)</f>
-        <v/>
+        <v>3.838149324</v>
       </c>
       <c r="M21" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L21/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.01002526849</v>
       </c>
       <c r="N21" s="82">
         <f>M21*(E21*1000)*K21</f>
-        <v/>
+        <v>1030.246717</v>
       </c>
       <c r="O21" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E21*1000)*K21</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P21" s="82">
         <f>MAX(N21,O21)</f>
-        <v/>
+        <v>1030.246717</v>
       </c>
       <c r="Q21" s="83">
         <f>ROUNDUP(P21/$B$9,0)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="R21" s="82">
         <f>Q21*$B$9</f>
-        <v/>
+        <v>1194</v>
       </c>
       <c r="S21" s="79">
         <f>R21*$B$6/(0.85*$B$5*(E21*1000))</f>
-        <v/>
+        <v>70.23529412</v>
       </c>
       <c r="T21" s="79">
         <f>0.9*R21*$B$6*(K21-S21/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U21" s="84">
+        <v>138.7540587</v>
+      </c>
+      <c r="U21" s="84" t="str">
         <f>IF(AND(T21&gt;=G21,P21&lt;=0.025*(E21*1000)*K21,P21&gt;=O21),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V21" s="80">
         <f>H21*1000000/(0.9*(E21*1000)*K21^2)</f>
-        <v/>
+        <v>2.944895822</v>
       </c>
       <c r="W21" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V21/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.007509198435</v>
       </c>
       <c r="X21" s="82">
         <f>W21*(E21*1000)*K21</f>
-        <v/>
+        <v>771.6827771</v>
       </c>
       <c r="Y21" s="82">
         <f>MAX(X21,O21)</f>
-        <v/>
+        <v>771.6827771</v>
       </c>
       <c r="Z21" s="83">
         <f>ROUNDUP(Y21/$B$9,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AA21" s="82">
         <f>Z21*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="AB21" s="79">
         <f>0.9*AA21*$B$6*(K21-(AA21*$B$6/(0.85*$B$5*(E21*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC21" s="84">
+        <v>96.02486534</v>
+      </c>
+      <c r="AC21" s="84" t="str">
         <f>IF(AB21&gt;=H21,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD21" s="79">
         <f>0.17*SQRT($B$5)*(E21*1000)*K21/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE21" s="79">
         <f>MAX(I21/0.75-AD21,0)</f>
-        <v/>
+        <v>11.42385128</v>
       </c>
       <c r="AF21" s="83">
         <f>IF(AE21&gt;0,MIN($B$11*$B$6*K21/(AE21*1000),MIN(K21/4,6*$B$8,150)),MIN(K21/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG21" s="79">
         <f>0.66*SQRT($B$5)*(E21*1000)*K21/1000</f>
-        <v/>
-      </c>
-      <c r="AH21" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH21" s="84" t="str">
         <f>IF(AE21&lt;=AG21,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI21" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E21*1000)*(F21*1000))^2/(2*((E21*1000)+(F21*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ21" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ21" s="85" t="str">
         <f>IF(J21&gt;AI21,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK21" s="80">
         <f>IF(J21&gt;AI21,J21*1000000/(0.75*2*0.85*((E21*1000-2*$B$7)*(F21*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL21" s="79">
         <f>1.25*R21*$B$6*(K21-(1.25*R21*$B$6/(0.85*$B$5*(E21*1000)))/2)/1000000</f>
-        <v/>
+        <v>187.2105962</v>
       </c>
       <c r="AM21" s="79">
         <f>1.25*AA21*$B$6*(K21-(1.25*AA21*$B$6/(0.85*$B$5*(E21*1000)))/2)/1000000</f>
-        <v/>
+        <v>130.9219244</v>
       </c>
       <c r="AN21" s="79">
         <f>(AL21+AM21)/B21</f>
-        <v/>
+        <v>82.63182353</v>
       </c>
       <c r="AO21" s="79">
         <f>MAX(I21,AN21)</f>
-        <v/>
+        <v>82.63182353</v>
       </c>
     </row>
     <row r="22">
@@ -4076,127 +4076,127 @@
       </c>
       <c r="K22" s="79">
         <f>F22*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L22" s="80">
         <f>G22*1000000/(0.9*(E22*1000)*K22^2)</f>
-        <v/>
+        <v>4.068564539</v>
       </c>
       <c r="M22" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L22/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.01069662762</v>
       </c>
       <c r="N22" s="82">
         <f>M22*(E22*1000)*K22</f>
-        <v/>
+        <v>1099.238938</v>
       </c>
       <c r="O22" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E22*1000)*K22</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P22" s="82">
         <f>MAX(N22,O22)</f>
-        <v/>
+        <v>1099.238938</v>
       </c>
       <c r="Q22" s="83">
         <f>ROUNDUP(P22/$B$9,0)</f>
-        <v/>
+        <v>6</v>
       </c>
       <c r="R22" s="82">
         <f>Q22*$B$9</f>
-        <v/>
+        <v>1194</v>
       </c>
       <c r="S22" s="79">
         <f>R22*$B$6/(0.85*$B$5*(E22*1000))</f>
-        <v/>
+        <v>70.23529412</v>
       </c>
       <c r="T22" s="79">
         <f>0.9*R22*$B$6*(K22-S22/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U22" s="84">
+        <v>138.7540587</v>
+      </c>
+      <c r="U22" s="84" t="str">
         <f>IF(AND(T22&gt;=G22,P22&lt;=0.025*(E22*1000)*K22,P22&gt;=O22),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V22" s="80">
         <f>H22*1000000/(0.9*(E22*1000)*K22^2)</f>
-        <v/>
+        <v>2.862830129</v>
       </c>
       <c r="W22" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V22/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.007284469533</v>
       </c>
       <c r="X22" s="82">
         <f>W22*(E22*1000)*K22</f>
-        <v/>
+        <v>748.5885116</v>
       </c>
       <c r="Y22" s="82">
         <f>MAX(X22,O22)</f>
-        <v/>
+        <v>748.5885116</v>
       </c>
       <c r="Z22" s="83">
         <f>ROUNDUP(Y22/$B$9,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AA22" s="82">
         <f>Z22*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="AB22" s="79">
         <f>0.9*AA22*$B$6*(K22-(AA22*$B$6/(0.85*$B$5*(E22*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC22" s="84">
+        <v>96.02486534</v>
+      </c>
+      <c r="AC22" s="84" t="str">
         <f>IF(AB22&gt;=H22,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD22" s="79">
         <f>0.17*SQRT($B$5)*(E22*1000)*K22/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE22" s="79">
         <f>MAX(I22/0.75-AD22,0)</f>
-        <v/>
+        <v>30.09051795</v>
       </c>
       <c r="AF22" s="83">
         <f>IF(AE22&gt;0,MIN($B$11*$B$6*K22/(AE22*1000),MIN(K22/4,6*$B$8,150)),MIN(K22/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG22" s="79">
         <f>0.66*SQRT($B$5)*(E22*1000)*K22/1000</f>
-        <v/>
-      </c>
-      <c r="AH22" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH22" s="84" t="str">
         <f>IF(AE22&lt;=AG22,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI22" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E22*1000)*(F22*1000))^2/(2*((E22*1000)+(F22*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ22" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ22" s="85" t="str">
         <f>IF(J22&gt;AI22,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK22" s="80">
         <f>IF(J22&gt;AI22,J22*1000000/(0.75*2*0.85*((E22*1000-2*$B$7)*(F22*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL22" s="79">
         <f>1.25*R22*$B$6*(K22-(1.25*R22*$B$6/(0.85*$B$5*(E22*1000)))/2)/1000000</f>
-        <v/>
+        <v>187.2105962</v>
       </c>
       <c r="AM22" s="79">
         <f>1.25*AA22*$B$6*(K22-(1.25*AA22*$B$6/(0.85*$B$5*(E22*1000)))/2)/1000000</f>
-        <v/>
+        <v>130.9219244</v>
       </c>
       <c r="AN22" s="79">
         <f>(AL22+AM22)/B22</f>
-        <v/>
+        <v>81.57244118</v>
       </c>
       <c r="AO22" s="79">
         <f>MAX(I22,AN22)</f>
-        <v/>
+        <v>91.9</v>
       </c>
     </row>
     <row r="23">
@@ -4236,127 +4236,127 @@
       </c>
       <c r="K23" s="79">
         <f>F23*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L23" s="80">
         <f>G23*1000000/(0.9*(E23*1000)*K23^2)</f>
-        <v/>
+        <v>3.282627711</v>
       </c>
       <c r="M23" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L23/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.008445066931</v>
       </c>
       <c r="N23" s="82">
         <f>M23*(E23*1000)*K23</f>
-        <v/>
+        <v>867.8573032</v>
       </c>
       <c r="O23" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E23*1000)*K23</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P23" s="82">
         <f>MAX(N23,O23)</f>
-        <v/>
+        <v>867.8573032</v>
       </c>
       <c r="Q23" s="83">
         <f>ROUNDUP(P23/$B$9,0)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="R23" s="82">
         <f>Q23*$B$9</f>
-        <v/>
+        <v>995</v>
       </c>
       <c r="S23" s="79">
         <f>R23*$B$6/(0.85*$B$5*(E23*1000))</f>
-        <v/>
+        <v>58.52941176</v>
       </c>
       <c r="T23" s="79">
         <f>0.9*R23*$B$6*(K23-S23/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U23" s="84">
+        <v>117.829732</v>
+      </c>
+      <c r="U23" s="84" t="str">
         <f>IF(AND(T23&gt;=G23,P23&lt;=0.025*(E23*1000)*K23,P23&gt;=O23),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V23" s="80">
         <f>H23*1000000/(0.9*(E23*1000)*K23^2)</f>
-        <v/>
+        <v>2.752357081</v>
       </c>
       <c r="W23" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V23/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.006983555036</v>
       </c>
       <c r="X23" s="82">
         <f>W23*(E23*1000)*K23</f>
-        <v/>
+        <v>717.6650333</v>
       </c>
       <c r="Y23" s="82">
         <f>MAX(X23,O23)</f>
-        <v/>
+        <v>717.6650333</v>
       </c>
       <c r="Z23" s="83">
         <f>ROUNDUP(Y23/$B$9,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AA23" s="82">
         <f>Z23*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="AB23" s="79">
         <f>0.9*AA23*$B$6*(K23-(AA23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC23" s="84">
+        <v>96.02486534</v>
+      </c>
+      <c r="AC23" s="84" t="str">
         <f>IF(AB23&gt;=H23,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD23" s="79">
         <f>0.17*SQRT($B$5)*(E23*1000)*K23/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE23" s="79">
         <f>MAX(I23/0.75-AD23,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF23" s="83">
         <f>IF(AE23&gt;0,MIN($B$11*$B$6*K23/(AE23*1000),MIN(K23/4,6*$B$8,150)),MIN(K23/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG23" s="79">
         <f>0.66*SQRT($B$5)*(E23*1000)*K23/1000</f>
-        <v/>
-      </c>
-      <c r="AH23" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH23" s="84" t="str">
         <f>IF(AE23&lt;=AG23,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI23" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E23*1000)*(F23*1000))^2/(2*((E23*1000)+(F23*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ23" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ23" s="85" t="str">
         <f>IF(J23&gt;AI23,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK23" s="80">
         <f>IF(J23&gt;AI23,J23*1000000/(0.75*2*0.85*((E23*1000-2*$B$7)*(F23*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL23" s="79">
         <f>1.25*R23*$B$6*(K23-(1.25*R23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v/>
+        <v>159.8306178</v>
       </c>
       <c r="AM23" s="79">
         <f>1.25*AA23*$B$6*(K23-(1.25*AA23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v/>
+        <v>130.9219244</v>
       </c>
       <c r="AN23" s="79">
         <f>(AL23+AM23)/B23</f>
-        <v/>
+        <v>72.68813556</v>
       </c>
       <c r="AO23" s="79">
         <f>MAX(I23,AN23)</f>
-        <v/>
+        <v>72.68813556</v>
       </c>
     </row>
     <row r="24">
@@ -4396,127 +4396,127 @@
       </c>
       <c r="K24" s="79">
         <f>F24*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L24" s="80">
         <f>G24*1000000/(0.9*(E24*1000)*K24^2)</f>
-        <v/>
+        <v>3.07746348</v>
       </c>
       <c r="M24" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L24/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.007874408491</v>
       </c>
       <c r="N24" s="82">
         <f>M24*(E24*1000)*K24</f>
-        <v/>
+        <v>809.2135885</v>
       </c>
       <c r="O24" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E24*1000)*K24</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P24" s="82">
         <f>MAX(N24,O24)</f>
-        <v/>
+        <v>809.2135885</v>
       </c>
       <c r="Q24" s="83">
         <f>ROUNDUP(P24/$B$9,0)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="R24" s="82">
         <f>Q24*$B$9</f>
-        <v/>
+        <v>995</v>
       </c>
       <c r="S24" s="79">
         <f>R24*$B$6/(0.85*$B$5*(E24*1000))</f>
-        <v/>
+        <v>58.52941176</v>
       </c>
       <c r="T24" s="79">
         <f>0.9*R24*$B$6*(K24-S24/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U24" s="84">
+        <v>117.829732</v>
+      </c>
+      <c r="U24" s="84" t="str">
         <f>IF(AND(T24&gt;=G24,P24&lt;=0.025*(E24*1000)*K24,P24&gt;=O24),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V24" s="80">
         <f>H24*1000000/(0.9*(E24*1000)*K24^2)</f>
-        <v/>
+        <v>2.241024688</v>
       </c>
       <c r="W24" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V24/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.005613849275</v>
       </c>
       <c r="X24" s="82">
         <f>W24*(E24*1000)*K24</f>
-        <v/>
+        <v>576.9072207</v>
       </c>
       <c r="Y24" s="82">
         <f>MAX(X24,O24)</f>
-        <v/>
+        <v>576.9072207</v>
       </c>
       <c r="Z24" s="83">
         <f>ROUNDUP(Y24/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA24" s="82">
         <f>Z24*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB24" s="79">
         <f>0.9*AA24*$B$6*(K24-(AA24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC24" s="84">
+        <v>73.33945883</v>
+      </c>
+      <c r="AC24" s="84" t="str">
         <f>IF(AB24&gt;=H24,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD24" s="79">
         <f>0.17*SQRT($B$5)*(E24*1000)*K24/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE24" s="79">
         <f>MAX(I24/0.75-AD24,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF24" s="83">
         <f>IF(AE24&gt;0,MIN($B$11*$B$6*K24/(AE24*1000),MIN(K24/4,6*$B$8,150)),MIN(K24/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG24" s="79">
         <f>0.66*SQRT($B$5)*(E24*1000)*K24/1000</f>
-        <v/>
-      </c>
-      <c r="AH24" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH24" s="84" t="str">
         <f>IF(AE24&lt;=AG24,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI24" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E24*1000)*(F24*1000))^2/(2*((E24*1000)+(F24*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ24" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ24" s="85" t="str">
         <f>IF(J24&gt;AI24,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK24" s="80">
         <f>IF(J24&gt;AI24,J24*1000000/(0.75*2*0.85*((E24*1000-2*$B$7)*(F24*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL24" s="79">
         <f>1.25*R24*$B$6*(K24-(1.25*R24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v/>
+        <v>159.8306178</v>
       </c>
       <c r="AM24" s="79">
         <f>1.25*AA24*$B$6*(K24-(1.25*AA24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v/>
+        <v>100.4845159</v>
       </c>
       <c r="AN24" s="79">
         <f>(AL24+AM24)/B24</f>
-        <v/>
+        <v>51.04218309</v>
       </c>
       <c r="AO24" s="79">
         <f>MAX(I24,AN24)</f>
-        <v/>
+        <v>51.04218309</v>
       </c>
     </row>
     <row r="25">
@@ -4556,127 +4556,127 @@
       </c>
       <c r="K25" s="79">
         <f>F25*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L25" s="80">
         <f>G25*1000000/(0.9*(E25*1000)*K25^2)</f>
-        <v/>
+        <v>2.944895822</v>
       </c>
       <c r="M25" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L25/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.007509198435</v>
       </c>
       <c r="N25" s="82">
         <f>M25*(E25*1000)*K25</f>
-        <v/>
+        <v>771.6827771</v>
       </c>
       <c r="O25" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E25*1000)*K25</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="P25" s="82">
         <f>MAX(N25,O25)</f>
-        <v/>
+        <v>771.6827771</v>
       </c>
       <c r="Q25" s="83">
         <f>ROUNDUP(P25/$B$9,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="R25" s="82">
         <f>Q25*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="S25" s="79">
         <f>R25*$B$6/(0.85*$B$5*(E25*1000))</f>
-        <v/>
+        <v>46.82352941</v>
       </c>
       <c r="T25" s="79">
         <f>0.9*R25*$B$6*(K25-S25/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U25" s="84">
+        <v>96.02486534</v>
+      </c>
+      <c r="U25" s="84" t="str">
         <f>IF(AND(T25&gt;=G25,P25&lt;=0.025*(E25*1000)*K25,P25&gt;=O25),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V25" s="80">
         <f>H25*1000000/(0.9*(E25*1000)*K25^2)</f>
-        <v/>
+        <v>2.149489876</v>
       </c>
       <c r="W25" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V25/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.005372514628</v>
       </c>
       <c r="X25" s="82">
         <f>W25*(E25*1000)*K25</f>
-        <v/>
+        <v>552.1064658</v>
       </c>
       <c r="Y25" s="82">
         <f>MAX(X25,O25)</f>
-        <v/>
+        <v>552.1064658</v>
       </c>
       <c r="Z25" s="83">
         <f>ROUNDUP(Y25/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA25" s="82">
         <f>Z25*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB25" s="79">
         <f>0.9*AA25*$B$6*(K25-(AA25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC25" s="84">
+        <v>73.33945883</v>
+      </c>
+      <c r="AC25" s="84" t="str">
         <f>IF(AB25&gt;=H25,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD25" s="79">
         <f>0.17*SQRT($B$5)*(E25*1000)*K25/1000</f>
-        <v/>
+        <v>92.44281538</v>
       </c>
       <c r="AE25" s="79">
         <f>MAX(I25/0.75-AD25,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF25" s="83">
         <f>IF(AE25&gt;0,MIN($B$11*$B$6*K25/(AE25*1000),MIN(K25/4,6*$B$8,150)),MIN(K25/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG25" s="79">
         <f>0.66*SQRT($B$5)*(E25*1000)*K25/1000</f>
-        <v/>
-      </c>
-      <c r="AH25" s="84">
+        <v>358.8956362</v>
+      </c>
+      <c r="AH25" s="84" t="str">
         <f>IF(AE25&lt;=AG25,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI25" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E25*1000)*(F25*1000))^2/(2*((E25*1000)+(F25*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ25" s="85">
+        <v>3.388073536</v>
+      </c>
+      <c r="AJ25" s="85" t="str">
         <f>IF(J25&gt;AI25,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK25" s="80">
         <f>IF(J25&gt;AI25,J25*1000000/(0.75*2*0.85*((E25*1000-2*$B$7)*(F25*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL25" s="79">
         <f>1.25*R25*$B$6*(K25-(1.25*R25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v/>
+        <v>130.9219244</v>
       </c>
       <c r="AM25" s="79">
         <f>1.25*AA25*$B$6*(K25-(1.25*AA25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v/>
+        <v>100.4845159</v>
       </c>
       <c r="AN25" s="79">
         <f>(AL25+AM25)/B25</f>
-        <v/>
+        <v>45.37381183</v>
       </c>
       <c r="AO25" s="79">
         <f>MAX(I25,AN25)</f>
-        <v/>
+        <v>48.5</v>
       </c>
     </row>
     <row r="27">
@@ -5137,127 +5137,127 @@
       </c>
       <c r="K14" s="79">
         <f>F14*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L14" s="80">
         <f>G14*1000000/(0.9*(E14*1000)*K14^2)</f>
-        <v/>
+        <v>1.566462729</v>
       </c>
       <c r="M14" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L14/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.003861223585</v>
       </c>
       <c r="N14" s="82">
         <f>M14*(E14*1000)*K14</f>
-        <v/>
+        <v>462.9317486</v>
       </c>
       <c r="O14" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E14*1000)*K14</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P14" s="82">
         <f>MAX(N14,O14)</f>
-        <v/>
+        <v>462.9317486</v>
       </c>
       <c r="Q14" s="83">
         <f>ROUNDUP(P14/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R14" s="82">
         <f>Q14*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="S14" s="79">
         <f>R14*$B$6/(0.85*$B$5*(E14*1000))</f>
-        <v/>
+        <v>30.10084034</v>
       </c>
       <c r="T14" s="79">
         <f>0.9*R14*$B$6*(K14-S14/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U14" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="U14" s="84" t="str">
         <f>IF(AND(T14&gt;=G14,P14&lt;=0.025*(E14*1000)*K14,P14&gt;=O14),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V14" s="80">
         <f>H14*1000000/(0.9*(E14*1000)*K14^2)</f>
-        <v/>
+        <v>1.48800432</v>
       </c>
       <c r="W14" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V14/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.003661137371</v>
       </c>
       <c r="X14" s="82">
         <f>W14*(E14*1000)*K14</f>
-        <v/>
+        <v>438.9429122</v>
       </c>
       <c r="Y14" s="82">
         <f>MAX(X14,O14)</f>
-        <v/>
+        <v>438.9429122</v>
       </c>
       <c r="Z14" s="83">
         <f>ROUNDUP(Y14/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA14" s="82">
         <f>Z14*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB14" s="79">
         <f>0.9*AA14*$B$6*(K14-(AA14*$B$6/(0.85*$B$5*(E14*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC14" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC14" s="84" t="str">
         <f>IF(AB14&gt;=H14,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD14" s="79">
         <f>0.17*SQRT($B$5)*(E14*1000)*K14/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE14" s="79">
         <f>MAX(I14/0.75-AD14,0)</f>
-        <v/>
+        <v>0.4167153857</v>
       </c>
       <c r="AF14" s="83">
         <f>IF(AE14&gt;0,MIN($B$11*$B$6*K14/(AE14*1000),MIN(K14/4,6*$B$8,150)),MIN(K14/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG14" s="79">
         <f>0.66*SQRT($B$5)*(E14*1000)*K14/1000</f>
-        <v/>
-      </c>
-      <c r="AH14" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH14" s="84" t="str">
         <f>IF(AE14&lt;=AG14,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI14" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E14*1000)*(F14*1000))^2/(2*((E14*1000)+(F14*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ14" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ14" s="85" t="str">
         <f>IF(J14&gt;AI14,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>SI - disenar</v>
       </c>
       <c r="AK14" s="80">
         <f>IF(J14&gt;AI14,J14*1000000/(0.75*2*0.85*((E14*1000-2*$B$7)*(F14*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0.5554691012</v>
       </c>
       <c r="AL14" s="79">
         <f>1.25*R14*$B$6*(K14-(1.25*R14*$B$6/(0.85*$B$5*(E14*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AM14" s="79">
         <f>1.25*AA14*$B$6*(K14-(1.25*AA14*$B$6/(0.85*$B$5*(E14*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN14" s="79">
         <f>(AL14+AM14)/B14</f>
-        <v/>
+        <v>135.2896818</v>
       </c>
       <c r="AO14" s="79">
         <f>MAX(I14,AN14)</f>
-        <v/>
+        <v>135.2896818</v>
       </c>
     </row>
     <row r="15">
@@ -5297,127 +5297,127 @@
       </c>
       <c r="K15" s="79">
         <f>F15*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L15" s="80">
         <f>G15*1000000/(0.9*(E15*1000)*K15^2)</f>
-        <v/>
+        <v>0.8765698175</v>
       </c>
       <c r="M15" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L15/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.002126989381</v>
       </c>
       <c r="N15" s="82">
         <f>M15*(E15*1000)*K15</f>
-        <v/>
+        <v>255.0100743</v>
       </c>
       <c r="O15" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E15*1000)*K15</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P15" s="82">
         <f>MAX(N15,O15)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Q15" s="83">
         <f>ROUNDUP(P15/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R15" s="82">
         <f>Q15*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="S15" s="79">
         <f>R15*$B$6/(0.85*$B$5*(E15*1000))</f>
-        <v/>
+        <v>30.10084034</v>
       </c>
       <c r="T15" s="79">
         <f>0.9*R15*$B$6*(K15-S15/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U15" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="U15" s="84" t="str">
         <f>IF(AND(T15&gt;=G15,P15&lt;=0.025*(E15*1000)*K15,P15&gt;=O15),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V15" s="80">
         <f>H15*1000000/(0.9*(E15*1000)*K15^2)</f>
-        <v/>
+        <v>0.297600864</v>
       </c>
       <c r="W15" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V15/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.0007130598475</v>
       </c>
       <c r="X15" s="82">
         <f>W15*(E15*1000)*K15</f>
-        <v/>
+        <v>85.49052776</v>
       </c>
       <c r="Y15" s="82">
         <f>MAX(X15,O15)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z15" s="83">
         <f>ROUNDUP(Y15/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA15" s="82">
         <f>Z15*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB15" s="79">
         <f>0.9*AA15*$B$6*(K15-(AA15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC15" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC15" s="84" t="str">
         <f>IF(AB15&gt;=H15,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD15" s="79">
         <f>0.17*SQRT($B$5)*(E15*1000)*K15/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE15" s="79">
         <f>MAX(I15/0.75-AD15,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF15" s="83">
         <f>IF(AE15&gt;0,MIN($B$11*$B$6*K15/(AE15*1000),MIN(K15/4,6*$B$8,150)),MIN(K15/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG15" s="79">
         <f>0.66*SQRT($B$5)*(E15*1000)*K15/1000</f>
-        <v/>
-      </c>
-      <c r="AH15" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH15" s="84" t="str">
         <f>IF(AE15&lt;=AG15,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI15" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E15*1000)*(F15*1000))^2/(2*((E15*1000)+(F15*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ15" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ15" s="85" t="str">
         <f>IF(J15&gt;AI15,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK15" s="80">
         <f>IF(J15&gt;AI15,J15*1000000/(0.75*2*0.85*((E15*1000-2*$B$7)*(F15*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL15" s="79">
         <f>1.25*R15*$B$6*(K15-(1.25*R15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AM15" s="79">
         <f>1.25*AA15*$B$6*(K15-(1.25*AA15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN15" s="79">
         <f>(AL15+AM15)/B15</f>
-        <v/>
+        <v>81.17380906</v>
       </c>
       <c r="AO15" s="79">
         <f>MAX(I15,AN15)</f>
-        <v/>
+        <v>81.17380906</v>
       </c>
     </row>
     <row r="16">
@@ -5457,127 +5457,127 @@
       </c>
       <c r="K16" s="79">
         <f>F16*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L16" s="80">
         <f>G16*1000000/(0.9*(E16*1000)*K16^2)</f>
-        <v/>
+        <v>0.7358857727</v>
       </c>
       <c r="M16" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L16/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.001780067576</v>
       </c>
       <c r="N16" s="82">
         <f>M16*(E16*1000)*K16</f>
-        <v/>
+        <v>213.4167518</v>
       </c>
       <c r="O16" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E16*1000)*K16</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P16" s="82">
         <f>MAX(N16,O16)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Q16" s="83">
         <f>ROUNDUP(P16/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R16" s="82">
         <f>Q16*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="S16" s="79">
         <f>R16*$B$6/(0.85*$B$5*(E16*1000))</f>
-        <v/>
+        <v>30.10084034</v>
       </c>
       <c r="T16" s="79">
         <f>0.9*R16*$B$6*(K16-S16/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U16" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="U16" s="84" t="str">
         <f>IF(AND(T16&gt;=G16,P16&lt;=0.025*(E16*1000)*K16,P16&gt;=O16),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V16" s="80">
         <f>H16*1000000/(0.9*(E16*1000)*K16^2)</f>
-        <v/>
+        <v>0.2786626272</v>
       </c>
       <c r="W16" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V16/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.0006674127972</v>
       </c>
       <c r="X16" s="82">
         <f>W16*(E16*1000)*K16</f>
-        <v/>
+        <v>80.01778878</v>
       </c>
       <c r="Y16" s="82">
         <f>MAX(X16,O16)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z16" s="83">
         <f>ROUNDUP(Y16/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA16" s="82">
         <f>Z16*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB16" s="79">
         <f>0.9*AA16*$B$6*(K16-(AA16*$B$6/(0.85*$B$5*(E16*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC16" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC16" s="84" t="str">
         <f>IF(AB16&gt;=H16,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD16" s="79">
         <f>0.17*SQRT($B$5)*(E16*1000)*K16/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE16" s="79">
         <f>MAX(I16/0.75-AD16,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF16" s="83">
         <f>IF(AE16&gt;0,MIN($B$11*$B$6*K16/(AE16*1000),MIN(K16/4,6*$B$8,150)),MIN(K16/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG16" s="79">
         <f>0.66*SQRT($B$5)*(E16*1000)*K16/1000</f>
-        <v/>
-      </c>
-      <c r="AH16" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH16" s="84" t="str">
         <f>IF(AE16&lt;=AG16,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI16" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E16*1000)*(F16*1000))^2/(2*((E16*1000)+(F16*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ16" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ16" s="85" t="str">
         <f>IF(J16&gt;AI16,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK16" s="80">
         <f>IF(J16&gt;AI16,J16*1000000/(0.75*2*0.85*((E16*1000-2*$B$7)*(F16*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL16" s="79">
         <f>1.25*R16*$B$6*(K16-(1.25*R16*$B$6/(0.85*$B$5*(E16*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AM16" s="79">
         <f>1.25*AA16*$B$6*(K16-(1.25*AA16*$B$6/(0.85*$B$5*(E16*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN16" s="79">
         <f>(AL16+AM16)/B16</f>
-        <v/>
+        <v>81.17380906</v>
       </c>
       <c r="AO16" s="79">
         <f>MAX(I16,AN16)</f>
-        <v/>
+        <v>81.17380906</v>
       </c>
     </row>
     <row r="17">
@@ -5617,127 +5617,127 @@
       </c>
       <c r="K17" s="79">
         <f>F17*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L17" s="80">
         <f>G17*1000000/(0.9*(E17*1000)*K17^2)</f>
-        <v/>
+        <v>2.62700399</v>
       </c>
       <c r="M17" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L17/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.006644301483</v>
       </c>
       <c r="N17" s="82">
         <f>M17*(E17*1000)*K17</f>
-        <v/>
+        <v>796.6019155</v>
       </c>
       <c r="O17" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E17*1000)*K17</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P17" s="82">
         <f>MAX(N17,O17)</f>
-        <v/>
+        <v>796.6019155</v>
       </c>
       <c r="Q17" s="83">
         <f>ROUNDUP(P17/$B$9,0)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="R17" s="82">
         <f>Q17*$B$9</f>
-        <v/>
+        <v>995</v>
       </c>
       <c r="S17" s="79">
         <f>R17*$B$6/(0.85*$B$5*(E17*1000))</f>
-        <v/>
+        <v>50.16806723</v>
       </c>
       <c r="T17" s="79">
         <f>0.9*R17*$B$6*(K17-S17/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U17" s="84">
+        <v>119.4021246</v>
+      </c>
+      <c r="U17" s="84" t="str">
         <f>IF(AND(T17&gt;=G17,P17&lt;=0.025*(E17*1000)*K17,P17&gt;=O17),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V17" s="80">
         <f>H17*1000000/(0.9*(E17*1000)*K17^2)</f>
-        <v/>
+        <v>2.348341363</v>
       </c>
       <c r="W17" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V17/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.005898254285</v>
       </c>
       <c r="X17" s="82">
         <f>W17*(E17*1000)*K17</f>
-        <v/>
+        <v>707.1564519</v>
       </c>
       <c r="Y17" s="82">
         <f>MAX(X17,O17)</f>
-        <v/>
+        <v>707.1564519</v>
       </c>
       <c r="Z17" s="83">
         <f>ROUNDUP(Y17/$B$9,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="AA17" s="82">
         <f>Z17*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="AB17" s="79">
         <f>0.9*AA17*$B$6*(K17-(AA17*$B$6/(0.85*$B$5*(E17*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC17" s="84">
+        <v>97.03119664</v>
+      </c>
+      <c r="AC17" s="84" t="str">
         <f>IF(AB17&gt;=H17,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD17" s="79">
         <f>0.17*SQRT($B$5)*(E17*1000)*K17/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE17" s="79">
         <f>MAX(I17/0.75-AD17,0)</f>
-        <v/>
+        <v>97.88338205</v>
       </c>
       <c r="AF17" s="83">
         <f>IF(AE17&gt;0,MIN($B$11*$B$6*K17/(AE17*1000),MIN(K17/4,6*$B$8,150)),MIN(K17/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG17" s="79">
         <f>0.66*SQRT($B$5)*(E17*1000)*K17/1000</f>
-        <v/>
-      </c>
-      <c r="AH17" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH17" s="84" t="str">
         <f>IF(AE17&lt;=AG17,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI17" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E17*1000)*(F17*1000))^2/(2*((E17*1000)+(F17*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ17" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ17" s="85" t="str">
         <f>IF(J17&gt;AI17,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK17" s="80">
         <f>IF(J17&gt;AI17,J17*1000000/(0.75*2*0.85*((E17*1000-2*$B$7)*(F17*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL17" s="79">
         <f>1.25*R17*$B$6*(K17-(1.25*R17*$B$6/(0.85*$B$5*(E17*1000)))/2)/1000000</f>
-        <v/>
+        <v>162.5604662</v>
       </c>
       <c r="AM17" s="79">
         <f>1.25*AA17*$B$6*(K17-(1.25*AA17*$B$6/(0.85*$B$5*(E17*1000)))/2)/1000000</f>
-        <v/>
+        <v>132.6690274</v>
       </c>
       <c r="AN17" s="79">
         <f>(AL17+AM17)/B17</f>
-        <v/>
+        <v>113.5498052</v>
       </c>
       <c r="AO17" s="79">
         <f>MAX(I17,AN17)</f>
-        <v/>
+        <v>154.3</v>
       </c>
     </row>
     <row r="18">
@@ -5777,127 +5777,127 @@
       </c>
       <c r="K18" s="79">
         <f>F18*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L18" s="80">
         <f>G18*1000000/(0.9*(E18*1000)*K18^2)</f>
-        <v/>
+        <v>0.7818786335</v>
       </c>
       <c r="M18" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L18/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.001893242565</v>
       </c>
       <c r="N18" s="82">
         <f>M18*(E18*1000)*K18</f>
-        <v/>
+        <v>226.9855843</v>
       </c>
       <c r="O18" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E18*1000)*K18</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P18" s="82">
         <f>MAX(N18,O18)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Q18" s="83">
         <f>ROUNDUP(P18/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R18" s="82">
         <f>Q18*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="S18" s="79">
         <f>R18*$B$6/(0.85*$B$5*(E18*1000))</f>
-        <v/>
+        <v>30.10084034</v>
       </c>
       <c r="T18" s="79">
         <f>0.9*R18*$B$6*(K18-S18/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U18" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="U18" s="84" t="str">
         <f>IF(AND(T18&gt;=G18,P18&lt;=0.025*(E18*1000)*K18,P18&gt;=O18),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V18" s="80">
         <f>H18*1000000/(0.9*(E18*1000)*K18^2)</f>
-        <v/>
+        <v>0.3895865855</v>
       </c>
       <c r="W18" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V18/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.0009353059067</v>
       </c>
       <c r="X18" s="82">
         <f>W18*(E18*1000)*K18</f>
-        <v/>
+        <v>112.1361634</v>
       </c>
       <c r="Y18" s="82">
         <f>MAX(X18,O18)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z18" s="83">
         <f>ROUNDUP(Y18/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA18" s="82">
         <f>Z18*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB18" s="79">
         <f>0.9*AA18*$B$6*(K18-(AA18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC18" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC18" s="84" t="str">
         <f>IF(AB18&gt;=H18,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD18" s="79">
         <f>0.17*SQRT($B$5)*(E18*1000)*K18/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE18" s="79">
         <f>MAX(I18/0.75-AD18,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF18" s="83">
         <f>IF(AE18&gt;0,MIN($B$11*$B$6*K18/(AE18*1000),MIN(K18/4,6*$B$8,150)),MIN(K18/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG18" s="79">
         <f>0.66*SQRT($B$5)*(E18*1000)*K18/1000</f>
-        <v/>
-      </c>
-      <c r="AH18" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH18" s="84" t="str">
         <f>IF(AE18&lt;=AG18,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI18" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E18*1000)*(F18*1000))^2/(2*((E18*1000)+(F18*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ18" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ18" s="85" t="str">
         <f>IF(J18&gt;AI18,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>SI - disenar</v>
       </c>
       <c r="AK18" s="80">
         <f>IF(J18&gt;AI18,J18*1000000/(0.75*2*0.85*((E18*1000-2*$B$7)*(F18*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0.1383269357</v>
       </c>
       <c r="AL18" s="79">
         <f>1.25*R18*$B$6*(K18-(1.25*R18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AM18" s="79">
         <f>1.25*AA18*$B$6*(K18-(1.25*AA18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN18" s="79">
         <f>(AL18+AM18)/B18</f>
-        <v/>
+        <v>78.05173948</v>
       </c>
       <c r="AO18" s="79">
         <f>MAX(I18,AN18)</f>
-        <v/>
+        <v>78.05173948</v>
       </c>
     </row>
     <row r="19">
@@ -5937,127 +5937,127 @@
       </c>
       <c r="K19" s="79">
         <f>F19*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L19" s="80">
         <f>G19*1000000/(0.9*(E19*1000)*K19^2)</f>
-        <v/>
+        <v>2.194130006</v>
       </c>
       <c r="M19" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L19/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.005490067678</v>
       </c>
       <c r="N19" s="82">
         <f>M19*(E19*1000)*K19</f>
-        <v/>
+        <v>658.217939</v>
       </c>
       <c r="O19" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E19*1000)*K19</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P19" s="82">
         <f>MAX(N19,O19)</f>
-        <v/>
+        <v>658.217939</v>
       </c>
       <c r="Q19" s="83">
         <f>ROUNDUP(P19/$B$9,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="R19" s="82">
         <f>Q19*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="S19" s="79">
         <f>R19*$B$6/(0.85*$B$5*(E19*1000))</f>
-        <v/>
+        <v>40.13445378</v>
       </c>
       <c r="T19" s="79">
         <f>0.9*R19*$B$6*(K19-S19/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U19" s="84">
+        <v>97.03119664</v>
+      </c>
+      <c r="U19" s="84" t="str">
         <f>IF(AND(T19&gt;=G19,P19&lt;=0.025*(E19*1000)*K19,P19&gt;=O19),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V19" s="80">
         <f>H19*1000000/(0.9*(E19*1000)*K19^2)</f>
-        <v/>
+        <v>1.152526982</v>
       </c>
       <c r="W19" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V19/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.002813980878</v>
       </c>
       <c r="X19" s="82">
         <f>W19*(E19*1000)*K19</f>
-        <v/>
+        <v>337.3752024</v>
       </c>
       <c r="Y19" s="82">
         <f>MAX(X19,O19)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z19" s="83">
         <f>ROUNDUP(Y19/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA19" s="82">
         <f>Z19*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB19" s="79">
         <f>0.9*AA19*$B$6*(K19-(AA19*$B$6/(0.85*$B$5*(E19*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC19" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC19" s="84" t="str">
         <f>IF(AB19&gt;=H19,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD19" s="79">
         <f>0.17*SQRT($B$5)*(E19*1000)*K19/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE19" s="79">
         <f>MAX(I19/0.75-AD19,0)</f>
-        <v/>
+        <v>10.41671539</v>
       </c>
       <c r="AF19" s="83">
         <f>IF(AE19&gt;0,MIN($B$11*$B$6*K19/(AE19*1000),MIN(K19/4,6*$B$8,150)),MIN(K19/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG19" s="79">
         <f>0.66*SQRT($B$5)*(E19*1000)*K19/1000</f>
-        <v/>
-      </c>
-      <c r="AH19" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH19" s="84" t="str">
         <f>IF(AE19&lt;=AG19,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI19" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E19*1000)*(F19*1000))^2/(2*((E19*1000)+(F19*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ19" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ19" s="85" t="str">
         <f>IF(J19&gt;AI19,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK19" s="80">
         <f>IF(J19&gt;AI19,J19*1000000/(0.75*2*0.85*((E19*1000-2*$B$7)*(F19*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL19" s="79">
         <f>1.25*R19*$B$6*(K19-(1.25*R19*$B$6/(0.85*$B$5*(E19*1000)))/2)/1000000</f>
-        <v/>
+        <v>132.6690274</v>
       </c>
       <c r="AM19" s="79">
         <f>1.25*AA19*$B$6*(K19-(1.25*AA19*$B$6/(0.85*$B$5*(E19*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN19" s="79">
         <f>(AL19+AM19)/B19</f>
-        <v/>
+        <v>86.71714395</v>
       </c>
       <c r="AO19" s="79">
         <f>MAX(I19,AN19)</f>
-        <v/>
+        <v>88.7</v>
       </c>
     </row>
     <row r="20">
@@ -6097,127 +6097,127 @@
       </c>
       <c r="K20" s="79">
         <f>F20*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L20" s="80">
         <f>G20*1000000/(0.9*(E20*1000)*K20^2)</f>
-        <v/>
+        <v>2.131904371</v>
       </c>
       <c r="M20" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L20/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.005326279752</v>
       </c>
       <c r="N20" s="82">
         <f>M20*(E20*1000)*K20</f>
-        <v/>
+        <v>638.5809952</v>
       </c>
       <c r="O20" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E20*1000)*K20</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P20" s="82">
         <f>MAX(N20,O20)</f>
-        <v/>
+        <v>638.5809952</v>
       </c>
       <c r="Q20" s="83">
         <f>ROUNDUP(P20/$B$9,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="R20" s="82">
         <f>Q20*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="S20" s="79">
         <f>R20*$B$6/(0.85*$B$5*(E20*1000))</f>
-        <v/>
+        <v>40.13445378</v>
       </c>
       <c r="T20" s="79">
         <f>0.9*R20*$B$6*(K20-S20/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U20" s="84">
+        <v>97.03119664</v>
+      </c>
+      <c r="U20" s="84" t="str">
         <f>IF(AND(T20&gt;=G20,P20&lt;=0.025*(E20*1000)*K20,P20&gt;=O20),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V20" s="80">
         <f>H20*1000000/(0.9*(E20*1000)*K20^2)</f>
-        <v/>
+        <v>1.011842937</v>
       </c>
       <c r="W20" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V20/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.002462661944</v>
       </c>
       <c r="X20" s="82">
         <f>W20*(E20*1000)*K20</f>
-        <v/>
+        <v>295.2546971</v>
       </c>
       <c r="Y20" s="82">
         <f>MAX(X20,O20)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z20" s="83">
         <f>ROUNDUP(Y20/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA20" s="82">
         <f>Z20*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB20" s="79">
         <f>0.9*AA20*$B$6*(K20-(AA20*$B$6/(0.85*$B$5*(E20*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC20" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC20" s="84" t="str">
         <f>IF(AB20&gt;=H20,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD20" s="79">
         <f>0.17*SQRT($B$5)*(E20*1000)*K20/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE20" s="79">
         <f>MAX(I20/0.75-AD20,0)</f>
-        <v/>
+        <v>6.683382052</v>
       </c>
       <c r="AF20" s="83">
         <f>IF(AE20&gt;0,MIN($B$11*$B$6*K20/(AE20*1000),MIN(K20/4,6*$B$8,150)),MIN(K20/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG20" s="79">
         <f>0.66*SQRT($B$5)*(E20*1000)*K20/1000</f>
-        <v/>
-      </c>
-      <c r="AH20" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH20" s="84" t="str">
         <f>IF(AE20&lt;=AG20,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI20" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E20*1000)*(F20*1000))^2/(2*((E20*1000)+(F20*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ20" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ20" s="85" t="str">
         <f>IF(J20&gt;AI20,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK20" s="80">
         <f>IF(J20&gt;AI20,J20*1000000/(0.75*2*0.85*((E20*1000-2*$B$7)*(F20*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL20" s="79">
         <f>1.25*R20*$B$6*(K20-(1.25*R20*$B$6/(0.85*$B$5*(E20*1000)))/2)/1000000</f>
-        <v/>
+        <v>132.6690274</v>
       </c>
       <c r="AM20" s="79">
         <f>1.25*AA20*$B$6*(K20-(1.25*AA20*$B$6/(0.85*$B$5*(E20*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN20" s="79">
         <f>(AL20+AM20)/B20</f>
-        <v/>
+        <v>83.6201031</v>
       </c>
       <c r="AO20" s="79">
         <f>MAX(I20,AN20)</f>
-        <v/>
+        <v>85.9</v>
       </c>
     </row>
     <row r="21">
@@ -6257,127 +6257,127 @@
       </c>
       <c r="K21" s="79">
         <f>F21*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L21" s="80">
         <f>G21*1000000/(0.9*(E21*1000)*K21^2)</f>
-        <v/>
+        <v>1.515058944</v>
       </c>
       <c r="M21" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L21/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.003730047188</v>
       </c>
       <c r="N21" s="82">
         <f>M21*(E21*1000)*K21</f>
-        <v/>
+        <v>447.2046825</v>
       </c>
       <c r="O21" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E21*1000)*K21</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P21" s="82">
         <f>MAX(N21,O21)</f>
-        <v/>
+        <v>447.2046825</v>
       </c>
       <c r="Q21" s="83">
         <f>ROUNDUP(P21/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R21" s="82">
         <f>Q21*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="S21" s="79">
         <f>R21*$B$6/(0.85*$B$5*(E21*1000))</f>
-        <v/>
+        <v>30.10084034</v>
       </c>
       <c r="T21" s="79">
         <f>0.9*R21*$B$6*(K21-S21/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U21" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="U21" s="84" t="str">
         <f>IF(AND(T21&gt;=G21,P21&lt;=0.025*(E21*1000)*K21,P21&gt;=O21),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V21" s="80">
         <f>H21*1000000/(0.9*(E21*1000)*K21^2)</f>
-        <v/>
+        <v>1.239101779</v>
       </c>
       <c r="W21" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V21/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.003031320918</v>
       </c>
       <c r="X21" s="82">
         <f>W21*(E21*1000)*K21</f>
-        <v/>
+        <v>363.4326431</v>
       </c>
       <c r="Y21" s="82">
         <f>MAX(X21,O21)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z21" s="83">
         <f>ROUNDUP(Y21/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA21" s="82">
         <f>Z21*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB21" s="79">
         <f>0.9*AA21*$B$6*(K21-(AA21*$B$6/(0.85*$B$5*(E21*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC21" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC21" s="84" t="str">
         <f>IF(AB21&gt;=H21,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD21" s="79">
         <f>0.17*SQRT($B$5)*(E21*1000)*K21/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE21" s="79">
         <f>MAX(I21/0.75-AD21,0)</f>
-        <v/>
+        <v>19.35004872</v>
       </c>
       <c r="AF21" s="83">
         <f>IF(AE21&gt;0,MIN($B$11*$B$6*K21/(AE21*1000),MIN(K21/4,6*$B$8,150)),MIN(K21/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG21" s="79">
         <f>0.66*SQRT($B$5)*(E21*1000)*K21/1000</f>
-        <v/>
-      </c>
-      <c r="AH21" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH21" s="84" t="str">
         <f>IF(AE21&lt;=AG21,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI21" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E21*1000)*(F21*1000))^2/(2*((E21*1000)+(F21*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ21" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ21" s="85" t="str">
         <f>IF(J21&gt;AI21,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK21" s="80">
         <f>IF(J21&gt;AI21,J21*1000000/(0.75*2*0.85*((E21*1000-2*$B$7)*(F21*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL21" s="79">
         <f>1.25*R21*$B$6*(K21-(1.25*R21*$B$6/(0.85*$B$5*(E21*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AM21" s="79">
         <f>1.25*AA21*$B$6*(K21-(1.25*AA21*$B$6/(0.85*$B$5*(E21*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN21" s="79">
         <f>(AL21+AM21)/B21</f>
-        <v/>
+        <v>68.79136361</v>
       </c>
       <c r="AO21" s="79">
         <f>MAX(I21,AN21)</f>
-        <v/>
+        <v>95.4</v>
       </c>
     </row>
     <row r="22">
@@ -6417,127 +6417,127 @@
       </c>
       <c r="K22" s="79">
         <f>F22*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L22" s="80">
         <f>G22*1000000/(0.9*(E22*1000)*K22^2)</f>
-        <v/>
+        <v>1.055130336</v>
       </c>
       <c r="M22" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L22/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.002570517068</v>
       </c>
       <c r="N22" s="82">
         <f>M22*(E22*1000)*K22</f>
-        <v/>
+        <v>308.1857175</v>
       </c>
       <c r="O22" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E22*1000)*K22</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P22" s="82">
         <f>MAX(N22,O22)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Q22" s="83">
         <f>ROUNDUP(P22/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R22" s="82">
         <f>Q22*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="S22" s="79">
         <f>R22*$B$6/(0.85*$B$5*(E22*1000))</f>
-        <v/>
+        <v>30.10084034</v>
       </c>
       <c r="T22" s="79">
         <f>0.9*R22*$B$6*(K22-S22/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U22" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="U22" s="84" t="str">
         <f>IF(AND(T22&gt;=G22,P22&lt;=0.025*(E22*1000)*K22,P22&gt;=O22),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V22" s="80">
         <f>H22*1000000/(0.9*(E22*1000)*K22^2)</f>
-        <v/>
+        <v>0.4031138975</v>
       </c>
       <c r="W22" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V22/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.0009680639453</v>
       </c>
       <c r="X22" s="82">
         <f>W22*(E22*1000)*K22</f>
-        <v/>
+        <v>116.0636066</v>
       </c>
       <c r="Y22" s="82">
         <f>MAX(X22,O22)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z22" s="83">
         <f>ROUNDUP(Y22/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA22" s="82">
         <f>Z22*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB22" s="79">
         <f>0.9*AA22*$B$6*(K22-(AA22*$B$6/(0.85*$B$5*(E22*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC22" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC22" s="84" t="str">
         <f>IF(AB22&gt;=H22,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD22" s="79">
         <f>0.17*SQRT($B$5)*(E22*1000)*K22/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE22" s="79">
         <f>MAX(I22/0.75-AD22,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF22" s="83">
         <f>IF(AE22&gt;0,MIN($B$11*$B$6*K22/(AE22*1000),MIN(K22/4,6*$B$8,150)),MIN(K22/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG22" s="79">
         <f>0.66*SQRT($B$5)*(E22*1000)*K22/1000</f>
-        <v/>
-      </c>
-      <c r="AH22" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH22" s="84" t="str">
         <f>IF(AE22&lt;=AG22,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI22" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E22*1000)*(F22*1000))^2/(2*((E22*1000)+(F22*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ22" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ22" s="85" t="str">
         <f>IF(J22&gt;AI22,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK22" s="80">
         <f>IF(J22&gt;AI22,J22*1000000/(0.75*2*0.85*((E22*1000-2*$B$7)*(F22*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL22" s="79">
         <f>1.25*R22*$B$6*(K22-(1.25*R22*$B$6/(0.85*$B$5*(E22*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AM22" s="79">
         <f>1.25*AA22*$B$6*(K22-(1.25*AA22*$B$6/(0.85*$B$5*(E22*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN22" s="79">
         <f>(AL22+AM22)/B22</f>
-        <v/>
+        <v>61.49530989</v>
       </c>
       <c r="AO22" s="79">
         <f>MAX(I22,AN22)</f>
-        <v/>
+        <v>61.49530989</v>
       </c>
     </row>
     <row r="23">
@@ -6577,127 +6577,127 @@
       </c>
       <c r="K23" s="79">
         <f>F23*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L23" s="80">
         <f>G23*1000000/(0.9*(E23*1000)*K23^2)</f>
-        <v/>
+        <v>0.9983156254</v>
       </c>
       <c r="M23" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L23/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.002429001202</v>
       </c>
       <c r="N23" s="82">
         <f>M23*(E23*1000)*K23</f>
-        <v/>
+        <v>291.2190266</v>
       </c>
       <c r="O23" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E23*1000)*K23</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P23" s="82">
         <f>MAX(N23,O23)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Q23" s="83">
         <f>ROUNDUP(P23/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R23" s="82">
         <f>Q23*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="S23" s="79">
         <f>R23*$B$6/(0.85*$B$5*(E23*1000))</f>
-        <v/>
+        <v>30.10084034</v>
       </c>
       <c r="T23" s="79">
         <f>0.9*R23*$B$6*(K23-S23/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U23" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="U23" s="84" t="str">
         <f>IF(AND(T23&gt;=G23,P23&lt;=0.025*(E23*1000)*K23,P23&gt;=O23),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V23" s="80">
         <f>H23*1000000/(0.9*(E23*1000)*K23^2)</f>
-        <v/>
+        <v>0.3977029727</v>
       </c>
       <c r="W23" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V23/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.0009549584185</v>
       </c>
       <c r="X23" s="82">
         <f>W23*(E23*1000)*K23</f>
-        <v/>
+        <v>114.4923522</v>
       </c>
       <c r="Y23" s="82">
         <f>MAX(X23,O23)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z23" s="83">
         <f>ROUNDUP(Y23/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA23" s="82">
         <f>Z23*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB23" s="79">
         <f>0.9*AA23*$B$6*(K23-(AA23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC23" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC23" s="84" t="str">
         <f>IF(AB23&gt;=H23,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD23" s="79">
         <f>0.17*SQRT($B$5)*(E23*1000)*K23/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE23" s="79">
         <f>MAX(I23/0.75-AD23,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF23" s="83">
         <f>IF(AE23&gt;0,MIN($B$11*$B$6*K23/(AE23*1000),MIN(K23/4,6*$B$8,150)),MIN(K23/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG23" s="79">
         <f>0.66*SQRT($B$5)*(E23*1000)*K23/1000</f>
-        <v/>
-      </c>
-      <c r="AH23" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH23" s="84" t="str">
         <f>IF(AE23&lt;=AG23,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI23" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E23*1000)*(F23*1000))^2/(2*((E23*1000)+(F23*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ23" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ23" s="85" t="str">
         <f>IF(J23&gt;AI23,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK23" s="80">
         <f>IF(J23&gt;AI23,J23*1000000/(0.75*2*0.85*((E23*1000-2*$B$7)*(F23*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL23" s="79">
         <f>1.25*R23*$B$6*(K23-(1.25*R23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AM23" s="79">
         <f>1.25*AA23*$B$6*(K23-(1.25*AA23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN23" s="79">
         <f>(AL23+AM23)/B23</f>
-        <v/>
+        <v>61.49530989</v>
       </c>
       <c r="AO23" s="79">
         <f>MAX(I23,AN23)</f>
-        <v/>
+        <v>61.49530989</v>
       </c>
     </row>
     <row r="24">
@@ -6737,127 +6737,127 @@
       </c>
       <c r="K24" s="79">
         <f>F24*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L24" s="80">
         <f>G24*1000000/(0.9*(E24*1000)*K24^2)</f>
-        <v/>
+        <v>1.030781174</v>
       </c>
       <c r="M24" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L24/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.00250982213</v>
       </c>
       <c r="N24" s="82">
         <f>M24*(E24*1000)*K24</f>
-        <v/>
+        <v>300.9088498</v>
       </c>
       <c r="O24" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E24*1000)*K24</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P24" s="82">
         <f>MAX(N24,O24)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Q24" s="83">
         <f>ROUNDUP(P24/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R24" s="82">
         <f>Q24*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="S24" s="79">
         <f>R24*$B$6/(0.85*$B$5*(E24*1000))</f>
-        <v/>
+        <v>30.10084034</v>
       </c>
       <c r="T24" s="79">
         <f>0.9*R24*$B$6*(K24-S24/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U24" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="U24" s="84" t="str">
         <f>IF(AND(T24&gt;=G24,P24&lt;=0.025*(E24*1000)*K24,P24&gt;=O24),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V24" s="80">
         <f>H24*1000000/(0.9*(E24*1000)*K24^2)</f>
-        <v/>
+        <v>0.9360899903</v>
       </c>
       <c r="W24" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V24/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.002274430093</v>
       </c>
       <c r="X24" s="82">
         <f>W24*(E24*1000)*K24</f>
-        <v/>
+        <v>272.68711</v>
       </c>
       <c r="Y24" s="82">
         <f>MAX(X24,O24)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z24" s="83">
         <f>ROUNDUP(Y24/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA24" s="82">
         <f>Z24*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB24" s="79">
         <f>0.9*AA24*$B$6*(K24-(AA24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC24" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC24" s="84" t="str">
         <f>IF(AB24&gt;=H24,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD24" s="79">
         <f>0.17*SQRT($B$5)*(E24*1000)*K24/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE24" s="79">
         <f>MAX(I24/0.75-AD24,0)</f>
-        <v/>
+        <v>38.41671539</v>
       </c>
       <c r="AF24" s="83">
         <f>IF(AE24&gt;0,MIN($B$11*$B$6*K24/(AE24*1000),MIN(K24/4,6*$B$8,150)),MIN(K24/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG24" s="79">
         <f>0.66*SQRT($B$5)*(E24*1000)*K24/1000</f>
-        <v/>
-      </c>
-      <c r="AH24" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH24" s="84" t="str">
         <f>IF(AE24&lt;=AG24,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI24" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E24*1000)*(F24*1000))^2/(2*((E24*1000)+(F24*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ24" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ24" s="85" t="str">
         <f>IF(J24&gt;AI24,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>SI - disenar</v>
       </c>
       <c r="AK24" s="80">
         <f>IF(J24&gt;AI24,J24*1000000/(0.75*2*0.85*((E24*1000-2*$B$7)*(F24*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0.1231974271</v>
       </c>
       <c r="AL24" s="79">
         <f>1.25*R24*$B$6*(K24-(1.25*R24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AM24" s="79">
         <f>1.25*AA24*$B$6*(K24-(1.25*AA24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN24" s="79">
         <f>(AL24+AM24)/B24</f>
-        <v/>
+        <v>55.59849936</v>
       </c>
       <c r="AO24" s="79">
         <f>MAX(I24,AN24)</f>
-        <v/>
+        <v>109.7</v>
       </c>
     </row>
     <row r="25">
@@ -6897,127 +6897,127 @@
       </c>
       <c r="K25" s="79">
         <f>F25*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L25" s="80">
         <f>G25*1000000/(0.9*(E25*1000)*K25^2)</f>
-        <v/>
+        <v>1.263450941</v>
       </c>
       <c r="M25" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L25/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.003092606666</v>
       </c>
       <c r="N25" s="82">
         <f>M25*(E25*1000)*K25</f>
-        <v/>
+        <v>370.7803447</v>
       </c>
       <c r="O25" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E25*1000)*K25</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P25" s="82">
         <f>MAX(N25,O25)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Q25" s="83">
         <f>ROUNDUP(P25/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R25" s="82">
         <f>Q25*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="S25" s="79">
         <f>R25*$B$6/(0.85*$B$5*(E25*1000))</f>
-        <v/>
+        <v>30.10084034</v>
       </c>
       <c r="T25" s="79">
         <f>0.9*R25*$B$6*(K25-S25/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U25" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="U25" s="84" t="str">
         <f>IF(AND(T25&gt;=G25,P25&lt;=0.025*(E25*1000)*K25,P25&gt;=O25),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V25" s="80">
         <f>H25*1000000/(0.9*(E25*1000)*K25^2)</f>
-        <v/>
+        <v>0.9469118398</v>
       </c>
       <c r="W25" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V25/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.002301280456</v>
       </c>
       <c r="X25" s="82">
         <f>W25*(E25*1000)*K25</f>
-        <v/>
+        <v>275.9062671</v>
       </c>
       <c r="Y25" s="82">
         <f>MAX(X25,O25)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z25" s="83">
         <f>ROUNDUP(Y25/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA25" s="82">
         <f>Z25*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB25" s="79">
         <f>0.9*AA25*$B$6*(K25-(AA25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC25" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC25" s="84" t="str">
         <f>IF(AB25&gt;=H25,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD25" s="79">
         <f>0.17*SQRT($B$5)*(E25*1000)*K25/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE25" s="79">
         <f>MAX(I25/0.75-AD25,0)</f>
-        <v/>
+        <v>39.61671539</v>
       </c>
       <c r="AF25" s="83">
         <f>IF(AE25&gt;0,MIN($B$11*$B$6*K25/(AE25*1000),MIN(K25/4,6*$B$8,150)),MIN(K25/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG25" s="79">
         <f>0.66*SQRT($B$5)*(E25*1000)*K25/1000</f>
-        <v/>
-      </c>
-      <c r="AH25" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH25" s="84" t="str">
         <f>IF(AE25&lt;=AG25,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI25" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E25*1000)*(F25*1000))^2/(2*((E25*1000)+(F25*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ25" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ25" s="85" t="str">
         <f>IF(J25&gt;AI25,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>SI - disenar</v>
       </c>
       <c r="AK25" s="80">
         <f>IF(J25&gt;AI25,J25*1000000/(0.75*2*0.85*((E25*1000-2*$B$7)*(F25*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0.1296815022</v>
       </c>
       <c r="AL25" s="79">
         <f>1.25*R25*$B$6*(K25-(1.25*R25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AM25" s="79">
         <f>1.25*AA25*$B$6*(K25-(1.25*AA25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN25" s="79">
         <f>(AL25+AM25)/B25</f>
-        <v/>
+        <v>55.59849936</v>
       </c>
       <c r="AO25" s="79">
         <f>MAX(I25,AN25)</f>
-        <v/>
+        <v>110.6</v>
       </c>
     </row>
     <row r="26">
@@ -7057,127 +7057,127 @@
       </c>
       <c r="K26" s="79">
         <f>F26*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L26" s="80">
         <f>G26*1000000/(0.9*(E26*1000)*K26^2)</f>
-        <v/>
+        <v>1.763961485</v>
       </c>
       <c r="M26" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L26/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.00436827755</v>
       </c>
       <c r="N26" s="82">
         <f>M26*(E26*1000)*K26</f>
-        <v/>
+        <v>523.7237162</v>
       </c>
       <c r="O26" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E26*1000)*K26</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P26" s="82">
         <f>MAX(N26,O26)</f>
-        <v/>
+        <v>523.7237162</v>
       </c>
       <c r="Q26" s="83">
         <f>ROUNDUP(P26/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R26" s="82">
         <f>Q26*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="S26" s="79">
         <f>R26*$B$6/(0.85*$B$5*(E26*1000))</f>
-        <v/>
+        <v>30.10084034</v>
       </c>
       <c r="T26" s="79">
         <f>0.9*R26*$B$6*(K26-S26/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U26" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="U26" s="84" t="str">
         <f>IF(AND(T26&gt;=G26,P26&lt;=0.025*(E26*1000)*K26,P26&gt;=O26),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V26" s="80">
         <f>H26*1000000/(0.9*(E26*1000)*K26^2)</f>
-        <v/>
+        <v>0.6168454271</v>
       </c>
       <c r="W26" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V26/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.001488221982</v>
       </c>
       <c r="X26" s="82">
         <f>W26*(E26*1000)*K26</f>
-        <v/>
+        <v>178.426654</v>
       </c>
       <c r="Y26" s="82">
         <f>MAX(X26,O26)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z26" s="83">
         <f>ROUNDUP(Y26/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA26" s="82">
         <f>Z26*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB26" s="79">
         <f>0.9*AA26*$B$6*(K26-(AA26*$B$6/(0.85*$B$5*(E26*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC26" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC26" s="84" t="str">
         <f>IF(AB26&gt;=H26,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD26" s="79">
         <f>0.17*SQRT($B$5)*(E26*1000)*K26/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE26" s="79">
         <f>MAX(I26/0.75-AD26,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF26" s="83">
         <f>IF(AE26&gt;0,MIN($B$11*$B$6*K26/(AE26*1000),MIN(K26/4,6*$B$8,150)),MIN(K26/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG26" s="79">
         <f>0.66*SQRT($B$5)*(E26*1000)*K26/1000</f>
-        <v/>
-      </c>
-      <c r="AH26" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH26" s="84" t="str">
         <f>IF(AE26&lt;=AG26,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI26" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E26*1000)*(F26*1000))^2/(2*((E26*1000)+(F26*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ26" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ26" s="85" t="str">
         <f>IF(J26&gt;AI26,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK26" s="80">
         <f>IF(J26&gt;AI26,J26*1000000/(0.75*2*0.85*((E26*1000-2*$B$7)*(F26*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL26" s="79">
         <f>1.25*R26*$B$6*(K26-(1.25*R26*$B$6/(0.85*$B$5*(E26*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AM26" s="79">
         <f>1.25*AA26*$B$6*(K26-(1.25*AA26*$B$6/(0.85*$B$5*(E26*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN26" s="79">
         <f>(AL26+AM26)/B26</f>
-        <v/>
+        <v>50.73363066</v>
       </c>
       <c r="AO26" s="79">
         <f>MAX(I26,AN26)</f>
-        <v/>
+        <v>74</v>
       </c>
     </row>
     <row r="27">
@@ -7217,127 +7217,127 @@
       </c>
       <c r="K27" s="79">
         <f>F27*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L27" s="80">
         <f>G27*1000000/(0.9*(E27*1000)*K27^2)</f>
-        <v/>
+        <v>1.647626601</v>
       </c>
       <c r="M27" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L27/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.004069010286</v>
       </c>
       <c r="N27" s="82">
         <f>M27*(E27*1000)*K27</f>
-        <v/>
+        <v>487.8438157</v>
       </c>
       <c r="O27" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E27*1000)*K27</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P27" s="82">
         <f>MAX(N27,O27)</f>
-        <v/>
+        <v>487.8438157</v>
       </c>
       <c r="Q27" s="83">
         <f>ROUNDUP(P27/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="R27" s="82">
         <f>Q27*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="S27" s="79">
         <f>R27*$B$6/(0.85*$B$5*(E27*1000))</f>
-        <v/>
+        <v>30.10084034</v>
       </c>
       <c r="T27" s="79">
         <f>0.9*R27*$B$6*(K27-S27/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U27" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="U27" s="84" t="str">
         <f>IF(AND(T27&gt;=G27,P27&lt;=0.025*(E27*1000)*K27,P27&gt;=O27),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V27" s="80">
         <f>H27*1000000/(0.9*(E27*1000)*K27^2)</f>
-        <v/>
+        <v>0.7440021599</v>
       </c>
       <c r="W27" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V27/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.001800022669</v>
       </c>
       <c r="X27" s="82">
         <f>W27*(E27*1000)*K27</f>
-        <v/>
+        <v>215.8092179</v>
       </c>
       <c r="Y27" s="82">
         <f>MAX(X27,O27)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z27" s="83">
         <f>ROUNDUP(Y27/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA27" s="82">
         <f>Z27*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB27" s="79">
         <f>0.9*AA27*$B$6*(K27-(AA27*$B$6/(0.85*$B$5*(E27*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC27" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC27" s="84" t="str">
         <f>IF(AB27&gt;=H27,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD27" s="79">
         <f>0.17*SQRT($B$5)*(E27*1000)*K27/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE27" s="79">
         <f>MAX(I27/0.75-AD27,0)</f>
-        <v/>
+        <v>5.750048719</v>
       </c>
       <c r="AF27" s="83">
         <f>IF(AE27&gt;0,MIN($B$11*$B$6*K27/(AE27*1000),MIN(K27/4,6*$B$8,150)),MIN(K27/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG27" s="79">
         <f>0.66*SQRT($B$5)*(E27*1000)*K27/1000</f>
-        <v/>
-      </c>
-      <c r="AH27" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH27" s="84" t="str">
         <f>IF(AE27&lt;=AG27,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI27" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E27*1000)*(F27*1000))^2/(2*((E27*1000)+(F27*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ27" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ27" s="85" t="str">
         <f>IF(J27&gt;AI27,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>SI - disenar</v>
       </c>
       <c r="AK27" s="80">
         <f>IF(J27&gt;AI27,J27*1000000/(0.75*2*0.85*((E27*1000-2*$B$7)*(F27*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0.1188747104</v>
       </c>
       <c r="AL27" s="79">
         <f>1.25*R27*$B$6*(K27-(1.25*R27*$B$6/(0.85*$B$5*(E27*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AM27" s="79">
         <f>1.25*AA27*$B$6*(K27-(1.25*AA27*$B$6/(0.85*$B$5*(E27*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN27" s="79">
         <f>(AL27+AM27)/B27</f>
-        <v/>
+        <v>50.73363066</v>
       </c>
       <c r="AO27" s="79">
         <f>MAX(I27,AN27)</f>
-        <v/>
+        <v>85.2</v>
       </c>
     </row>
     <row r="28">
@@ -7377,127 +7377,127 @@
       </c>
       <c r="K28" s="79">
         <f>F28*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L28" s="80">
         <f>G28*1000000/(0.9*(E28*1000)*K28^2)</f>
-        <v/>
+        <v>2.110260672</v>
       </c>
       <c r="M28" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L28/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.005269432385</v>
       </c>
       <c r="N28" s="82">
         <f>M28*(E28*1000)*K28</f>
-        <v/>
+        <v>631.7654223</v>
       </c>
       <c r="O28" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E28*1000)*K28</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P28" s="82">
         <f>MAX(N28,O28)</f>
-        <v/>
+        <v>631.7654223</v>
       </c>
       <c r="Q28" s="83">
         <f>ROUNDUP(P28/$B$9,0)</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="R28" s="82">
         <f>Q28*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="S28" s="79">
         <f>R28*$B$6/(0.85*$B$5*(E28*1000))</f>
-        <v/>
+        <v>40.13445378</v>
       </c>
       <c r="T28" s="79">
         <f>0.9*R28*$B$6*(K28-S28/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U28" s="84">
+        <v>97.03119664</v>
+      </c>
+      <c r="U28" s="84" t="str">
         <f>IF(AND(T28&gt;=G28,P28&lt;=0.025*(E28*1000)*K28,P28&gt;=O28),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V28" s="80">
         <f>H28*1000000/(0.9*(E28*1000)*K28^2)</f>
-        <v/>
+        <v>0.7088311487</v>
       </c>
       <c r="W28" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V28/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.001713602932</v>
       </c>
       <c r="X28" s="82">
         <f>W28*(E28*1000)*K28</f>
-        <v/>
+        <v>205.4481395</v>
       </c>
       <c r="Y28" s="82">
         <f>MAX(X28,O28)</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="Z28" s="83">
         <f>ROUNDUP(Y28/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA28" s="82">
         <f>Z28*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB28" s="79">
         <f>0.9*AA28*$B$6*(K28-(AA28*$B$6/(0.85*$B$5*(E28*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC28" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC28" s="84" t="str">
         <f>IF(AB28&gt;=H28,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD28" s="79">
         <f>0.17*SQRT($B$5)*(E28*1000)*K28/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE28" s="79">
         <f>MAX(I28/0.75-AD28,0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AF28" s="83">
         <f>IF(AE28&gt;0,MIN($B$11*$B$6*K28/(AE28*1000),MIN(K28/4,6*$B$8,150)),MIN(K28/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG28" s="79">
         <f>0.66*SQRT($B$5)*(E28*1000)*K28/1000</f>
-        <v/>
-      </c>
-      <c r="AH28" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH28" s="84" t="str">
         <f>IF(AE28&lt;=AG28,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI28" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E28*1000)*(F28*1000))^2/(2*((E28*1000)+(F28*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ28" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ28" s="85" t="str">
         <f>IF(J28&gt;AI28,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK28" s="80">
         <f>IF(J28&gt;AI28,J28*1000000/(0.75*2*0.85*((E28*1000-2*$B$7)*(F28*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL28" s="79">
         <f>1.25*R28*$B$6*(K28-(1.25*R28*$B$6/(0.85*$B$5*(E28*1000)))/2)/1000000</f>
-        <v/>
+        <v>132.6690274</v>
       </c>
       <c r="AM28" s="79">
         <f>1.25*AA28*$B$6*(K28-(1.25*AA28*$B$6/(0.85*$B$5*(E28*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN28" s="79">
         <f>(AL28+AM28)/B28</f>
-        <v/>
+        <v>56.01346619</v>
       </c>
       <c r="AO28" s="79">
         <f>MAX(I28,AN28)</f>
-        <v/>
+        <v>79.2</v>
       </c>
     </row>
     <row r="29">
@@ -7537,127 +7537,127 @@
       </c>
       <c r="K29" s="79">
         <f>F29*1000-$B$7-$B$10-$B$8/2</f>
-        <v/>
+        <v>342.55</v>
       </c>
       <c r="L29" s="80">
         <f>G29*1000000/(0.9*(E29*1000)*K29^2)</f>
-        <v/>
+        <v>2.808269971</v>
       </c>
       <c r="M29" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L29/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.007135626135</v>
       </c>
       <c r="N29" s="82">
         <f>M29*(E29*1000)*K29</f>
-        <v/>
+        <v>855.5080564</v>
       </c>
       <c r="O29" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E29*1000)*K29</f>
-        <v/>
+        <v>399.6416667</v>
       </c>
       <c r="P29" s="82">
         <f>MAX(N29,O29)</f>
-        <v/>
+        <v>855.5080564</v>
       </c>
       <c r="Q29" s="83">
         <f>ROUNDUP(P29/$B$9,0)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="R29" s="82">
         <f>Q29*$B$9</f>
-        <v/>
+        <v>995</v>
       </c>
       <c r="S29" s="79">
         <f>R29*$B$6/(0.85*$B$5*(E29*1000))</f>
-        <v/>
+        <v>50.16806723</v>
       </c>
       <c r="T29" s="79">
         <f>0.9*R29*$B$6*(K29-S29/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="U29" s="84">
+        <v>119.4021246</v>
+      </c>
+      <c r="U29" s="84" t="str">
         <f>IF(AND(T29&gt;=G29,P29&lt;=0.025*(E29*1000)*K29,P29&gt;=O29),"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="V29" s="80">
         <f>H29*1000000/(0.9*(E29*1000)*K29^2)</f>
-        <v/>
+        <v>1.368963974</v>
       </c>
       <c r="W29" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V29/(0.85*$B$5)))</f>
-        <v/>
+        <v>0.003358992417</v>
       </c>
       <c r="X29" s="82">
         <f>W29*(E29*1000)*K29</f>
-        <v/>
+        <v>402.7179983</v>
       </c>
       <c r="Y29" s="82">
         <f>MAX(X29,O29)</f>
-        <v/>
+        <v>402.7179983</v>
       </c>
       <c r="Z29" s="83">
         <f>ROUNDUP(Y29/$B$9,0)</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="AA29" s="82">
         <f>Z29*$B$9</f>
-        <v/>
+        <v>597</v>
       </c>
       <c r="AB29" s="79">
         <f>0.9*AA29*$B$6*(K29-(AA29*$B$6/(0.85*$B$5*(E29*1000)))/2)/1000000</f>
-        <v/>
-      </c>
-      <c r="AC29" s="84">
+        <v>73.90552018</v>
+      </c>
+      <c r="AC29" s="84" t="str">
         <f>IF(AB29&gt;=H29,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AD29" s="79">
         <f>0.17*SQRT($B$5)*(E29*1000)*K29/1000</f>
-        <v/>
+        <v>107.8499513</v>
       </c>
       <c r="AE29" s="79">
         <f>MAX(I29/0.75-AD29,0)</f>
-        <v/>
+        <v>43.21671539</v>
       </c>
       <c r="AF29" s="83">
         <f>IF(AE29&gt;0,MIN($B$11*$B$6*K29/(AE29*1000),MIN(K29/4,6*$B$8,150)),MIN(K29/4,6*$B$8,150))</f>
-        <v/>
+        <v>85.6375</v>
       </c>
       <c r="AG29" s="79">
         <f>0.66*SQRT($B$5)*(E29*1000)*K29/1000</f>
-        <v/>
-      </c>
-      <c r="AH29" s="84">
+        <v>418.7115756</v>
+      </c>
+      <c r="AH29" s="84" t="str">
         <f>IF(AE29&lt;=AG29,"CUMPLE","AUMENTAR SECCION")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="AI29" s="79">
         <f>0.75*0.083*SQRT($B$5)*(((E29*1000)*(F29*1000))^2/(2*((E29*1000)+(F29*1000))))/1000000</f>
-        <v/>
-      </c>
-      <c r="AJ29" s="85">
+        <v>4.304108233</v>
+      </c>
+      <c r="AJ29" s="85" t="str">
         <f>IF(J29&gt;AI29,"SI - disenar","No - despreciable")</f>
-        <v/>
+        <v>No - despreciable</v>
       </c>
       <c r="AK29" s="80">
         <f>IF(J29&gt;AI29,J29*1000000/(0.75*2*0.85*((E29*1000-2*$B$7)*(F29*1000-2*$B$7))*$B$6),0)</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="AL29" s="79">
         <f>1.25*R29*$B$6*(K29-(1.25*R29*$B$6/(0.85*$B$5*(E29*1000)))/2)/1000000</f>
-        <v/>
+        <v>162.5604662</v>
       </c>
       <c r="AM29" s="79">
         <f>1.25*AA29*$B$6*(K29-(1.25*AA29*$B$6/(0.85*$B$5*(E29*1000)))/2)/1000000</f>
-        <v/>
+        <v>101.4672613</v>
       </c>
       <c r="AN29" s="79">
         <f>(AL29+AM29)/B29</f>
-        <v/>
+        <v>48.00504136</v>
       </c>
       <c r="AO29" s="79">
         <f>MAX(I29,AN29)</f>
-        <v/>
+        <v>113.3</v>
       </c>
     </row>
     <row r="31">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="C16" s="19">
         <f>C8*1000-C11*1000-C12/2</f>
-        <v/>
+        <v>303.65</v>
       </c>
     </row>
     <row r="17">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C17" s="19">
         <f>(1.2*C14+1.6*C15)*C10</f>
-        <v/>
+        <v>9.0624</v>
       </c>
     </row>
     <row r="18">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="C18" s="21">
         <f>MAX(0.25*SQRT(C5)/C6,1.4/C6)*C7*1000*C16</f>
-        <v/>
+        <v>151.825</v>
       </c>
     </row>
     <row r="19">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="C19" s="21">
         <f>0.17*SQRT(C5)*C7*1000*C16/1000</f>
-        <v/>
+        <v>40.97250167</v>
       </c>
     </row>
     <row r="20">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="C20" s="21">
         <f>0.75*1.1*C19</f>
-        <v/>
+        <v>33.80231387</v>
       </c>
     </row>
     <row r="22">
@@ -7945,19 +7945,19 @@
       </c>
       <c r="C25" s="19">
         <f>MIN(C24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>462.5</v>
       </c>
       <c r="D25" s="19">
         <f>MIN(D24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="E25" s="19">
         <f>MIN(E24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="F25" s="19">
         <f>MIN(F24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
     </row>
     <row r="26">
@@ -7968,19 +7968,19 @@
       </c>
       <c r="C26" s="19">
         <f>$C$17*C24^2/10</f>
-        <v/>
+        <v>3.1016064</v>
       </c>
       <c r="D26" s="19">
         <f>$C$17*D24^2/10</f>
-        <v/>
+        <v>9.57216</v>
       </c>
       <c r="E26" s="19">
         <f>$C$17*E24^2/10</f>
-        <v/>
+        <v>17.9458176</v>
       </c>
       <c r="F26" s="19">
         <f>$C$17*F24^2/10</f>
-        <v/>
+        <v>20.8797696</v>
       </c>
     </row>
     <row r="27">
@@ -7991,19 +7991,19 @@
       </c>
       <c r="C27" s="19">
         <f>$C$17*C24^2/14</f>
-        <v/>
+        <v>2.215433143</v>
       </c>
       <c r="D27" s="19">
         <f>$C$17*D24^2/14</f>
-        <v/>
+        <v>6.837257143</v>
       </c>
       <c r="E27" s="19">
         <f>$C$17*E24^2/14</f>
-        <v/>
+        <v>12.81844114</v>
       </c>
       <c r="F27" s="19">
         <f>$C$17*F24^2/14</f>
-        <v/>
+        <v>14.91412114</v>
       </c>
     </row>
     <row r="28">
@@ -8014,19 +8014,19 @@
       </c>
       <c r="C28" s="19">
         <f>1.15*$C$17*C24/2</f>
-        <v/>
+        <v>9.640128</v>
       </c>
       <c r="D28" s="19">
         <f>1.15*$C$17*D24/2</f>
-        <v/>
+        <v>16.93536</v>
       </c>
       <c r="E28" s="19">
         <f>1.15*$C$17*E24/2</f>
-        <v/>
+        <v>23.188416</v>
       </c>
       <c r="F28" s="19">
         <f>1.15*$C$17*F24/2</f>
-        <v/>
+        <v>25.012224</v>
       </c>
     </row>
     <row r="29">
@@ -8048,19 +8048,19 @@
       </c>
       <c r="C30" s="16">
         <f>C27*1000000/(0.9*C25*$C$16^2)</f>
-        <v/>
+        <v>0.05772418781</v>
       </c>
       <c r="D30" s="16">
         <f>D27*1000000/(0.9*D25*$C$16^2)</f>
-        <v/>
+        <v>0.1029918469</v>
       </c>
       <c r="E30" s="16">
         <f>E27*1000000/(0.9*E25*$C$16^2)</f>
-        <v/>
+        <v>0.1930883833</v>
       </c>
       <c r="F30" s="16">
         <f>F27*1000000/(0.9*F25*$C$16^2)</f>
-        <v/>
+        <v>0.2246562985</v>
       </c>
     </row>
     <row r="31">
@@ -8071,19 +8071,19 @@
       </c>
       <c r="C31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0001376056186</v>
       </c>
       <c r="D31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0002457515699</v>
       </c>
       <c r="E31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0004616144332</v>
       </c>
       <c r="F31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0005374445961</v>
       </c>
     </row>
     <row r="32">
@@ -8094,19 +8094,19 @@
       </c>
       <c r="C32" s="16">
         <f>C31*C25*$C$16</f>
-        <v/>
+        <v>19.32507507</v>
       </c>
       <c r="D32" s="16">
         <f>D31*D25*$C$16</f>
-        <v/>
+        <v>59.69797136</v>
       </c>
       <c r="E32" s="16">
         <f>E31*E25*$C$16</f>
-        <v/>
+        <v>112.1353781</v>
       </c>
       <c r="F32" s="16">
         <f>F31*F25*$C$16</f>
-        <v/>
+        <v>130.5560413</v>
       </c>
     </row>
     <row r="33">
@@ -8117,19 +8117,19 @@
       </c>
       <c r="C33" s="16">
         <f>C32*$C$6/(0.85*$C$5*C25)</f>
-        <v/>
+        <v>0.7373637547</v>
       </c>
       <c r="D33" s="16">
         <f>D32*$C$6/(0.85*$C$5*D25)</f>
-        <v/>
+        <v>1.316867015</v>
       </c>
       <c r="E33" s="16">
         <f>E32*$C$6/(0.85*$C$5*E25)</f>
-        <v/>
+        <v>2.473574517</v>
       </c>
       <c r="F33" s="16">
         <f>F32*$C$6/(0.85*$C$5*F25)</f>
-        <v/>
+        <v>2.879912676</v>
       </c>
     </row>
     <row r="34">
@@ -8138,21 +8138,21 @@
           <t>a &lt;= hf ? (viga T)</t>
         </is>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="18" t="str">
         <f>IF(C33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="D34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="D34" s="18" t="str">
         <f>IF(D33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="E34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="E34" s="18" t="str">
         <f>IF(E33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="F34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="F34" s="18" t="str">
         <f>IF(F33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
+        <v>Si (T)</v>
       </c>
     </row>
     <row r="35">
@@ -8163,19 +8163,19 @@
       </c>
       <c r="C35" s="19">
         <f>MAX(C32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="D35" s="19">
         <f>MAX(D32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="E35" s="19">
         <f>MAX(E32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="F35" s="19">
         <f>MAX(F32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
     </row>
     <row r="36">
@@ -8186,19 +8186,19 @@
       </c>
       <c r="C36" s="19">
         <f>ROUNDUP(C35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D36" s="19">
         <f>ROUNDUP(D35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E36" s="19">
         <f>ROUNDUP(E35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F36" s="19">
         <f>ROUNDUP(F35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -8220,19 +8220,19 @@
       </c>
       <c r="C38" s="16">
         <f>C26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>0.2491760774</v>
       </c>
       <c r="D38" s="16">
         <f>D26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>0.7690057903</v>
       </c>
       <c r="E38" s="16">
         <f>E26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>1.441726595</v>
       </c>
       <c r="F38" s="16">
         <f>F26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>1.677433696</v>
       </c>
     </row>
     <row r="39">
@@ -8243,19 +8243,19 @@
       </c>
       <c r="C39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0005964149999</v>
       </c>
       <c r="D39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.001861542708</v>
       </c>
       <c r="E39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.003543472336</v>
       </c>
       <c r="F39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.00414552547</v>
       </c>
     </row>
     <row r="40">
@@ -8266,19 +8266,19 @@
       </c>
       <c r="C40" s="16">
         <f>C39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>27.16521221</v>
       </c>
       <c r="D40" s="16">
         <f>D39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>84.78861649</v>
       </c>
       <c r="E40" s="16">
         <f>E39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>161.3963062</v>
       </c>
       <c r="F40" s="16">
         <f>F39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>188.8183213</v>
       </c>
     </row>
     <row r="41">
@@ -8289,19 +8289,19 @@
       </c>
       <c r="C41" s="19">
         <f>MAX(C40,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="D41" s="19">
         <f>MAX(D40,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="E41" s="19">
         <f>MAX(E40,$C$18)</f>
-        <v/>
+        <v>161.3963062</v>
       </c>
       <c r="F41" s="19">
         <f>MAX(F40,$C$18)</f>
-        <v/>
+        <v>188.8183213</v>
       </c>
     </row>
     <row r="42">
@@ -8312,19 +8312,19 @@
       </c>
       <c r="C42" s="19">
         <f>ROUNDUP(C41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D42" s="19">
         <f>ROUNDUP(D41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E42" s="19">
         <f>ROUNDUP(E41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F42" s="19">
         <f>ROUNDUP(F41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -8344,21 +8344,21 @@
           <t>Vu &lt;= phi 1.1 Vc ?</t>
         </is>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="18" t="str">
         <f>IF(C28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="D44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="D44" s="18" t="str">
         <f>IF(D28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="E44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="E44" s="18" t="str">
         <f>IF(E28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="F44" s="18" t="str">
         <f>IF(F28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
+        <v>Si - sin estribos</v>
       </c>
     </row>
     <row r="45">
@@ -8367,21 +8367,21 @@
           <t>CHECK deflexion (h&gt;=Ln/18.5)</t>
         </is>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="18" t="str">
         <f>IF($C$8&gt;=C24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="D45" s="18" t="str">
         <f>IF($C$8&gt;=D24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="E45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="E45" s="18" t="str">
         <f>IF($C$8&gt;=E24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="F45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="F45" s="18" t="str">
         <f>IF($C$8&gt;=F24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
     </row>
   </sheetData>
@@ -8554,7 +8554,7 @@
       </c>
       <c r="C16" s="19">
         <f>C8*1000-C11*1000-C12/2</f>
-        <v/>
+        <v>303.65</v>
       </c>
     </row>
     <row r="17">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="C17" s="19">
         <f>(1.2*C14+1.6*C15)*C10</f>
-        <v/>
+        <v>10.60096</v>
       </c>
     </row>
     <row r="18">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="C18" s="21">
         <f>MAX(0.25*SQRT(C5)/C6,1.4/C6)*C7*1000*C16</f>
-        <v/>
+        <v>151.825</v>
       </c>
     </row>
     <row r="19">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="C19" s="21">
         <f>0.17*SQRT(C5)*C7*1000*C16/1000</f>
-        <v/>
+        <v>40.97250167</v>
       </c>
     </row>
     <row r="20">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="C20" s="21">
         <f>0.75*1.1*C19</f>
-        <v/>
+        <v>33.80231387</v>
       </c>
     </row>
     <row r="22">
@@ -8666,19 +8666,19 @@
       </c>
       <c r="C25" s="19">
         <f>MIN(C24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>462.5</v>
       </c>
       <c r="D25" s="19">
         <f>MIN(D24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="E25" s="19">
         <f>MIN(E24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="F25" s="19">
         <f>MIN(F24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
     </row>
     <row r="26">
@@ -8689,19 +8689,19 @@
       </c>
       <c r="C26" s="19">
         <f>$C$17*C24^2/10</f>
-        <v/>
+        <v>3.62817856</v>
       </c>
       <c r="D26" s="19">
         <f>$C$17*D24^2/10</f>
-        <v/>
+        <v>11.197264</v>
       </c>
       <c r="E26" s="19">
         <f>$C$17*E24^2/10</f>
-        <v/>
+        <v>20.99255104</v>
       </c>
       <c r="F26" s="19">
         <f>$C$17*F24^2/10</f>
-        <v/>
+        <v>24.42461184</v>
       </c>
     </row>
     <row r="27">
@@ -8712,19 +8712,19 @@
       </c>
       <c r="C27" s="19">
         <f>$C$17*C24^2/14</f>
-        <v/>
+        <v>2.591556114</v>
       </c>
       <c r="D27" s="19">
         <f>$C$17*D24^2/14</f>
-        <v/>
+        <v>7.998045714</v>
       </c>
       <c r="E27" s="19">
         <f>$C$17*E24^2/14</f>
-        <v/>
+        <v>14.99467931</v>
       </c>
       <c r="F27" s="19">
         <f>$C$17*F24^2/14</f>
-        <v/>
+        <v>17.44615131</v>
       </c>
     </row>
     <row r="28">
@@ -8735,19 +8735,19 @@
       </c>
       <c r="C28" s="19">
         <f>1.15*$C$17*C24/2</f>
-        <v/>
+        <v>11.2767712</v>
       </c>
       <c r="D28" s="19">
         <f>1.15*$C$17*D24/2</f>
-        <v/>
+        <v>19.810544</v>
       </c>
       <c r="E28" s="19">
         <f>1.15*$C$17*E24/2</f>
-        <v/>
+        <v>27.1252064</v>
       </c>
       <c r="F28" s="19">
         <f>1.15*$C$17*F24/2</f>
-        <v/>
+        <v>29.2586496</v>
       </c>
     </row>
     <row r="29">
@@ -8769,19 +8769,19 @@
       </c>
       <c r="C30" s="16">
         <f>C27*1000000/(0.9*C25*$C$16^2)</f>
-        <v/>
+        <v>0.06752425472</v>
       </c>
       <c r="D30" s="16">
         <f>D27*1000000/(0.9*D25*$C$16^2)</f>
-        <v/>
+        <v>0.1204771859</v>
       </c>
       <c r="E30" s="16">
         <f>E27*1000000/(0.9*E25*$C$16^2)</f>
-        <v/>
+        <v>0.2258697727</v>
       </c>
       <c r="F30" s="16">
         <f>F27*1000000/(0.9*F25*$C$16^2)</f>
-        <v/>
+        <v>0.2627970995</v>
       </c>
     </row>
     <row r="31">
@@ -8792,19 +8792,19 @@
       </c>
       <c r="C31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0001610007519</v>
       </c>
       <c r="D31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0002875801693</v>
       </c>
       <c r="E31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0005403615608</v>
       </c>
       <c r="F31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0006292005562</v>
       </c>
     </row>
     <row r="32">
@@ -8815,19 +8815,19 @@
       </c>
       <c r="C32" s="16">
         <f>C31*C25*$C$16</f>
-        <v/>
+        <v>22.61064372</v>
       </c>
       <c r="D32" s="16">
         <f>D31*D25*$C$16</f>
-        <v/>
+        <v>69.85897472</v>
       </c>
       <c r="E32" s="16">
         <f>E31*E25*$C$16</f>
-        <v/>
+        <v>131.2646304</v>
       </c>
       <c r="F32" s="16">
         <f>F31*F25*$C$16</f>
-        <v/>
+        <v>152.8453991</v>
       </c>
     </row>
     <row r="33">
@@ -8838,19 +8838,19 @@
       </c>
       <c r="C33" s="16">
         <f>C32*$C$6/(0.85*$C$5*C25)</f>
-        <v/>
+        <v>0.8627272644</v>
       </c>
       <c r="D33" s="16">
         <f>D32*$C$6/(0.85*$C$5*D25)</f>
-        <v/>
+        <v>1.541006795</v>
       </c>
       <c r="E33" s="16">
         <f>E32*$C$6/(0.85*$C$5*E25)</f>
-        <v/>
+        <v>2.895543317</v>
       </c>
       <c r="F33" s="16">
         <f>F32*$C$6/(0.85*$C$5*F25)</f>
-        <v/>
+        <v>3.371589686</v>
       </c>
     </row>
     <row r="34">
@@ -8859,21 +8859,21 @@
           <t>a &lt;= hf ? (viga T)</t>
         </is>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="18" t="str">
         <f>IF(C33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="D34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="D34" s="18" t="str">
         <f>IF(D33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="E34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="E34" s="18" t="str">
         <f>IF(E33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="F34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="F34" s="18" t="str">
         <f>IF(F33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
+        <v>Si (T)</v>
       </c>
     </row>
     <row r="35">
@@ -8884,19 +8884,19 @@
       </c>
       <c r="C35" s="19">
         <f>MAX(C32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="D35" s="19">
         <f>MAX(D32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="E35" s="19">
         <f>MAX(E32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="F35" s="19">
         <f>MAX(F32,$C$18)</f>
-        <v/>
+        <v>152.8453991</v>
       </c>
     </row>
     <row r="36">
@@ -8907,19 +8907,19 @@
       </c>
       <c r="C36" s="19">
         <f>ROUNDUP(C35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D36" s="19">
         <f>ROUNDUP(D35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E36" s="19">
         <f>ROUNDUP(E35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F36" s="19">
         <f>ROUNDUP(F35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -8941,19 +8941,19 @@
       </c>
       <c r="C38" s="16">
         <f>C26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>0.2914796996</v>
       </c>
       <c r="D38" s="16">
         <f>D26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>0.8995629881</v>
       </c>
       <c r="E38" s="16">
         <f>E26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>1.686494303</v>
       </c>
       <c r="F38" s="16">
         <f>F26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>1.962218343</v>
       </c>
     </row>
     <row r="39">
@@ -8964,19 +8964,19 @@
       </c>
       <c r="C39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0006983018625</v>
       </c>
       <c r="D39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.002183899739</v>
       </c>
       <c r="E39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.004168806263</v>
       </c>
       <c r="F39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.004882271123</v>
       </c>
     </row>
     <row r="40">
@@ -8987,19 +8987,19 @@
       </c>
       <c r="C40" s="16">
         <f>C39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>31.80590408</v>
       </c>
       <c r="D40" s="16">
         <f>D39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>99.47117335</v>
       </c>
       <c r="E40" s="16">
         <f>E39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>189.8787033</v>
       </c>
       <c r="F40" s="16">
         <f>F39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>222.375244</v>
       </c>
     </row>
     <row r="41">
@@ -9010,19 +9010,19 @@
       </c>
       <c r="C41" s="19">
         <f>MAX(C40,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="D41" s="19">
         <f>MAX(D40,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="E41" s="19">
         <f>MAX(E40,$C$18)</f>
-        <v/>
+        <v>189.8787033</v>
       </c>
       <c r="F41" s="19">
         <f>MAX(F40,$C$18)</f>
-        <v/>
+        <v>222.375244</v>
       </c>
     </row>
     <row r="42">
@@ -9033,19 +9033,19 @@
       </c>
       <c r="C42" s="19">
         <f>ROUNDUP(C41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D42" s="19">
         <f>ROUNDUP(D41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E42" s="19">
         <f>ROUNDUP(E41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F42" s="19">
         <f>ROUNDUP(F41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -9065,21 +9065,21 @@
           <t>Vu &lt;= phi 1.1 Vc ?</t>
         </is>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="18" t="str">
         <f>IF(C28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="D44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="D44" s="18" t="str">
         <f>IF(D28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="E44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="E44" s="18" t="str">
         <f>IF(E28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="F44" s="18" t="str">
         <f>IF(F28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
+        <v>Si - sin estribos</v>
       </c>
     </row>
     <row r="45">
@@ -9088,21 +9088,21 @@
           <t>CHECK deflexion (h&gt;=Ln/18.5)</t>
         </is>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="18" t="str">
         <f>IF($C$8&gt;=C24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="D45" s="18" t="str">
         <f>IF($C$8&gt;=D24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="E45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="E45" s="18" t="str">
         <f>IF($C$8&gt;=E24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="F45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="F45" s="18" t="str">
         <f>IF($C$8&gt;=F24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
     </row>
   </sheetData>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="B13" s="86">
         <f>0.25*$B$10*$B$11</f>
-        <v/>
+        <v>97.1625</v>
       </c>
     </row>
     <row r="15">
@@ -9362,51 +9362,51 @@
       </c>
       <c r="D16" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="E16" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="F16" s="79">
         <f>E16*1000-$B$7-9.5-$B$8/2</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="G16" s="82">
         <f>$B$13*1000/(0.9*$B$6)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="H16" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*D16*1000*F16</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="I16" s="82">
         <f>MAX(G16,H16)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="J16" s="83">
         <f>MAX(4,ROUNDUP(I16/$B$9,0))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K16" s="82">
         <f>J16*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="L16" s="79">
         <f>0.9*K16*$B$6/1000</f>
-        <v/>
-      </c>
-      <c r="M16" s="84">
+        <v>300.888</v>
+      </c>
+      <c r="M16" s="84" t="str">
         <f>IF(L16&gt;=$B$13,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="N16" s="80">
         <f>B16/20</f>
-        <v/>
-      </c>
-      <c r="O16" s="84">
+        <v>0.125</v>
+      </c>
+      <c r="O16" s="84" t="str">
         <f>IF($B$12&gt;=N16,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="P16" s="85" t="inlineStr">
         <is>
@@ -9428,51 +9428,51 @@
       </c>
       <c r="D17" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="E17" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="F17" s="79">
         <f>E17*1000-$B$7-9.5-$B$8/2</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="G17" s="82">
         <f>$B$13*1000/(0.9*$B$6)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="H17" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*D17*1000*F17</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="I17" s="82">
         <f>MAX(G17,H17)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="J17" s="83">
         <f>MAX(4,ROUNDUP(I17/$B$9,0))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K17" s="82">
         <f>J17*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="L17" s="79">
         <f>0.9*K17*$B$6/1000</f>
-        <v/>
-      </c>
-      <c r="M17" s="84">
+        <v>300.888</v>
+      </c>
+      <c r="M17" s="84" t="str">
         <f>IF(L17&gt;=$B$13,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="N17" s="80">
         <f>B17/20</f>
-        <v/>
-      </c>
-      <c r="O17" s="84">
+        <v>0.13</v>
+      </c>
+      <c r="O17" s="84" t="str">
         <f>IF($B$12&gt;=N17,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="P17" s="85" t="inlineStr">
         <is>
@@ -9494,51 +9494,51 @@
       </c>
       <c r="D18" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="E18" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="F18" s="79">
         <f>E18*1000-$B$7-9.5-$B$8/2</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="G18" s="82">
         <f>$B$13*1000/(0.9*$B$6)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="H18" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*D18*1000*F18</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="I18" s="82">
         <f>MAX(G18,H18)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="J18" s="83">
         <f>MAX(4,ROUNDUP(I18/$B$9,0))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K18" s="82">
         <f>J18*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="L18" s="79">
         <f>0.9*K18*$B$6/1000</f>
-        <v/>
-      </c>
-      <c r="M18" s="84">
+        <v>300.888</v>
+      </c>
+      <c r="M18" s="84" t="str">
         <f>IF(L18&gt;=$B$13,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="N18" s="80">
         <f>B18/20</f>
-        <v/>
-      </c>
-      <c r="O18" s="84">
+        <v>0.135</v>
+      </c>
+      <c r="O18" s="84" t="str">
         <f>IF($B$12&gt;=N18,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="P18" s="85" t="inlineStr">
         <is>
@@ -9560,51 +9560,51 @@
       </c>
       <c r="D19" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="E19" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="F19" s="79">
         <f>E19*1000-$B$7-9.5-$B$8/2</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="G19" s="82">
         <f>$B$13*1000/(0.9*$B$6)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="H19" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*D19*1000*F19</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="I19" s="82">
         <f>MAX(G19,H19)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="J19" s="83">
         <f>MAX(4,ROUNDUP(I19/$B$9,0))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K19" s="82">
         <f>J19*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="L19" s="79">
         <f>0.9*K19*$B$6/1000</f>
-        <v/>
-      </c>
-      <c r="M19" s="84">
+        <v>300.888</v>
+      </c>
+      <c r="M19" s="84" t="str">
         <f>IF(L19&gt;=$B$13,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="N19" s="80">
         <f>B19/20</f>
-        <v/>
-      </c>
-      <c r="O19" s="84">
+        <v>0.14</v>
+      </c>
+      <c r="O19" s="84" t="str">
         <f>IF($B$12&gt;=N19,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="P19" s="85" t="inlineStr">
         <is>
@@ -9626,51 +9626,51 @@
       </c>
       <c r="D20" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="E20" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="F20" s="79">
         <f>E20*1000-$B$7-9.5-$B$8/2</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="G20" s="82">
         <f>$B$13*1000/(0.9*$B$6)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="H20" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*D20*1000*F20</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="I20" s="82">
         <f>MAX(G20,H20)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="J20" s="83">
         <f>MAX(4,ROUNDUP(I20/$B$9,0))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K20" s="82">
         <f>J20*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="L20" s="79">
         <f>0.9*K20*$B$6/1000</f>
-        <v/>
-      </c>
-      <c r="M20" s="84">
+        <v>300.888</v>
+      </c>
+      <c r="M20" s="84" t="str">
         <f>IF(L20&gt;=$B$13,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="N20" s="80">
         <f>B20/20</f>
-        <v/>
-      </c>
-      <c r="O20" s="84">
+        <v>0.1825</v>
+      </c>
+      <c r="O20" s="84" t="str">
         <f>IF($B$12&gt;=N20,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="P20" s="85" t="inlineStr">
         <is>
@@ -9692,51 +9692,51 @@
       </c>
       <c r="D21" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="E21" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="F21" s="79">
         <f>E21*1000-$B$7-9.5-$B$8/2</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="G21" s="82">
         <f>$B$13*1000/(0.9*$B$6)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="H21" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*D21*1000*F21</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="I21" s="82">
         <f>MAX(G21,H21)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="J21" s="83">
         <f>MAX(4,ROUNDUP(I21/$B$9,0))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K21" s="82">
         <f>J21*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="L21" s="79">
         <f>0.9*K21*$B$6/1000</f>
-        <v/>
-      </c>
-      <c r="M21" s="84">
+        <v>300.888</v>
+      </c>
+      <c r="M21" s="84" t="str">
         <f>IF(L21&gt;=$B$13,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="N21" s="80">
         <f>B21/20</f>
-        <v/>
-      </c>
-      <c r="O21" s="84">
+        <v>0.1925</v>
+      </c>
+      <c r="O21" s="84" t="str">
         <f>IF($B$12&gt;=N21,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="P21" s="85" t="inlineStr">
         <is>
@@ -9758,51 +9758,51 @@
       </c>
       <c r="D22" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="E22" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="F22" s="79">
         <f>E22*1000-$B$7-9.5-$B$8/2</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="G22" s="82">
         <f>$B$13*1000/(0.9*$B$6)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="H22" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*D22*1000*F22</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="I22" s="82">
         <f>MAX(G22,H22)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="J22" s="83">
         <f>MAX(4,ROUNDUP(I22/$B$9,0))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K22" s="82">
         <f>J22*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="L22" s="79">
         <f>0.9*K22*$B$6/1000</f>
-        <v/>
-      </c>
-      <c r="M22" s="84">
+        <v>300.888</v>
+      </c>
+      <c r="M22" s="84" t="str">
         <f>IF(L22&gt;=$B$13,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="N22" s="80">
         <f>B22/20</f>
-        <v/>
-      </c>
-      <c r="O22" s="84">
+        <v>0.195</v>
+      </c>
+      <c r="O22" s="84" t="str">
         <f>IF($B$12&gt;=N22,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="P22" s="85" t="inlineStr">
         <is>
@@ -9824,51 +9824,51 @@
       </c>
       <c r="D23" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="E23" s="87">
         <f>$B$12</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="F23" s="79">
         <f>E23*1000-$B$7-9.5-$B$8/2</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="G23" s="82">
         <f>$B$13*1000/(0.9*$B$6)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="H23" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*D23*1000*F23</f>
-        <v/>
+        <v>242.55</v>
       </c>
       <c r="I23" s="82">
         <f>MAX(G23,H23)</f>
-        <v/>
+        <v>257.0436508</v>
       </c>
       <c r="J23" s="83">
         <f>MAX(4,ROUNDUP(I23/$B$9,0))</f>
-        <v/>
+        <v>4</v>
       </c>
       <c r="K23" s="82">
         <f>J23*$B$9</f>
-        <v/>
+        <v>796</v>
       </c>
       <c r="L23" s="79">
         <f>0.9*K23*$B$6/1000</f>
-        <v/>
-      </c>
-      <c r="M23" s="84">
+        <v>300.888</v>
+      </c>
+      <c r="M23" s="84" t="str">
         <f>IF(L23&gt;=$B$13,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="N23" s="80">
         <f>B23/20</f>
-        <v/>
-      </c>
-      <c r="O23" s="84">
+        <v>0.2</v>
+      </c>
+      <c r="O23" s="84" t="str">
         <f>IF($B$12&gt;=N23,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
       <c r="P23" s="85" t="inlineStr">
         <is>
@@ -10015,27 +10015,27 @@
       </c>
       <c r="D10" s="16">
         <f>($E$5*1*0.8)/(1.1*SQRT($C$5)*2.5)*C10</f>
-        <v/>
+        <v>219.356836</v>
       </c>
       <c r="E10" s="16">
         <f>($E$5*1.3*0.8)/(1.1*SQRT($C$5)*2.5)*C10</f>
-        <v/>
+        <v>285.1638868</v>
       </c>
       <c r="F10" s="19">
         <f>MAX(0.24*$E$5/SQRT($C$5)*C10,8*C10,150)</f>
-        <v/>
+        <v>180.9693897</v>
       </c>
       <c r="G10" s="16">
         <f>12*C10</f>
-        <v/>
+        <v>114</v>
       </c>
       <c r="H10" s="16">
         <f>MAX(6*C10,75)</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="I10" s="16">
         <f>6*C10</f>
-        <v/>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -10049,27 +10049,27 @@
       </c>
       <c r="D11" s="16">
         <f>($E$5*1*0.8)/(1.1*SQRT($C$5)*2.5)*C11</f>
-        <v/>
+        <v>293.2454544</v>
       </c>
       <c r="E11" s="16">
         <f>($E$5*1.3*0.8)/(1.1*SQRT($C$5)*2.5)*C11</f>
-        <v/>
+        <v>381.2190907</v>
       </c>
       <c r="F11" s="19">
         <f>MAX(0.24*$E$5/SQRT($C$5)*C11,8*C11,150)</f>
-        <v/>
+        <v>241.9274999</v>
       </c>
       <c r="G11" s="16">
         <f>12*C11</f>
-        <v/>
+        <v>152.4</v>
       </c>
       <c r="H11" s="16">
         <f>MAX(6*C11,75)</f>
-        <v/>
+        <v>76.2</v>
       </c>
       <c r="I11" s="16">
         <f>6*C11</f>
-        <v/>
+        <v>76.2</v>
       </c>
     </row>
     <row r="12">
@@ -10083,27 +10083,27 @@
       </c>
       <c r="D12" s="16">
         <f>($E$5*1*0.8)/(1.1*SQRT($C$5)*2.5)*C12</f>
-        <v/>
+        <v>367.1340728</v>
       </c>
       <c r="E12" s="16">
         <f>($E$5*1.3*0.8)/(1.1*SQRT($C$5)*2.5)*C12</f>
-        <v/>
+        <v>477.2742947</v>
       </c>
       <c r="F12" s="19">
         <f>MAX(0.24*$E$5/SQRT($C$5)*C12,8*C12,150)</f>
-        <v/>
+        <v>302.8856101</v>
       </c>
       <c r="G12" s="16">
         <f>12*C12</f>
-        <v/>
+        <v>190.8</v>
       </c>
       <c r="H12" s="16">
         <f>MAX(6*C12,75)</f>
-        <v/>
+        <v>95.4</v>
       </c>
       <c r="I12" s="16">
         <f>6*C12</f>
-        <v/>
+        <v>95.4</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="33">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="E17" s="16">
         <f>F11</f>
-        <v/>
+        <v>241.9274999</v>
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="G17" s="19">
         <f>(D17/4*1000+E17)/1000</f>
-        <v/>
+        <v>1.5169275</v>
       </c>
     </row>
     <row r="18">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="E18" s="16">
         <f>F12</f>
-        <v/>
+        <v>302.8856101</v>
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="G18" s="19">
         <f>(D18*1000+2*E18)/1000</f>
-        <v/>
+        <v>5.70577122</v>
       </c>
     </row>
     <row r="19">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="E19" s="16">
         <f>F10</f>
-        <v/>
+        <v>180.9693897</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="G19" s="19">
         <f>(D19/4*1000+E19)/1000</f>
-        <v/>
+        <v>1.45596939</v>
       </c>
     </row>
     <row r="20" ht="27.95" customHeight="1" s="33">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="E20" s="16">
         <f>F10</f>
-        <v/>
+        <v>180.9693897</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="G20" s="19">
         <f>(D20*1000+2*E20)/1000</f>
-        <v/>
+        <v>5.461938779</v>
       </c>
     </row>
     <row r="22" ht="60" customHeight="1" s="33">
@@ -10337,19 +10337,19 @@
       </c>
       <c r="F24" s="16">
         <f>2*D24</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="G24" s="19">
         <f>MIN(E24/4,6*15.9,150)</f>
-        <v/>
+        <v>85.65</v>
       </c>
       <c r="H24" s="19">
         <f>E24/2</f>
-        <v/>
+        <v>171.3</v>
       </c>
       <c r="I24" s="16">
         <f>2*((C24-2*$G$5)+(D24-2*$G$5))+2*MAX(10*9.5,75)</f>
-        <v/>
+        <v>1270</v>
       </c>
     </row>
     <row r="25">
@@ -10369,19 +10369,19 @@
       </c>
       <c r="F25" s="16">
         <f>2*D25</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="G25" s="19">
         <f>MIN(E25/4,6*15.9,150)</f>
-        <v/>
+        <v>85.65</v>
       </c>
       <c r="H25" s="19">
         <f>E25/2</f>
-        <v/>
+        <v>171.3</v>
       </c>
       <c r="I25" s="16">
         <f>2*((C25-2*$G$5)+(D25-2*$G$5))+2*MAX(10*9.5,75)</f>
-        <v/>
+        <v>1370</v>
       </c>
     </row>
     <row r="26">
@@ -10401,19 +10401,19 @@
       </c>
       <c r="F26" s="16">
         <f>2*D26</f>
-        <v/>
+        <v>680</v>
       </c>
       <c r="G26" s="19">
         <f>MIN(E26/4,6*15.9,150)</f>
-        <v/>
+        <v>76</v>
       </c>
       <c r="H26" s="19">
         <f>E26/2</f>
-        <v/>
+        <v>152</v>
       </c>
       <c r="I26" s="16">
         <f>2*((C26-2*$G$5)+(D26-2*$G$5))+2*MAX(10*9.5,75)</f>
-        <v/>
+        <v>850</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" s="33">

--- a/Proyectos/Diseno-Estructural/DISENO-VIGAS-VIGUETAS-FINAL-v2.xlsx
+++ b/Proyectos/Diseno-Estructural/DISENO-VIGAS-VIGUETAS-FINAL-v2.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Irregularidades" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Vigas de Carga VC" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Vigas de Rigidez VR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Diseno Viguetas Entrepiso" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Diseno Viguetas Cubierta" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Riostras Cimentacion" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Despiece y Longitudes" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Irregularidades" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vigas de Carga VC" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vigas de Rigidez VR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diseno Viguetas Entrepiso" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Diseno Viguetas Cubierta" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Riostras Cimentacion" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Despiece y Longitudes" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B7" s="66" t="inlineStr">
         <is>
-          <t>12 grupos por LONGITUD + CONDICION DE APOYO (0.30x0.40). Flexion +/-, cortante, cortante por capacidad y torsion.</t>
+          <t>9 grupos por LONGITUD (0.30x0.40), diseno con la mayor solicitacion. Flexion +/-, cortante, cortante por capacidad y torsion.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B8" s="66" t="inlineStr">
         <is>
-          <t>16 grupos por LONGITUD + CONDICION DE APOYO (0.35x0.40). Mismo calculo completo.</t>
+          <t>8 grupos por LONGITUD (0.35x0.40). Mismo calculo completo.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
     <row r="19">
       <c r="B19" s="68" t="inlineStr">
         <is>
-          <t>5. AGRUPACION (criterio del profesor): vigas/viguetas con la MISMA longitud Y la MISMA condicion de apoyo forman un grupo; el grupo se disena con su MAYOR solicitacion.</t>
+          <t>5. AGRUPACION: las vigas con la MISMA longitud total forman un grupo (VC 9 grupos, VR 8 grupos); el grupo se disena con su MAYOR solicitacion de la envolvente.</t>
         </is>
       </c>
     </row>
@@ -1397,20 +1397,20 @@
       </c>
       <c r="D18" s="7">
         <f>MAX(E68:E72,H68:H72)</f>
-        <v>1.023571884</v>
+        <v/>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>1.20 / 1.40</t>
         </is>
       </c>
-      <c r="F18" s="7" t="str">
+      <c r="F18" s="7">
         <f>IF(D18&gt;1.4,"Extrema",IF(D18&gt;1.2,"Si","No"))</f>
-        <v>No</v>
+        <v/>
       </c>
       <c r="G18" s="8">
         <f>IF(D18&gt;1.4,0.8,IF(D18&gt;1.2,0.9,1))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J18" s="32" t="inlineStr">
         <is>
@@ -1431,20 +1431,20 @@
       </c>
       <c r="D19" s="7">
         <f>MAX(C42/C40,C43/C41)</f>
-        <v>0.1657285804</v>
+        <v/>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="F19" s="7" t="str">
+      <c r="F19" s="7">
         <f>IF(AND(C42/C40&gt;0.15,C43/C41&gt;0.15),"Si","No")</f>
-        <v>No</v>
+        <v/>
       </c>
       <c r="G19" s="8">
         <f>IF(AND(C42/C40&gt;0.15,C43/C41&gt;0.15),0.9,1)</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -1460,19 +1460,19 @@
       </c>
       <c r="D20" s="7">
         <f>C45</f>
-        <v>27.03</v>
+        <v/>
       </c>
       <c r="E20" s="7">
         <f>0.5*C40*C41</f>
-        <v>292.617</v>
-      </c>
-      <c r="F20" s="7" t="str">
+        <v/>
+      </c>
+      <c r="F20" s="7">
         <f>IF(C45&gt;0.5*C40*C41,"Si","No")</f>
-        <v>No</v>
+        <v/>
       </c>
       <c r="G20" s="8">
         <f>IF(C45&gt;0.5*C40*C41,0.9,1)</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="G23" s="9">
         <f>MIN(G18:G22)</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="33">
@@ -1603,20 +1603,20 @@
       </c>
       <c r="D27" s="7">
         <f>MIN(G52:G55)</f>
-        <v>1.064936106</v>
+        <v/>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>0.70 / 0.60</t>
         </is>
       </c>
-      <c r="F27" s="7" t="str">
+      <c r="F27" s="7">
         <f>IF(D27&lt;0.6,"Extrema",IF(D27&lt;0.7,"Si","No"))</f>
-        <v>No</v>
+        <v/>
       </c>
       <c r="G27" s="8">
         <f>IF(D27&lt;0.6,0.8,IF(D27&lt;0.7,0.9,1))</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="33">
@@ -1632,20 +1632,20 @@
       </c>
       <c r="D28" s="7">
         <f>MAX(H60:H63)</f>
-        <v>1.323326017</v>
+        <v/>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="F28" s="7" t="str">
+      <c r="F28" s="7">
         <f>IF(D28&gt;1.5,"Si","No")</f>
-        <v>No</v>
+        <v/>
       </c>
       <c r="G28" s="8">
         <f>IF(D28&gt;1.5,0.9,1)</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G32" s="9">
         <f>MIN(G27:G31)</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="34" ht="31.5" customHeight="1" s="33">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C36" s="9">
         <f>IF(E35="Si",1,0.75)</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="38" ht="31.5" customHeight="1" s="33">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C44" s="7">
         <f>C40*C41</f>
-        <v>585.234</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C46" s="10">
         <f>C13*G32*G23*C36</f>
-        <v>5</v>
+        <v/>
       </c>
     </row>
     <row r="47" ht="57.95" customHeight="1" s="33">
@@ -1938,18 +1938,18 @@
       </c>
       <c r="D52" s="7">
         <f>SUM(C52:C56)</f>
-        <v>15128.72</v>
+        <v/>
       </c>
       <c r="E52" s="7" t="n">
         <v>0.022</v>
       </c>
       <c r="F52" s="7">
         <f>D52/E52</f>
-        <v>687669.0909</v>
+        <v/>
       </c>
       <c r="G52" s="7">
         <f>F52/F53</f>
-        <v>1.410636191</v>
+        <v/>
       </c>
     </row>
     <row r="53">
@@ -1961,18 +1961,18 @@
       </c>
       <c r="D53" s="7">
         <f>SUM(C53:C56)</f>
-        <v>14137.17</v>
+        <v/>
       </c>
       <c r="E53" s="7" t="n">
         <v>0.029</v>
       </c>
       <c r="F53" s="7">
         <f>D53/E53</f>
-        <v>487488.6207</v>
+        <v/>
       </c>
       <c r="G53" s="7">
         <f>F53/F54</f>
-        <v>1.087083105</v>
+        <v/>
       </c>
     </row>
     <row r="54">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="D54" s="7">
         <f>SUM(C54:C56)</f>
-        <v>11659.37</v>
+        <v/>
       </c>
       <c r="E54" s="7" t="n">
         <v>0.026</v>
       </c>
       <c r="F54" s="7">
         <f>D54/E54</f>
-        <v>448437.3077</v>
+        <v/>
       </c>
       <c r="G54" s="7">
         <f>F54/F55</f>
-        <v>1.064936106</v>
+        <v/>
       </c>
     </row>
     <row r="55">
@@ -2007,18 +2007,18 @@
       </c>
       <c r="D55" s="7">
         <f>SUM(C55:C56)</f>
-        <v>8000.77</v>
+        <v/>
       </c>
       <c r="E55" s="7" t="n">
         <v>0.019</v>
       </c>
       <c r="F55" s="7">
         <f>D55/E55</f>
-        <v>421093.1579</v>
+        <v/>
       </c>
       <c r="G55" s="7">
         <f>F55/F56</f>
-        <v>1.870865889</v>
+        <v/>
       </c>
     </row>
     <row r="56">
@@ -2030,14 +2030,14 @@
       </c>
       <c r="D56" s="7">
         <f>SUM(C56:C56)</f>
-        <v>3151.11</v>
+        <v/>
       </c>
       <c r="E56" s="7" t="n">
         <v>0.014</v>
       </c>
       <c r="F56" s="7">
         <f>D56/E56</f>
-        <v>225079.2857</v>
+        <v/>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2093,11 +2093,11 @@
       </c>
       <c r="E60" s="7">
         <f>C60/C61</f>
-        <v>0.7556716842</v>
+        <v/>
       </c>
       <c r="H60" s="7">
         <f>E60</f>
-        <v>0.7556716842</v>
+        <v/>
       </c>
     </row>
     <row r="61">
@@ -2109,15 +2109,15 @@
       </c>
       <c r="D61" s="7">
         <f>C61/C60</f>
-        <v>1.323326017</v>
+        <v/>
       </c>
       <c r="E61" s="7">
         <f>C61/C62</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="H61" s="7">
         <f>MAX(D61,E61)</f>
-        <v>1.323326017</v>
+        <v/>
       </c>
     </row>
     <row r="62">
@@ -2129,15 +2129,15 @@
       </c>
       <c r="D62" s="7">
         <f>C62/C61</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="E62" s="7">
         <f>C62/C63</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="H62" s="7">
         <f>MAX(D62,E62)</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D63" s="7">
         <f>C63/C62</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="H63" s="7">
         <f>D63</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="64">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E68" s="7">
         <f>C68/((C68+D68)/2)</f>
-        <v>1.023571884</v>
+        <v/>
       </c>
       <c r="F68" s="7" t="n">
         <v>0.02097</v>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="H68" s="7">
         <f>F68/((F68+G68)/2)</f>
-        <v>1.013288234</v>
+        <v/>
       </c>
     </row>
     <row r="69">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E69" s="7">
         <f>C69/((C69+D69)/2)</f>
-        <v>1.022820801</v>
+        <v/>
       </c>
       <c r="F69" s="7" t="n">
         <v>0.04338</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="H69" s="7">
         <f>F69/((F69+G69)/2)</f>
-        <v>1.014143776</v>
+        <v/>
       </c>
     </row>
     <row r="70">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="E70" s="7">
         <f>C70/((C70+D70)/2)</f>
-        <v>1.022321985</v>
+        <v/>
       </c>
       <c r="F70" s="7" t="n">
         <v>0.0625</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="H70" s="7">
         <f>F70/((F70+G70)/2)</f>
-        <v>1.014363386</v>
+        <v/>
       </c>
     </row>
     <row r="71">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E71" s="7">
         <f>C71/((C71+D71)/2)</f>
-        <v>1.022007838</v>
+        <v/>
       </c>
       <c r="F71" s="7" t="n">
         <v>0.07592</v>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="H71" s="7">
         <f>F71/((F71+G71)/2)</f>
-        <v>1.014498564</v>
+        <v/>
       </c>
     </row>
     <row r="72">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E72" s="7">
         <f>C72/((C72+D72)/2)</f>
-        <v>1.021769631</v>
+        <v/>
       </c>
       <c r="F72" s="7" t="n">
         <v>0.08278000000000001</v>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H72" s="7">
         <f>F72/((F72+G72)/2)</f>
-        <v>1.014522949</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2366,7 +2366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO27"/>
+  <dimension ref="A1:AO24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="33" min="1" max="1"/>
@@ -2422,14 +2422,14 @@
     <row r="2">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>Agrupadas por longitud + condicion de apoyo. d, As, estribos, capacidad y torsion calculados con formulas.</t>
+          <t>Agrupadas por longitud (9 grupos), diseno con la mayor solicitacion de la envolvente. d, As, estribos, capacidad y torsion con formulas.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="71" t="inlineStr">
         <is>
-          <t>Criterio del profesor: se agrupan las vigas con la MISMA longitud Y la MISMA condicion de apoyo; cada grupo se disena con su mayor solicitacion. Celdas azules = ENTRADA (envolvente del modelo SAP). El resto se calcula solo.</t>
+          <t>Criterio de agrupacion: se agrupan las vigas con la MISMA longitud total; cada grupo se disena con su MAYOR solicitacion (envolvente de todas las condiciones de apoyo). Celdas azules = ENTRADA (envolvente del modelo SAP). El resto se calcula solo.</t>
         </is>
       </c>
     </row>
@@ -2770,11 +2770,11 @@
       </c>
       <c r="C14" s="76" t="inlineStr">
         <is>
-          <t>Extremo</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D14" s="77" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="E14" s="75" t="n">
         <v>0.3</v>
@@ -2783,16 +2783,16 @@
         <v>0.4</v>
       </c>
       <c r="G14" s="78" t="n">
-        <v>10.4</v>
+        <v>117.9</v>
       </c>
       <c r="H14" s="78" t="n">
-        <v>4</v>
+        <v>106.4</v>
       </c>
       <c r="I14" s="78" t="n">
-        <v>14.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="J14" s="78" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K14" s="79">
         <f>F14*1000-$B$7-$B$10-$B$8/2</f>
@@ -2800,15 +2800,15 @@
       </c>
       <c r="L14" s="80">
         <f>G14*1000000/(0.9*(E14*1000)*K14^2)</f>
-        <v>0.3282627711</v>
+        <v>3.721363531</v>
       </c>
       <c r="M14" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L14/(0.85*$B$5)))</f>
-        <v>0.0007870436534</v>
+        <v>0.009688654252</v>
       </c>
       <c r="N14" s="82">
         <f>M14*(E14*1000)*K14</f>
-        <v>80.88054104</v>
+        <v>995.6545542</v>
       </c>
       <c r="O14" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E14*1000)*K14</f>
@@ -2816,23 +2816,23 @@
       </c>
       <c r="P14" s="82">
         <f>MAX(N14,O14)</f>
-        <v>342.55</v>
+        <v>995.6545542</v>
       </c>
       <c r="Q14" s="83">
         <f>ROUNDUP(P14/$B$9,0)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R14" s="82">
         <f>Q14*$B$9</f>
-        <v>398</v>
+        <v>1194</v>
       </c>
       <c r="S14" s="79">
         <f>R14*$B$6/(0.85*$B$5*(E14*1000))</f>
-        <v>23.41176471</v>
+        <v>70.23529412</v>
       </c>
       <c r="T14" s="79">
         <f>0.9*R14*$B$6*(K14-S14/2)/1000000</f>
-        <v>49.77351244</v>
+        <v>138.7540587</v>
       </c>
       <c r="U14" s="84" t="str">
         <f>IF(AND(T14&gt;=G14,P14&lt;=0.025*(E14*1000)*K14,P14&gt;=O14),"CUMPLE","REVISAR")</f>
@@ -2840,31 +2840,31 @@
       </c>
       <c r="V14" s="80">
         <f>H14*1000000/(0.9*(E14*1000)*K14^2)</f>
-        <v>0.126254912</v>
+        <v>3.358380659</v>
       </c>
       <c r="W14" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V14/(0.85*$B$5)))</f>
-        <v>0.0003014085253</v>
+        <v>0.008657486195</v>
       </c>
       <c r="X14" s="82">
         <f>W14*(E14*1000)*K14</f>
-        <v>30.97424711</v>
+        <v>889.6865688</v>
       </c>
       <c r="Y14" s="82">
         <f>MAX(X14,O14)</f>
-        <v>342.55</v>
+        <v>889.6865688</v>
       </c>
       <c r="Z14" s="83">
         <f>ROUNDUP(Y14/$B$9,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA14" s="82">
         <f>Z14*$B$9</f>
-        <v>398</v>
+        <v>995</v>
       </c>
       <c r="AB14" s="79">
         <f>0.9*AA14*$B$6*(K14-(AA14*$B$6/(0.85*$B$5*(E14*1000)))/2)/1000000</f>
-        <v>49.77351244</v>
+        <v>117.829732</v>
       </c>
       <c r="AC14" s="84" t="str">
         <f>IF(AB14&gt;=H14,"CUMPLE","REVISAR")</f>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AE14" s="79">
         <f>MAX(I14/0.75-AD14,0)</f>
-        <v>0</v>
+        <v>36.75718462</v>
       </c>
       <c r="AF14" s="83">
         <f>IF(AE14&gt;0,MIN($B$11*$B$6*K14/(AE14*1000),MIN(K14/4,6*$B$8,150)),MIN(K14/4,6*$B$8,150))</f>
@@ -2904,19 +2904,19 @@
       </c>
       <c r="AL14" s="79">
         <f>1.25*R14*$B$6*(K14-(1.25*R14*$B$6/(0.85*$B$5*(E14*1000)))/2)/1000000</f>
-        <v>68.51839235</v>
+        <v>187.2105962</v>
       </c>
       <c r="AM14" s="79">
         <f>1.25*AA14*$B$6*(K14-(1.25*AA14*$B$6/(0.85*$B$5*(E14*1000)))/2)/1000000</f>
-        <v>68.51839235</v>
+        <v>159.8306178</v>
       </c>
       <c r="AN14" s="79">
         <f>(AL14+AM14)/B14</f>
-        <v>54.81471388</v>
+        <v>138.8164856</v>
       </c>
       <c r="AO14" s="79">
         <f>MAX(I14,AN14)</f>
-        <v>54.81471388</v>
+        <v>138.8164856</v>
       </c>
     </row>
     <row r="15">
@@ -2930,11 +2930,11 @@
       </c>
       <c r="C15" s="76" t="inlineStr">
         <is>
-          <t>Extremo</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D15" s="77" t="n">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="E15" s="75" t="n">
         <v>0.3</v>
@@ -2943,16 +2943,16 @@
         <v>0.4</v>
       </c>
       <c r="G15" s="78" t="n">
-        <v>6.9</v>
+        <v>112.6</v>
       </c>
       <c r="H15" s="78" t="n">
-        <v>2.3</v>
+        <v>103.3</v>
       </c>
       <c r="I15" s="78" t="n">
-        <v>12</v>
+        <v>91.7</v>
       </c>
       <c r="J15" s="78" t="n">
-        <v>0.3</v>
+        <v>6</v>
       </c>
       <c r="K15" s="79">
         <f>F15*1000-$B$7-$B$10-$B$8/2</f>
@@ -2960,15 +2960,15 @@
       </c>
       <c r="L15" s="80">
         <f>G15*1000000/(0.9*(E15*1000)*K15^2)</f>
-        <v>0.2177897232</v>
+        <v>3.554075772</v>
       </c>
       <c r="M15" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L15/(0.85*$B$5)))</f>
-        <v>0.0005209414896</v>
+        <v>0.00921063658</v>
       </c>
       <c r="N15" s="82">
         <f>M15*(E15*1000)*K15</f>
-        <v>53.53455218</v>
+        <v>946.5310681</v>
       </c>
       <c r="O15" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E15*1000)*K15</f>
@@ -2976,23 +2976,23 @@
       </c>
       <c r="P15" s="82">
         <f>MAX(N15,O15)</f>
-        <v>342.55</v>
+        <v>946.5310681</v>
       </c>
       <c r="Q15" s="83">
         <f>ROUNDUP(P15/$B$9,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R15" s="82">
         <f>Q15*$B$9</f>
-        <v>398</v>
+        <v>995</v>
       </c>
       <c r="S15" s="79">
         <f>R15*$B$6/(0.85*$B$5*(E15*1000))</f>
-        <v>23.41176471</v>
+        <v>58.52941176</v>
       </c>
       <c r="T15" s="79">
         <f>0.9*R15*$B$6*(K15-S15/2)/1000000</f>
-        <v>49.77351244</v>
+        <v>117.829732</v>
       </c>
       <c r="U15" s="84" t="str">
         <f>IF(AND(T15&gt;=G15,P15&lt;=0.025*(E15*1000)*K15,P15&gt;=O15),"CUMPLE","REVISAR")</f>
@@ -3000,31 +3000,31 @@
       </c>
       <c r="V15" s="80">
         <f>H15*1000000/(0.9*(E15*1000)*K15^2)</f>
-        <v>0.07259657439</v>
+        <v>3.260533102</v>
       </c>
       <c r="W15" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V15/(0.85*$B$5)))</f>
-        <v>0.0001731134124</v>
+        <v>0.008383287347</v>
       </c>
       <c r="X15" s="82">
         <f>W15*(E15*1000)*K15</f>
-        <v>17.78999983</v>
+        <v>861.5085242</v>
       </c>
       <c r="Y15" s="82">
         <f>MAX(X15,O15)</f>
-        <v>342.55</v>
+        <v>861.5085242</v>
       </c>
       <c r="Z15" s="83">
         <f>ROUNDUP(Y15/$B$9,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA15" s="82">
         <f>Z15*$B$9</f>
-        <v>398</v>
+        <v>995</v>
       </c>
       <c r="AB15" s="79">
         <f>0.9*AA15*$B$6*(K15-(AA15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v>49.77351244</v>
+        <v>117.829732</v>
       </c>
       <c r="AC15" s="84" t="str">
         <f>IF(AB15&gt;=H15,"CUMPLE","REVISAR")</f>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AE15" s="79">
         <f>MAX(I15/0.75-AD15,0)</f>
-        <v>0</v>
+        <v>29.82385128</v>
       </c>
       <c r="AF15" s="83">
         <f>IF(AE15&gt;0,MIN($B$11*$B$6*K15/(AE15*1000),MIN(K15/4,6*$B$8,150)),MIN(K15/4,6*$B$8,150))</f>
@@ -3056,27 +3056,27 @@
       </c>
       <c r="AJ15" s="85" t="str">
         <f>IF(J15&gt;AI15,"SI - disenar","No - despreciable")</f>
-        <v>No - despreciable</v>
+        <v>SI - disenar</v>
       </c>
       <c r="AK15" s="80">
         <f>IF(J15&gt;AI15,J15*1000000/(0.75*2*0.85*((E15*1000-2*$B$7)*(F15*1000-2*$B$7))*$B$6),0)</f>
-        <v>0</v>
+        <v>0.1591545709</v>
       </c>
       <c r="AL15" s="79">
         <f>1.25*R15*$B$6*(K15-(1.25*R15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v>68.51839235</v>
+        <v>159.8306178</v>
       </c>
       <c r="AM15" s="79">
         <f>1.25*AA15*$B$6*(K15-(1.25*AA15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v>68.51839235</v>
+        <v>159.8306178</v>
       </c>
       <c r="AN15" s="79">
         <f>(AL15+AM15)/B15</f>
-        <v>52.70645566</v>
+        <v>122.9466291</v>
       </c>
       <c r="AO15" s="79">
         <f>MAX(I15,AN15)</f>
-        <v>52.70645566</v>
+        <v>122.9466291</v>
       </c>
     </row>
     <row r="16">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="C16" s="76" t="inlineStr">
         <is>
-          <t>Extremo</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D16" s="77" t="n">
@@ -3103,16 +3103,16 @@
         <v>0.4</v>
       </c>
       <c r="G16" s="78" t="n">
-        <v>118.8</v>
+        <v>107.9</v>
       </c>
       <c r="H16" s="78" t="n">
-        <v>102.8</v>
+        <v>104.9</v>
       </c>
       <c r="I16" s="78" t="n">
-        <v>88.3</v>
+        <v>76</v>
       </c>
       <c r="J16" s="78" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K16" s="79">
         <f>F16*1000-$B$7-$B$10-$B$8/2</f>
@@ -3120,15 +3120,15 @@
       </c>
       <c r="L16" s="80">
         <f>G16*1000000/(0.9*(E16*1000)*K16^2)</f>
-        <v>3.749770886</v>
+        <v>3.405726251</v>
       </c>
       <c r="M16" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L16/(0.85*$B$5)))</f>
-        <v>0.009770311012</v>
+        <v>0.008790726834</v>
       </c>
       <c r="N16" s="82">
         <f>M16*(E16*1000)*K16</f>
-        <v>1004.046011</v>
+        <v>903.3790431</v>
       </c>
       <c r="O16" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E16*1000)*K16</f>
@@ -3136,23 +3136,23 @@
       </c>
       <c r="P16" s="82">
         <f>MAX(N16,O16)</f>
-        <v>1004.046011</v>
+        <v>903.3790431</v>
       </c>
       <c r="Q16" s="83">
         <f>ROUNDUP(P16/$B$9,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R16" s="82">
         <f>Q16*$B$9</f>
-        <v>1194</v>
+        <v>995</v>
       </c>
       <c r="S16" s="79">
         <f>R16*$B$6/(0.85*$B$5*(E16*1000))</f>
-        <v>70.23529412</v>
+        <v>58.52941176</v>
       </c>
       <c r="T16" s="79">
         <f>0.9*R16*$B$6*(K16-S16/2)/1000000</f>
-        <v>138.7540587</v>
+        <v>117.829732</v>
       </c>
       <c r="U16" s="84" t="str">
         <f>IF(AND(T16&gt;=G16,P16&lt;=0.025*(E16*1000)*K16,P16&gt;=O16),"CUMPLE","REVISAR")</f>
@@ -3160,19 +3160,19 @@
       </c>
       <c r="V16" s="80">
         <f>H16*1000000/(0.9*(E16*1000)*K16^2)</f>
-        <v>3.244751238</v>
+        <v>3.311035067</v>
       </c>
       <c r="W16" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V16/(0.85*$B$5)))</f>
-        <v>0.008339207425</v>
+        <v>0.008524614319</v>
       </c>
       <c r="X16" s="82">
         <f>W16*(E16*1000)*K16</f>
-        <v>856.978651</v>
+        <v>876.0319905</v>
       </c>
       <c r="Y16" s="82">
         <f>MAX(X16,O16)</f>
-        <v>856.978651</v>
+        <v>876.0319905</v>
       </c>
       <c r="Z16" s="83">
         <f>ROUNDUP(Y16/$B$9,0)</f>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="AE16" s="79">
         <f>MAX(I16/0.75-AD16,0)</f>
-        <v>25.29051795</v>
+        <v>8.89051795</v>
       </c>
       <c r="AF16" s="83">
         <f>IF(AE16&gt;0,MIN($B$11*$B$6*K16/(AE16*1000),MIN(K16/4,6*$B$8,150)),MIN(K16/4,6*$B$8,150))</f>
@@ -3216,15 +3216,15 @@
       </c>
       <c r="AJ16" s="85" t="str">
         <f>IF(J16&gt;AI16,"SI - disenar","No - despreciable")</f>
-        <v>No - despreciable</v>
+        <v>SI - disenar</v>
       </c>
       <c r="AK16" s="80">
         <f>IF(J16&gt;AI16,J16*1000000/(0.75*2*0.85*((E16*1000-2*$B$7)*(F16*1000-2*$B$7))*$B$6),0)</f>
-        <v>0</v>
+        <v>0.1591545709</v>
       </c>
       <c r="AL16" s="79">
         <f>1.25*R16*$B$6*(K16-(1.25*R16*$B$6/(0.85*$B$5*(E16*1000)))/2)/1000000</f>
-        <v>187.2105962</v>
+        <v>159.8306178</v>
       </c>
       <c r="AM16" s="79">
         <f>1.25*AA16*$B$6*(K16-(1.25*AA16*$B$6/(0.85*$B$5*(E16*1000)))/2)/1000000</f>
@@ -3232,11 +3232,11 @@
       </c>
       <c r="AN16" s="79">
         <f>(AL16+AM16)/B16</f>
-        <v>130.9589487</v>
+        <v>120.6268814</v>
       </c>
       <c r="AO16" s="79">
         <f>MAX(I16,AN16)</f>
-        <v>130.9589487</v>
+        <v>120.6268814</v>
       </c>
     </row>
     <row r="17">
@@ -3250,11 +3250,11 @@
       </c>
       <c r="C17" s="76" t="inlineStr">
         <is>
-          <t>Extremo</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D17" s="77" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E17" s="75" t="n">
         <v>0.3</v>
@@ -3263,16 +3263,16 @@
         <v>0.4</v>
       </c>
       <c r="G17" s="78" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="H17" s="78" t="n">
-        <v>89.59999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I17" s="78" t="n">
-        <v>64.90000000000001</v>
+        <v>52.2</v>
       </c>
       <c r="J17" s="78" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K17" s="79">
         <f>F17*1000-$B$7-$B$10-$B$8/2</f>
@@ -3280,15 +3280,15 @@
       </c>
       <c r="L17" s="80">
         <f>G17*1000000/(0.9*(E17*1000)*K17^2)</f>
-        <v>3.345755167</v>
+        <v>2.99855416</v>
       </c>
       <c r="M17" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L17/(0.85*$B$5)))</f>
-        <v>0.008622017764</v>
+        <v>0.007656693712</v>
       </c>
       <c r="N17" s="82">
         <f>M17*(E17*1000)*K17</f>
-        <v>886.0416556</v>
+        <v>786.8401293</v>
       </c>
       <c r="O17" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E17*1000)*K17</f>
@@ -3296,23 +3296,23 @@
       </c>
       <c r="P17" s="82">
         <f>MAX(N17,O17)</f>
-        <v>886.0416556</v>
+        <v>786.8401293</v>
       </c>
       <c r="Q17" s="83">
         <f>ROUNDUP(P17/$B$9,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R17" s="82">
         <f>Q17*$B$9</f>
-        <v>995</v>
+        <v>796</v>
       </c>
       <c r="S17" s="79">
         <f>R17*$B$6/(0.85*$B$5*(E17*1000))</f>
-        <v>58.52941176</v>
+        <v>46.82352941</v>
       </c>
       <c r="T17" s="79">
         <f>0.9*R17*$B$6*(K17-S17/2)/1000000</f>
-        <v>117.829732</v>
+        <v>96.02486534</v>
       </c>
       <c r="U17" s="84" t="str">
         <f>IF(AND(T17&gt;=G17,P17&lt;=0.025*(E17*1000)*K17,P17&gt;=O17),"CUMPLE","REVISAR")</f>
@@ -3320,19 +3320,19 @@
       </c>
       <c r="V17" s="80">
         <f>H17*1000000/(0.9*(E17*1000)*K17^2)</f>
-        <v>2.828110028</v>
+        <v>2.87545562</v>
       </c>
       <c r="W17" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V17/(0.85*$B$5)))</f>
-        <v>0.007189699199</v>
+        <v>0.007318976598</v>
       </c>
       <c r="X17" s="82">
         <f>W17*(E17*1000)*K17</f>
-        <v>738.8494382</v>
+        <v>752.1346301</v>
       </c>
       <c r="Y17" s="82">
         <f>MAX(X17,O17)</f>
-        <v>738.8494382</v>
+        <v>752.1346301</v>
       </c>
       <c r="Z17" s="83">
         <f>ROUNDUP(Y17/$B$9,0)</f>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="AL17" s="79">
         <f>1.25*R17*$B$6*(K17-(1.25*R17*$B$6/(0.85*$B$5*(E17*1000)))/2)/1000000</f>
-        <v>159.8306178</v>
+        <v>130.9219244</v>
       </c>
       <c r="AM17" s="79">
         <f>1.25*AA17*$B$6*(K17-(1.25*AA17*$B$6/(0.85*$B$5*(E17*1000)))/2)/1000000</f>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="AN17" s="79">
         <f>(AL17+AM17)/B17</f>
-        <v>77.53401126</v>
+        <v>69.82502635</v>
       </c>
       <c r="AO17" s="79">
         <f>MAX(I17,AN17)</f>
-        <v>77.53401126</v>
+        <v>69.82502635</v>
       </c>
     </row>
     <row r="18">
@@ -3406,15 +3406,15 @@
         </is>
       </c>
       <c r="B18" s="75" t="n">
-        <v>3.75</v>
+        <v>3.81</v>
       </c>
       <c r="C18" s="76" t="inlineStr">
         <is>
-          <t>Interior</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D18" s="77" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E18" s="75" t="n">
         <v>0.3</v>
@@ -3423,16 +3423,16 @@
         <v>0.4</v>
       </c>
       <c r="G18" s="78" t="n">
-        <v>25</v>
+        <v>91.3</v>
       </c>
       <c r="H18" s="78" t="n">
-        <v>16.5</v>
+        <v>83.5</v>
       </c>
       <c r="I18" s="78" t="n">
-        <v>21.7</v>
+        <v>46.6</v>
       </c>
       <c r="J18" s="78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="K18" s="79">
         <f>F18*1000-$B$7-$B$10-$B$8/2</f>
@@ -3440,15 +3440,15 @@
       </c>
       <c r="L18" s="80">
         <f>G18*1000000/(0.9*(E18*1000)*K18^2)</f>
-        <v>0.7890931999</v>
+        <v>2.881768366</v>
       </c>
       <c r="M18" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L18/(0.85*$B$5)))</f>
-        <v>0.00191101673</v>
+        <v>0.007336239182</v>
       </c>
       <c r="N18" s="82">
         <f>M18*(E18*1000)*K18</f>
-        <v>196.3856342</v>
+        <v>753.9086195</v>
       </c>
       <c r="O18" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E18*1000)*K18</f>
@@ -3456,23 +3456,23 @@
       </c>
       <c r="P18" s="82">
         <f>MAX(N18,O18)</f>
-        <v>342.55</v>
+        <v>753.9086195</v>
       </c>
       <c r="Q18" s="83">
         <f>ROUNDUP(P18/$B$9,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R18" s="82">
         <f>Q18*$B$9</f>
-        <v>398</v>
+        <v>796</v>
       </c>
       <c r="S18" s="79">
         <f>R18*$B$6/(0.85*$B$5*(E18*1000))</f>
-        <v>23.41176471</v>
+        <v>46.82352941</v>
       </c>
       <c r="T18" s="79">
         <f>0.9*R18*$B$6*(K18-S18/2)/1000000</f>
-        <v>49.77351244</v>
+        <v>96.02486534</v>
       </c>
       <c r="U18" s="84" t="str">
         <f>IF(AND(T18&gt;=G18,P18&lt;=0.025*(E18*1000)*K18,P18&gt;=O18),"CUMPLE","REVISAR")</f>
@@ -3480,31 +3480,31 @@
       </c>
       <c r="V18" s="80">
         <f>H18*1000000/(0.9*(E18*1000)*K18^2)</f>
-        <v>0.5208015119</v>
+        <v>2.635571288</v>
       </c>
       <c r="W18" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V18/(0.85*$B$5)))</f>
-        <v>0.001253875997</v>
+        <v>0.006667414591</v>
       </c>
       <c r="X18" s="82">
         <f>W18*(E18*1000)*K18</f>
-        <v>128.8545668</v>
+        <v>685.1768605</v>
       </c>
       <c r="Y18" s="82">
         <f>MAX(X18,O18)</f>
-        <v>342.55</v>
+        <v>685.1768605</v>
       </c>
       <c r="Z18" s="83">
         <f>ROUNDUP(Y18/$B$9,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA18" s="82">
         <f>Z18*$B$9</f>
-        <v>398</v>
+        <v>796</v>
       </c>
       <c r="AB18" s="79">
         <f>0.9*AA18*$B$6*(K18-(AA18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v>49.77351244</v>
+        <v>96.02486534</v>
       </c>
       <c r="AC18" s="84" t="str">
         <f>IF(AB18&gt;=H18,"CUMPLE","REVISAR")</f>
@@ -3544,19 +3544,19 @@
       </c>
       <c r="AL18" s="79">
         <f>1.25*R18*$B$6*(K18-(1.25*R18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v>68.51839235</v>
+        <v>130.9219244</v>
       </c>
       <c r="AM18" s="79">
         <f>1.25*AA18*$B$6*(K18-(1.25*AA18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v>68.51839235</v>
+        <v>130.9219244</v>
       </c>
       <c r="AN18" s="79">
         <f>(AL18+AM18)/B18</f>
-        <v>36.54314259</v>
+        <v>68.72541964</v>
       </c>
       <c r="AO18" s="79">
         <f>MAX(I18,AN18)</f>
-        <v>36.54314259</v>
+        <v>68.72541964</v>
       </c>
     </row>
     <row r="19">
@@ -3566,15 +3566,15 @@
         </is>
       </c>
       <c r="B19" s="75" t="n">
-        <v>3.81</v>
+        <v>3.85</v>
       </c>
       <c r="C19" s="76" t="inlineStr">
         <is>
-          <t>Extremo</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D19" s="77" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E19" s="75" t="n">
         <v>0.3</v>
@@ -3583,16 +3583,16 @@
         <v>0.4</v>
       </c>
       <c r="G19" s="78" t="n">
-        <v>113.9</v>
+        <v>105.9</v>
       </c>
       <c r="H19" s="78" t="n">
-        <v>81.09999999999999</v>
+        <v>100.7</v>
       </c>
       <c r="I19" s="78" t="n">
-        <v>73.5</v>
+        <v>56.4</v>
       </c>
       <c r="J19" s="78" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="K19" s="79">
         <f>F19*1000-$B$7-$B$10-$B$8/2</f>
@@ -3600,15 +3600,15 @@
       </c>
       <c r="L19" s="80">
         <f>G19*1000000/(0.9*(E19*1000)*K19^2)</f>
-        <v>3.595108619</v>
+        <v>3.342598795</v>
       </c>
       <c r="M19" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L19/(0.85*$B$5)))</f>
-        <v>0.009327439421</v>
+        <v>0.008613154747</v>
       </c>
       <c r="N19" s="82">
         <f>M19*(E19*1000)*K19</f>
-        <v>958.5343121</v>
+        <v>885.1308476</v>
       </c>
       <c r="O19" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E19*1000)*K19</f>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="P19" s="82">
         <f>MAX(N19,O19)</f>
-        <v>958.5343121</v>
+        <v>885.1308476</v>
       </c>
       <c r="Q19" s="83">
         <f>ROUNDUP(P19/$B$9,0)</f>
@@ -3640,31 +3640,31 @@
       </c>
       <c r="V19" s="80">
         <f>H19*1000000/(0.9*(E19*1000)*K19^2)</f>
-        <v>2.55981834</v>
+        <v>3.178467409</v>
       </c>
       <c r="W19" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V19/(0.85*$B$5)))</f>
-        <v>0.006463414983</v>
+        <v>0.008154509126</v>
       </c>
       <c r="X19" s="82">
         <f>W19*(E19*1000)*K19</f>
-        <v>664.2128408</v>
+        <v>837.9981303</v>
       </c>
       <c r="Y19" s="82">
         <f>MAX(X19,O19)</f>
-        <v>664.2128408</v>
+        <v>837.9981303</v>
       </c>
       <c r="Z19" s="83">
         <f>ROUNDUP(Y19/$B$9,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA19" s="82">
         <f>Z19*$B$9</f>
-        <v>796</v>
+        <v>995</v>
       </c>
       <c r="AB19" s="79">
         <f>0.9*AA19*$B$6*(K19-(AA19*$B$6/(0.85*$B$5*(E19*1000)))/2)/1000000</f>
-        <v>96.02486534</v>
+        <v>117.829732</v>
       </c>
       <c r="AC19" s="84" t="str">
         <f>IF(AB19&gt;=H19,"CUMPLE","REVISAR")</f>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="AE19" s="79">
         <f>MAX(I19/0.75-AD19,0)</f>
-        <v>5.557184616</v>
+        <v>0</v>
       </c>
       <c r="AF19" s="83">
         <f>IF(AE19&gt;0,MIN($B$11*$B$6*K19/(AE19*1000),MIN(K19/4,6*$B$8,150)),MIN(K19/4,6*$B$8,150))</f>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="AK19" s="80">
         <f>IF(J19&gt;AI19,J19*1000000/(0.75*2*0.85*((E19*1000-2*$B$7)*(F19*1000-2*$B$7))*$B$6),0)</f>
-        <v>0.1830277566</v>
+        <v>0.1511968424</v>
       </c>
       <c r="AL19" s="79">
         <f>1.25*R19*$B$6*(K19-(1.25*R19*$B$6/(0.85*$B$5*(E19*1000)))/2)/1000000</f>
@@ -3708,15 +3708,15 @@
       </c>
       <c r="AM19" s="79">
         <f>1.25*AA19*$B$6*(K19-(1.25*AA19*$B$6/(0.85*$B$5*(E19*1000)))/2)/1000000</f>
-        <v>130.9219244</v>
+        <v>159.8306178</v>
       </c>
       <c r="AN19" s="79">
         <f>(AL19+AM19)/B19</f>
-        <v>76.31300321</v>
+        <v>83.02889238</v>
       </c>
       <c r="AO19" s="79">
         <f>MAX(I19,AN19)</f>
-        <v>76.31300321</v>
+        <v>83.02889238</v>
       </c>
     </row>
     <row r="20">
@@ -3726,15 +3726,15 @@
         </is>
       </c>
       <c r="B20" s="75" t="n">
-        <v>3.81</v>
+        <v>3.9</v>
       </c>
       <c r="C20" s="76" t="inlineStr">
         <is>
-          <t>Interior</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D20" s="77" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E20" s="75" t="n">
         <v>0.3</v>
@@ -3743,16 +3743,16 @@
         <v>0.4</v>
       </c>
       <c r="G20" s="78" t="n">
-        <v>105.7</v>
+        <v>106.1</v>
       </c>
       <c r="H20" s="78" t="n">
-        <v>74.2</v>
+        <v>96.2</v>
       </c>
       <c r="I20" s="78" t="n">
-        <v>68.40000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="J20" s="78" t="n">
-        <v>6.5</v>
+        <v>16.7</v>
       </c>
       <c r="K20" s="79">
         <f>F20*1000-$B$7-$B$10-$B$8/2</f>
@@ -3760,15 +3760,15 @@
       </c>
       <c r="L20" s="80">
         <f>G20*1000000/(0.9*(E20*1000)*K20^2)</f>
-        <v>3.336286049</v>
+        <v>3.34891154</v>
       </c>
       <c r="M20" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L20/(0.85*$B$5)))</f>
-        <v>0.008595433615</v>
+        <v>0.008630882417</v>
       </c>
       <c r="N20" s="82">
         <f>M20*(E20*1000)*K20</f>
-        <v>883.3097355</v>
+        <v>886.9526316</v>
       </c>
       <c r="O20" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E20*1000)*K20</f>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="P20" s="82">
         <f>MAX(N20,O20)</f>
-        <v>883.3097355</v>
+        <v>886.9526316</v>
       </c>
       <c r="Q20" s="83">
         <f>ROUNDUP(P20/$B$9,0)</f>
@@ -3800,31 +3800,31 @@
       </c>
       <c r="V20" s="80">
         <f>H20*1000000/(0.9*(E20*1000)*K20^2)</f>
-        <v>2.342028617</v>
+        <v>3.036430633</v>
       </c>
       <c r="W20" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V20/(0.85*$B$5)))</f>
-        <v>0.00588148049</v>
+        <v>0.007761075848</v>
       </c>
       <c r="X20" s="82">
         <f>W20*(E20*1000)*K20</f>
-        <v>604.4103425</v>
+        <v>797.5669596</v>
       </c>
       <c r="Y20" s="82">
         <f>MAX(X20,O20)</f>
-        <v>604.4103425</v>
+        <v>797.5669596</v>
       </c>
       <c r="Z20" s="83">
         <f>ROUNDUP(Y20/$B$9,0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA20" s="82">
         <f>Z20*$B$9</f>
-        <v>796</v>
+        <v>995</v>
       </c>
       <c r="AB20" s="79">
         <f>0.9*AA20*$B$6*(K20-(AA20*$B$6/(0.85*$B$5*(E20*1000)))/2)/1000000</f>
-        <v>96.02486534</v>
+        <v>117.829732</v>
       </c>
       <c r="AC20" s="84" t="str">
         <f>IF(AB20&gt;=H20,"CUMPLE","REVISAR")</f>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="AK20" s="80">
         <f>IF(J20&gt;AI20,J20*1000000/(0.75*2*0.85*((E20*1000-2*$B$7)*(F20*1000-2*$B$7))*$B$6),0)</f>
-        <v>0.1724174518</v>
+        <v>0.4429802224</v>
       </c>
       <c r="AL20" s="79">
         <f>1.25*R20*$B$6*(K20-(1.25*R20*$B$6/(0.85*$B$5*(E20*1000)))/2)/1000000</f>
@@ -3868,15 +3868,15 @@
       </c>
       <c r="AM20" s="79">
         <f>1.25*AA20*$B$6*(K20-(1.25*AA20*$B$6/(0.85*$B$5*(E20*1000)))/2)/1000000</f>
-        <v>130.9219244</v>
+        <v>159.8306178</v>
       </c>
       <c r="AN20" s="79">
         <f>(AL20+AM20)/B20</f>
-        <v>76.31300321</v>
+        <v>81.9644194</v>
       </c>
       <c r="AO20" s="79">
         <f>MAX(I20,AN20)</f>
-        <v>76.31300321</v>
+        <v>81.9644194</v>
       </c>
     </row>
     <row r="21">
@@ -3886,15 +3886,15 @@
         </is>
       </c>
       <c r="B21" s="75" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="C21" s="76" t="inlineStr">
         <is>
-          <t>Interior</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D21" s="77" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E21" s="75" t="n">
         <v>0.3</v>
@@ -3903,16 +3903,16 @@
         <v>0.4</v>
       </c>
       <c r="G21" s="78" t="n">
-        <v>121.6</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="H21" s="78" t="n">
-        <v>93.3</v>
+        <v>92.7</v>
       </c>
       <c r="I21" s="78" t="n">
-        <v>77.90000000000001</v>
+        <v>52.3</v>
       </c>
       <c r="J21" s="78" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="K21" s="79">
         <f>F21*1000-$B$7-$B$10-$B$8/2</f>
@@ -3920,15 +3920,15 @@
       </c>
       <c r="L21" s="80">
         <f>G21*1000000/(0.9*(E21*1000)*K21^2)</f>
-        <v>3.838149324</v>
+        <v>3.058525243</v>
       </c>
       <c r="M21" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L21/(0.85*$B$5)))</f>
-        <v>0.01002526849</v>
+        <v>0.007822068442</v>
       </c>
       <c r="N21" s="82">
         <f>M21*(E21*1000)*K21</f>
-        <v>1030.246717</v>
+        <v>803.8348634</v>
       </c>
       <c r="O21" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E21*1000)*K21</f>
@@ -3936,23 +3936,23 @@
       </c>
       <c r="P21" s="82">
         <f>MAX(N21,O21)</f>
-        <v>1030.246717</v>
+        <v>803.8348634</v>
       </c>
       <c r="Q21" s="83">
         <f>ROUNDUP(P21/$B$9,0)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R21" s="82">
         <f>Q21*$B$9</f>
-        <v>1194</v>
+        <v>995</v>
       </c>
       <c r="S21" s="79">
         <f>R21*$B$6/(0.85*$B$5*(E21*1000))</f>
-        <v>70.23529412</v>
+        <v>58.52941176</v>
       </c>
       <c r="T21" s="79">
         <f>0.9*R21*$B$6*(K21-S21/2)/1000000</f>
-        <v>138.7540587</v>
+        <v>117.829732</v>
       </c>
       <c r="U21" s="84" t="str">
         <f>IF(AND(T21&gt;=G21,P21&lt;=0.025*(E21*1000)*K21,P21&gt;=O21),"CUMPLE","REVISAR")</f>
@@ -3960,19 +3960,19 @@
       </c>
       <c r="V21" s="80">
         <f>H21*1000000/(0.9*(E21*1000)*K21^2)</f>
-        <v>2.944895822</v>
+        <v>2.925957585</v>
       </c>
       <c r="W21" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V21/(0.85*$B$5)))</f>
-        <v>0.007509198435</v>
+        <v>0.007457246828</v>
       </c>
       <c r="X21" s="82">
         <f>W21*(E21*1000)*K21</f>
-        <v>771.6827771</v>
+        <v>766.3439703</v>
       </c>
       <c r="Y21" s="82">
         <f>MAX(X21,O21)</f>
-        <v>771.6827771</v>
+        <v>766.3439703</v>
       </c>
       <c r="Z21" s="83">
         <f>ROUNDUP(Y21/$B$9,0)</f>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="AE21" s="79">
         <f>MAX(I21/0.75-AD21,0)</f>
-        <v>11.42385128</v>
+        <v>0</v>
       </c>
       <c r="AF21" s="83">
         <f>IF(AE21&gt;0,MIN($B$11*$B$6*K21/(AE21*1000),MIN(K21/4,6*$B$8,150)),MIN(K21/4,6*$B$8,150))</f>
@@ -4016,15 +4016,15 @@
       </c>
       <c r="AJ21" s="85" t="str">
         <f>IF(J21&gt;AI21,"SI - disenar","No - despreciable")</f>
-        <v>No - despreciable</v>
+        <v>SI - disenar</v>
       </c>
       <c r="AK21" s="80">
         <f>IF(J21&gt;AI21,J21*1000000/(0.75*2*0.85*((E21*1000-2*$B$7)*(F21*1000-2*$B$7))*$B$6),0)</f>
-        <v>0</v>
+        <v>0.14589169</v>
       </c>
       <c r="AL21" s="79">
         <f>1.25*R21*$B$6*(K21-(1.25*R21*$B$6/(0.85*$B$5*(E21*1000)))/2)/1000000</f>
-        <v>187.2105962</v>
+        <v>159.8306178</v>
       </c>
       <c r="AM21" s="79">
         <f>1.25*AA21*$B$6*(K21-(1.25*AA21*$B$6/(0.85*$B$5*(E21*1000)))/2)/1000000</f>
@@ -4032,11 +4032,11 @@
       </c>
       <c r="AN21" s="79">
         <f>(AL21+AM21)/B21</f>
-        <v>82.63182353</v>
+        <v>72.68813556</v>
       </c>
       <c r="AO21" s="79">
         <f>MAX(I21,AN21)</f>
-        <v>82.63182353</v>
+        <v>72.68813556</v>
       </c>
     </row>
     <row r="22">
@@ -4046,15 +4046,15 @@
         </is>
       </c>
       <c r="B22" s="75" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="C22" s="76" t="inlineStr">
         <is>
-          <t>Interior</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D22" s="77" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E22" s="75" t="n">
         <v>0.3</v>
@@ -4063,16 +4063,16 @@
         <v>0.4</v>
       </c>
       <c r="G22" s="78" t="n">
-        <v>128.9</v>
+        <v>80.8</v>
       </c>
       <c r="H22" s="78" t="n">
-        <v>90.7</v>
+        <v>76</v>
       </c>
       <c r="I22" s="78" t="n">
-        <v>91.90000000000001</v>
+        <v>34.2</v>
       </c>
       <c r="J22" s="78" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K22" s="79">
         <f>F22*1000-$B$7-$B$10-$B$8/2</f>
@@ -4080,15 +4080,15 @@
       </c>
       <c r="L22" s="80">
         <f>G22*1000000/(0.9*(E22*1000)*K22^2)</f>
-        <v>4.068564539</v>
+        <v>2.550349222</v>
       </c>
       <c r="M22" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L22/(0.85*$B$5)))</f>
-        <v>0.01069662762</v>
+        <v>0.006437973288</v>
       </c>
       <c r="N22" s="82">
         <f>M22*(E22*1000)*K22</f>
-        <v>1099.238938</v>
+        <v>661.598325</v>
       </c>
       <c r="O22" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E22*1000)*K22</f>
@@ -4096,23 +4096,23 @@
       </c>
       <c r="P22" s="82">
         <f>MAX(N22,O22)</f>
-        <v>1099.238938</v>
+        <v>661.598325</v>
       </c>
       <c r="Q22" s="83">
         <f>ROUNDUP(P22/$B$9,0)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R22" s="82">
         <f>Q22*$B$9</f>
-        <v>1194</v>
+        <v>796</v>
       </c>
       <c r="S22" s="79">
         <f>R22*$B$6/(0.85*$B$5*(E22*1000))</f>
-        <v>70.23529412</v>
+        <v>46.82352941</v>
       </c>
       <c r="T22" s="79">
         <f>0.9*R22*$B$6*(K22-S22/2)/1000000</f>
-        <v>138.7540587</v>
+        <v>96.02486534</v>
       </c>
       <c r="U22" s="84" t="str">
         <f>IF(AND(T22&gt;=G22,P22&lt;=0.025*(E22*1000)*K22,P22&gt;=O22),"CUMPLE","REVISAR")</f>
@@ -4120,19 +4120,19 @@
       </c>
       <c r="V22" s="80">
         <f>H22*1000000/(0.9*(E22*1000)*K22^2)</f>
-        <v>2.862830129</v>
+        <v>2.398843328</v>
       </c>
       <c r="W22" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V22/(0.85*$B$5)))</f>
-        <v>0.007284469533</v>
+        <v>0.006032644691</v>
       </c>
       <c r="X22" s="82">
         <f>W22*(E22*1000)*K22</f>
-        <v>748.5885116</v>
+        <v>619.9447317</v>
       </c>
       <c r="Y22" s="82">
         <f>MAX(X22,O22)</f>
-        <v>748.5885116</v>
+        <v>619.9447317</v>
       </c>
       <c r="Z22" s="83">
         <f>ROUNDUP(Y22/$B$9,0)</f>
@@ -4156,7 +4156,7 @@
       </c>
       <c r="AE22" s="79">
         <f>MAX(I22/0.75-AD22,0)</f>
-        <v>30.09051795</v>
+        <v>0</v>
       </c>
       <c r="AF22" s="83">
         <f>IF(AE22&gt;0,MIN($B$11*$B$6*K22/(AE22*1000),MIN(K22/4,6*$B$8,150)),MIN(K22/4,6*$B$8,150))</f>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="AL22" s="79">
         <f>1.25*R22*$B$6*(K22-(1.25*R22*$B$6/(0.85*$B$5*(E22*1000)))/2)/1000000</f>
-        <v>187.2105962</v>
+        <v>130.9219244</v>
       </c>
       <c r="AM22" s="79">
         <f>1.25*AA22*$B$6*(K22-(1.25*AA22*$B$6/(0.85*$B$5*(E22*1000)))/2)/1000000</f>
@@ -4192,495 +4192,15 @@
       </c>
       <c r="AN22" s="79">
         <f>(AL22+AM22)/B22</f>
-        <v>81.57244118</v>
+        <v>51.34193114</v>
       </c>
       <c r="AO22" s="79">
         <f>MAX(I22,AN22)</f>
-        <v>91.9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="72" t="inlineStr">
-        <is>
-          <t>VC-10</t>
-        </is>
-      </c>
-      <c r="B23" s="75" t="n">
-        <v>4</v>
-      </c>
-      <c r="C23" s="76" t="inlineStr">
-        <is>
-          <t>Interior</t>
-        </is>
-      </c>
-      <c r="D23" s="77" t="n">
-        <v>40</v>
-      </c>
-      <c r="E23" s="75" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F23" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G23" s="78" t="n">
-        <v>104</v>
-      </c>
-      <c r="H23" s="78" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="I23" s="78" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="J23" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="79">
-        <f>F23*1000-$B$7-$B$10-$B$8/2</f>
-        <v>342.55</v>
-      </c>
-      <c r="L23" s="80">
-        <f>G23*1000000/(0.9*(E23*1000)*K23^2)</f>
-        <v>3.282627711</v>
-      </c>
-      <c r="M23" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L23/(0.85*$B$5)))</f>
-        <v>0.008445066931</v>
-      </c>
-      <c r="N23" s="82">
-        <f>M23*(E23*1000)*K23</f>
-        <v>867.8573032</v>
-      </c>
-      <c r="O23" s="82">
-        <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E23*1000)*K23</f>
-        <v>342.55</v>
-      </c>
-      <c r="P23" s="82">
-        <f>MAX(N23,O23)</f>
-        <v>867.8573032</v>
-      </c>
-      <c r="Q23" s="83">
-        <f>ROUNDUP(P23/$B$9,0)</f>
-        <v>5</v>
-      </c>
-      <c r="R23" s="82">
-        <f>Q23*$B$9</f>
-        <v>995</v>
-      </c>
-      <c r="S23" s="79">
-        <f>R23*$B$6/(0.85*$B$5*(E23*1000))</f>
-        <v>58.52941176</v>
-      </c>
-      <c r="T23" s="79">
-        <f>0.9*R23*$B$6*(K23-S23/2)/1000000</f>
-        <v>117.829732</v>
-      </c>
-      <c r="U23" s="84" t="str">
-        <f>IF(AND(T23&gt;=G23,P23&lt;=0.025*(E23*1000)*K23,P23&gt;=O23),"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="V23" s="80">
-        <f>H23*1000000/(0.9*(E23*1000)*K23^2)</f>
-        <v>2.752357081</v>
-      </c>
-      <c r="W23" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V23/(0.85*$B$5)))</f>
-        <v>0.006983555036</v>
-      </c>
-      <c r="X23" s="82">
-        <f>W23*(E23*1000)*K23</f>
-        <v>717.6650333</v>
-      </c>
-      <c r="Y23" s="82">
-        <f>MAX(X23,O23)</f>
-        <v>717.6650333</v>
-      </c>
-      <c r="Z23" s="83">
-        <f>ROUNDUP(Y23/$B$9,0)</f>
-        <v>4</v>
-      </c>
-      <c r="AA23" s="82">
-        <f>Z23*$B$9</f>
-        <v>796</v>
-      </c>
-      <c r="AB23" s="79">
-        <f>0.9*AA23*$B$6*(K23-(AA23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v>96.02486534</v>
-      </c>
-      <c r="AC23" s="84" t="str">
-        <f>IF(AB23&gt;=H23,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AD23" s="79">
-        <f>0.17*SQRT($B$5)*(E23*1000)*K23/1000</f>
-        <v>92.44281538</v>
-      </c>
-      <c r="AE23" s="79">
-        <f>MAX(I23/0.75-AD23,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF23" s="83">
-        <f>IF(AE23&gt;0,MIN($B$11*$B$6*K23/(AE23*1000),MIN(K23/4,6*$B$8,150)),MIN(K23/4,6*$B$8,150))</f>
-        <v>85.6375</v>
-      </c>
-      <c r="AG23" s="79">
-        <f>0.66*SQRT($B$5)*(E23*1000)*K23/1000</f>
-        <v>358.8956362</v>
-      </c>
-      <c r="AH23" s="84" t="str">
-        <f>IF(AE23&lt;=AG23,"CUMPLE","AUMENTAR SECCION")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AI23" s="79">
-        <f>0.75*0.083*SQRT($B$5)*(((E23*1000)*(F23*1000))^2/(2*((E23*1000)+(F23*1000))))/1000000</f>
-        <v>3.388073536</v>
-      </c>
-      <c r="AJ23" s="85" t="str">
-        <f>IF(J23&gt;AI23,"SI - disenar","No - despreciable")</f>
-        <v>No - despreciable</v>
-      </c>
-      <c r="AK23" s="80">
-        <f>IF(J23&gt;AI23,J23*1000000/(0.75*2*0.85*((E23*1000-2*$B$7)*(F23*1000-2*$B$7))*$B$6),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL23" s="79">
-        <f>1.25*R23*$B$6*(K23-(1.25*R23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v>159.8306178</v>
-      </c>
-      <c r="AM23" s="79">
-        <f>1.25*AA23*$B$6*(K23-(1.25*AA23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v>130.9219244</v>
-      </c>
-      <c r="AN23" s="79">
-        <f>(AL23+AM23)/B23</f>
-        <v>72.68813556</v>
-      </c>
-      <c r="AO23" s="79">
-        <f>MAX(I23,AN23)</f>
-        <v>72.68813556</v>
+        <v>51.34193114</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="72" t="inlineStr">
-        <is>
-          <t>VC-11</t>
-        </is>
-      </c>
-      <c r="B24" s="75" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C24" s="76" t="inlineStr">
-        <is>
-          <t>Extremo</t>
-        </is>
-      </c>
-      <c r="D24" s="77" t="n">
-        <v>16</v>
-      </c>
-      <c r="E24" s="75" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F24" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G24" s="78" t="n">
-        <v>97.5</v>
-      </c>
-      <c r="H24" s="78" t="n">
-        <v>71</v>
-      </c>
-      <c r="I24" s="78" t="n">
-        <v>50</v>
-      </c>
-      <c r="J24" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="79">
-        <f>F24*1000-$B$7-$B$10-$B$8/2</f>
-        <v>342.55</v>
-      </c>
-      <c r="L24" s="80">
-        <f>G24*1000000/(0.9*(E24*1000)*K24^2)</f>
-        <v>3.07746348</v>
-      </c>
-      <c r="M24" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L24/(0.85*$B$5)))</f>
-        <v>0.007874408491</v>
-      </c>
-      <c r="N24" s="82">
-        <f>M24*(E24*1000)*K24</f>
-        <v>809.2135885</v>
-      </c>
-      <c r="O24" s="82">
-        <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E24*1000)*K24</f>
-        <v>342.55</v>
-      </c>
-      <c r="P24" s="82">
-        <f>MAX(N24,O24)</f>
-        <v>809.2135885</v>
-      </c>
-      <c r="Q24" s="83">
-        <f>ROUNDUP(P24/$B$9,0)</f>
-        <v>5</v>
-      </c>
-      <c r="R24" s="82">
-        <f>Q24*$B$9</f>
-        <v>995</v>
-      </c>
-      <c r="S24" s="79">
-        <f>R24*$B$6/(0.85*$B$5*(E24*1000))</f>
-        <v>58.52941176</v>
-      </c>
-      <c r="T24" s="79">
-        <f>0.9*R24*$B$6*(K24-S24/2)/1000000</f>
-        <v>117.829732</v>
-      </c>
-      <c r="U24" s="84" t="str">
-        <f>IF(AND(T24&gt;=G24,P24&lt;=0.025*(E24*1000)*K24,P24&gt;=O24),"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="V24" s="80">
-        <f>H24*1000000/(0.9*(E24*1000)*K24^2)</f>
-        <v>2.241024688</v>
-      </c>
-      <c r="W24" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V24/(0.85*$B$5)))</f>
-        <v>0.005613849275</v>
-      </c>
-      <c r="X24" s="82">
-        <f>W24*(E24*1000)*K24</f>
-        <v>576.9072207</v>
-      </c>
-      <c r="Y24" s="82">
-        <f>MAX(X24,O24)</f>
-        <v>576.9072207</v>
-      </c>
-      <c r="Z24" s="83">
-        <f>ROUNDUP(Y24/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA24" s="82">
-        <f>Z24*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="AB24" s="79">
-        <f>0.9*AA24*$B$6*(K24-(AA24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v>73.33945883</v>
-      </c>
-      <c r="AC24" s="84" t="str">
-        <f>IF(AB24&gt;=H24,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AD24" s="79">
-        <f>0.17*SQRT($B$5)*(E24*1000)*K24/1000</f>
-        <v>92.44281538</v>
-      </c>
-      <c r="AE24" s="79">
-        <f>MAX(I24/0.75-AD24,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF24" s="83">
-        <f>IF(AE24&gt;0,MIN($B$11*$B$6*K24/(AE24*1000),MIN(K24/4,6*$B$8,150)),MIN(K24/4,6*$B$8,150))</f>
-        <v>85.6375</v>
-      </c>
-      <c r="AG24" s="79">
-        <f>0.66*SQRT($B$5)*(E24*1000)*K24/1000</f>
-        <v>358.8956362</v>
-      </c>
-      <c r="AH24" s="84" t="str">
-        <f>IF(AE24&lt;=AG24,"CUMPLE","AUMENTAR SECCION")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AI24" s="79">
-        <f>0.75*0.083*SQRT($B$5)*(((E24*1000)*(F24*1000))^2/(2*((E24*1000)+(F24*1000))))/1000000</f>
-        <v>3.388073536</v>
-      </c>
-      <c r="AJ24" s="85" t="str">
-        <f>IF(J24&gt;AI24,"SI - disenar","No - despreciable")</f>
-        <v>No - despreciable</v>
-      </c>
-      <c r="AK24" s="80">
-        <f>IF(J24&gt;AI24,J24*1000000/(0.75*2*0.85*((E24*1000-2*$B$7)*(F24*1000-2*$B$7))*$B$6),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL24" s="79">
-        <f>1.25*R24*$B$6*(K24-(1.25*R24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v>159.8306178</v>
-      </c>
-      <c r="AM24" s="79">
-        <f>1.25*AA24*$B$6*(K24-(1.25*AA24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v>100.4845159</v>
-      </c>
-      <c r="AN24" s="79">
-        <f>(AL24+AM24)/B24</f>
-        <v>51.04218309</v>
-      </c>
-      <c r="AO24" s="79">
-        <f>MAX(I24,AN24)</f>
-        <v>51.04218309</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="72" t="inlineStr">
-        <is>
-          <t>VC-12</t>
-        </is>
-      </c>
-      <c r="B25" s="75" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="C25" s="76" t="inlineStr">
-        <is>
-          <t>Interior</t>
-        </is>
-      </c>
-      <c r="D25" s="77" t="n">
-        <v>4</v>
-      </c>
-      <c r="E25" s="75" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F25" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G25" s="78" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="H25" s="78" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="I25" s="78" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="J25" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="79">
-        <f>F25*1000-$B$7-$B$10-$B$8/2</f>
-        <v>342.55</v>
-      </c>
-      <c r="L25" s="80">
-        <f>G25*1000000/(0.9*(E25*1000)*K25^2)</f>
-        <v>2.944895822</v>
-      </c>
-      <c r="M25" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L25/(0.85*$B$5)))</f>
-        <v>0.007509198435</v>
-      </c>
-      <c r="N25" s="82">
-        <f>M25*(E25*1000)*K25</f>
-        <v>771.6827771</v>
-      </c>
-      <c r="O25" s="82">
-        <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E25*1000)*K25</f>
-        <v>342.55</v>
-      </c>
-      <c r="P25" s="82">
-        <f>MAX(N25,O25)</f>
-        <v>771.6827771</v>
-      </c>
-      <c r="Q25" s="83">
-        <f>ROUNDUP(P25/$B$9,0)</f>
-        <v>4</v>
-      </c>
-      <c r="R25" s="82">
-        <f>Q25*$B$9</f>
-        <v>796</v>
-      </c>
-      <c r="S25" s="79">
-        <f>R25*$B$6/(0.85*$B$5*(E25*1000))</f>
-        <v>46.82352941</v>
-      </c>
-      <c r="T25" s="79">
-        <f>0.9*R25*$B$6*(K25-S25/2)/1000000</f>
-        <v>96.02486534</v>
-      </c>
-      <c r="U25" s="84" t="str">
-        <f>IF(AND(T25&gt;=G25,P25&lt;=0.025*(E25*1000)*K25,P25&gt;=O25),"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="V25" s="80">
-        <f>H25*1000000/(0.9*(E25*1000)*K25^2)</f>
-        <v>2.149489876</v>
-      </c>
-      <c r="W25" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V25/(0.85*$B$5)))</f>
-        <v>0.005372514628</v>
-      </c>
-      <c r="X25" s="82">
-        <f>W25*(E25*1000)*K25</f>
-        <v>552.1064658</v>
-      </c>
-      <c r="Y25" s="82">
-        <f>MAX(X25,O25)</f>
-        <v>552.1064658</v>
-      </c>
-      <c r="Z25" s="83">
-        <f>ROUNDUP(Y25/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA25" s="82">
-        <f>Z25*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="AB25" s="79">
-        <f>0.9*AA25*$B$6*(K25-(AA25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v>73.33945883</v>
-      </c>
-      <c r="AC25" s="84" t="str">
-        <f>IF(AB25&gt;=H25,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AD25" s="79">
-        <f>0.17*SQRT($B$5)*(E25*1000)*K25/1000</f>
-        <v>92.44281538</v>
-      </c>
-      <c r="AE25" s="79">
-        <f>MAX(I25/0.75-AD25,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF25" s="83">
-        <f>IF(AE25&gt;0,MIN($B$11*$B$6*K25/(AE25*1000),MIN(K25/4,6*$B$8,150)),MIN(K25/4,6*$B$8,150))</f>
-        <v>85.6375</v>
-      </c>
-      <c r="AG25" s="79">
-        <f>0.66*SQRT($B$5)*(E25*1000)*K25/1000</f>
-        <v>358.8956362</v>
-      </c>
-      <c r="AH25" s="84" t="str">
-        <f>IF(AE25&lt;=AG25,"CUMPLE","AUMENTAR SECCION")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AI25" s="79">
-        <f>0.75*0.083*SQRT($B$5)*(((E25*1000)*(F25*1000))^2/(2*((E25*1000)+(F25*1000))))/1000000</f>
-        <v>3.388073536</v>
-      </c>
-      <c r="AJ25" s="85" t="str">
-        <f>IF(J25&gt;AI25,"SI - disenar","No - despreciable")</f>
-        <v>No - despreciable</v>
-      </c>
-      <c r="AK25" s="80">
-        <f>IF(J25&gt;AI25,J25*1000000/(0.75*2*0.85*((E25*1000-2*$B$7)*(F25*1000-2*$B$7))*$B$6),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL25" s="79">
-        <f>1.25*R25*$B$6*(K25-(1.25*R25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v>130.9219244</v>
-      </c>
-      <c r="AM25" s="79">
-        <f>1.25*AA25*$B$6*(K25-(1.25*AA25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v>100.4845159</v>
-      </c>
-      <c r="AN25" s="79">
-        <f>(AL25+AM25)/B25</f>
-        <v>45.37381183</v>
-      </c>
-      <c r="AO25" s="79">
-        <f>MAX(I25,AN25)</f>
-        <v>48.5</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="71" t="inlineStr">
+      <c r="A24" s="71" t="inlineStr">
         <is>
           <t>Nota: 'CUMPLE' verifica phiMn&gt;=Mu, cuantia&lt;=0.025 y As&gt;=As_min. El cortante por capacidad (DMO, C.21) toma V diseno=max(Vu,Ve) con Ve=(Mpr-+Mpr+)/Ln. En los apoyos se colocan las barras superiores (As-) y en el centro las inferiores (As+); estribos #3 a la separacion 's estribo' en zona de confinamiento (2h) y d/2 en el resto.</t>
         </is>
@@ -4707,7 +4227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO31"/>
+  <dimension ref="A1:AO23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="33" min="1" max="1"/>
@@ -4763,14 +4283,14 @@
     <row r="2">
       <c r="A2" s="70" t="inlineStr">
         <is>
-          <t>Agrupadas por longitud + condicion de apoyo. d, As, estribos, capacidad y torsion calculados con formulas.</t>
+          <t>Agrupadas por longitud (8 grupos), diseno con la mayor solicitacion de la envolvente. d, As, estribos, capacidad y torsion con formulas.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="71" t="inlineStr">
         <is>
-          <t>Criterio del profesor: se agrupan las vigas con la MISMA longitud Y la MISMA condicion de apoyo; cada grupo se disena con su mayor solicitacion. Celdas azules = ENTRADA (envolvente del modelo SAP). El resto se calcula solo.</t>
+          <t>Criterio de agrupacion: se agrupan las vigas con la MISMA longitud total; cada grupo se disena con su MAYOR solicitacion (envolvente de todas las condiciones de apoyo). Celdas azules = ENTRADA (envolvente del modelo SAP). El resto se calcula solo.</t>
         </is>
       </c>
     </row>
@@ -5111,7 +4631,7 @@
       </c>
       <c r="C14" s="76" t="inlineStr">
         <is>
-          <t>Extremo</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D14" s="77" t="n">
@@ -5124,16 +4644,16 @@
         <v>0.4</v>
       </c>
       <c r="G14" s="78" t="n">
-        <v>57.9</v>
+        <v>22.6</v>
       </c>
       <c r="H14" s="78" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="I14" s="78" t="n">
-        <v>81.2</v>
+        <v>16.8</v>
       </c>
       <c r="J14" s="78" t="n">
-        <v>25.7</v>
+        <v>24.9</v>
       </c>
       <c r="K14" s="79">
         <f>F14*1000-$B$7-$B$10-$B$8/2</f>
@@ -5141,15 +4661,15 @@
       </c>
       <c r="L14" s="80">
         <f>G14*1000000/(0.9*(E14*1000)*K14^2)</f>
-        <v>1.566462729</v>
+        <v>0.6114345023</v>
       </c>
       <c r="M14" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L14/(0.85*$B$5)))</f>
-        <v>0.003861223585</v>
+        <v>0.001474992942</v>
       </c>
       <c r="N14" s="82">
         <f>M14*(E14*1000)*K14</f>
-        <v>462.9317486</v>
+        <v>176.8405912</v>
       </c>
       <c r="O14" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E14*1000)*K14</f>
@@ -5157,7 +4677,7 @@
       </c>
       <c r="P14" s="82">
         <f>MAX(N14,O14)</f>
-        <v>462.9317486</v>
+        <v>399.6416667</v>
       </c>
       <c r="Q14" s="83">
         <f>ROUNDUP(P14/$B$9,0)</f>
@@ -5181,19 +4701,19 @@
       </c>
       <c r="V14" s="80">
         <f>H14*1000000/(0.9*(E14*1000)*K14^2)</f>
-        <v>1.48800432</v>
+        <v>0.08116387199</v>
       </c>
       <c r="W14" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V14/(0.85*$B$5)))</f>
-        <v>0.003661137371</v>
+        <v>0.0001935779533</v>
       </c>
       <c r="X14" s="82">
         <f>W14*(E14*1000)*K14</f>
-        <v>438.9429122</v>
+        <v>23.20854476</v>
       </c>
       <c r="Y14" s="82">
         <f>MAX(X14,O14)</f>
-        <v>438.9429122</v>
+        <v>399.6416667</v>
       </c>
       <c r="Z14" s="83">
         <f>ROUNDUP(Y14/$B$9,0)</f>
@@ -5217,7 +4737,7 @@
       </c>
       <c r="AE14" s="79">
         <f>MAX(I14/0.75-AD14,0)</f>
-        <v>0.4167153857</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="83">
         <f>IF(AE14&gt;0,MIN($B$11*$B$6*K14/(AE14*1000),MIN(K14/4,6*$B$8,150)),MIN(K14/4,6*$B$8,150))</f>
@@ -5241,7 +4761,7 @@
       </c>
       <c r="AK14" s="80">
         <f>IF(J14&gt;AI14,J14*1000000/(0.75*2*0.85*((E14*1000-2*$B$7)*(F14*1000-2*$B$7))*$B$6),0)</f>
-        <v>0.5554691012</v>
+        <v>0.5381782343</v>
       </c>
       <c r="AL14" s="79">
         <f>1.25*R14*$B$6*(K14-(1.25*R14*$B$6/(0.85*$B$5*(E14*1000)))/2)/1000000</f>
@@ -5267,15 +4787,15 @@
         </is>
       </c>
       <c r="B15" s="75" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="C15" s="76" t="inlineStr">
         <is>
-          <t>Extremo</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D15" s="77" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="E15" s="75" t="n">
         <v>0.35</v>
@@ -5284,16 +4804,16 @@
         <v>0.4</v>
       </c>
       <c r="G15" s="78" t="n">
-        <v>32.4</v>
+        <v>84.3</v>
       </c>
       <c r="H15" s="78" t="n">
-        <v>11</v>
+        <v>82.8</v>
       </c>
       <c r="I15" s="78" t="n">
-        <v>56.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J15" s="78" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="K15" s="79">
         <f>F15*1000-$B$7-$B$10-$B$8/2</f>
@@ -5301,15 +4821,15 @@
       </c>
       <c r="L15" s="80">
         <f>G15*1000000/(0.9*(E15*1000)*K15^2)</f>
-        <v>0.8765698175</v>
+        <v>2.280704803</v>
       </c>
       <c r="M15" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L15/(0.85*$B$5)))</f>
-        <v>0.002126989381</v>
+        <v>0.005718822444</v>
       </c>
       <c r="N15" s="82">
         <f>M15*(E15*1000)*K15</f>
-        <v>255.0100743</v>
+        <v>685.6439198</v>
       </c>
       <c r="O15" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E15*1000)*K15</f>
@@ -5317,23 +4837,23 @@
       </c>
       <c r="P15" s="82">
         <f>MAX(N15,O15)</f>
-        <v>399.6416667</v>
+        <v>685.6439198</v>
       </c>
       <c r="Q15" s="83">
         <f>ROUNDUP(P15/$B$9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R15" s="82">
         <f>Q15*$B$9</f>
-        <v>597</v>
+        <v>796</v>
       </c>
       <c r="S15" s="79">
         <f>R15*$B$6/(0.85*$B$5*(E15*1000))</f>
-        <v>30.10084034</v>
+        <v>40.13445378</v>
       </c>
       <c r="T15" s="79">
         <f>0.9*R15*$B$6*(K15-S15/2)/1000000</f>
-        <v>73.90552018</v>
+        <v>97.03119664</v>
       </c>
       <c r="U15" s="84" t="str">
         <f>IF(AND(T15&gt;=G15,P15&lt;=0.025*(E15*1000)*K15,P15&gt;=O15),"CUMPLE","REVISAR")</f>
@@ -5341,31 +4861,31 @@
       </c>
       <c r="V15" s="80">
         <f>H15*1000000/(0.9*(E15*1000)*K15^2)</f>
-        <v>0.297600864</v>
+        <v>2.240122867</v>
       </c>
       <c r="W15" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V15/(0.85*$B$5)))</f>
-        <v>0.0007130598475</v>
+        <v>0.005611466029</v>
       </c>
       <c r="X15" s="82">
         <f>W15*(E15*1000)*K15</f>
-        <v>85.49052776</v>
+        <v>672.7726909</v>
       </c>
       <c r="Y15" s="82">
         <f>MAX(X15,O15)</f>
-        <v>399.6416667</v>
+        <v>672.7726909</v>
       </c>
       <c r="Z15" s="83">
         <f>ROUNDUP(Y15/$B$9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA15" s="82">
         <f>Z15*$B$9</f>
-        <v>597</v>
+        <v>796</v>
       </c>
       <c r="AB15" s="79">
         <f>0.9*AA15*$B$6*(K15-(AA15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v>73.90552018</v>
+        <v>97.03119664</v>
       </c>
       <c r="AC15" s="84" t="str">
         <f>IF(AB15&gt;=H15,"CUMPLE","REVISAR")</f>
@@ -5405,19 +4925,19 @@
       </c>
       <c r="AL15" s="79">
         <f>1.25*R15*$B$6*(K15-(1.25*R15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
+        <v>132.6690274</v>
       </c>
       <c r="AM15" s="79">
         <f>1.25*AA15*$B$6*(K15-(1.25*AA15*$B$6/(0.85*$B$5*(E15*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
+        <v>132.6690274</v>
       </c>
       <c r="AN15" s="79">
         <f>(AL15+AM15)/B15</f>
-        <v>81.17380906</v>
+        <v>98.27335359</v>
       </c>
       <c r="AO15" s="79">
         <f>MAX(I15,AN15)</f>
-        <v>81.17380906</v>
+        <v>98.27335359</v>
       </c>
     </row>
     <row r="16">
@@ -5427,15 +4947,15 @@
         </is>
       </c>
       <c r="B16" s="75" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="C16" s="76" t="inlineStr">
         <is>
-          <t>Interior</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D16" s="77" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E16" s="75" t="n">
         <v>0.35</v>
@@ -5444,16 +4964,16 @@
         <v>0.4</v>
       </c>
       <c r="G16" s="78" t="n">
-        <v>27.2</v>
+        <v>83.5</v>
       </c>
       <c r="H16" s="78" t="n">
-        <v>10.3</v>
+        <v>81.5</v>
       </c>
       <c r="I16" s="78" t="n">
-        <v>54.8</v>
+        <v>63.5</v>
       </c>
       <c r="J16" s="78" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="K16" s="79">
         <f>F16*1000-$B$7-$B$10-$B$8/2</f>
@@ -5461,15 +4981,15 @@
       </c>
       <c r="L16" s="80">
         <f>G16*1000000/(0.9*(E16*1000)*K16^2)</f>
-        <v>0.7358857727</v>
+        <v>2.259061104</v>
       </c>
       <c r="M16" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L16/(0.85*$B$5)))</f>
-        <v>0.001780067576</v>
+        <v>0.005661537569</v>
       </c>
       <c r="N16" s="82">
         <f>M16*(E16*1000)*K16</f>
-        <v>213.4167518</v>
+        <v>678.775893</v>
       </c>
       <c r="O16" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E16*1000)*K16</f>
@@ -5477,23 +4997,23 @@
       </c>
       <c r="P16" s="82">
         <f>MAX(N16,O16)</f>
-        <v>399.6416667</v>
+        <v>678.775893</v>
       </c>
       <c r="Q16" s="83">
         <f>ROUNDUP(P16/$B$9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" s="82">
         <f>Q16*$B$9</f>
-        <v>597</v>
+        <v>796</v>
       </c>
       <c r="S16" s="79">
         <f>R16*$B$6/(0.85*$B$5*(E16*1000))</f>
-        <v>30.10084034</v>
+        <v>40.13445378</v>
       </c>
       <c r="T16" s="79">
         <f>0.9*R16*$B$6*(K16-S16/2)/1000000</f>
-        <v>73.90552018</v>
+        <v>97.03119664</v>
       </c>
       <c r="U16" s="84" t="str">
         <f>IF(AND(T16&gt;=G16,P16&lt;=0.025*(E16*1000)*K16,P16&gt;=O16),"CUMPLE","REVISAR")</f>
@@ -5501,31 +5021,31 @@
       </c>
       <c r="V16" s="80">
         <f>H16*1000000/(0.9*(E16*1000)*K16^2)</f>
-        <v>0.2786626272</v>
+        <v>2.204951856</v>
       </c>
       <c r="W16" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V16/(0.85*$B$5)))</f>
-        <v>0.0006674127972</v>
+        <v>0.005518606073</v>
       </c>
       <c r="X16" s="82">
         <f>W16*(E16*1000)*K16</f>
-        <v>80.01778878</v>
+        <v>661.6394787</v>
       </c>
       <c r="Y16" s="82">
         <f>MAX(X16,O16)</f>
-        <v>399.6416667</v>
+        <v>661.6394787</v>
       </c>
       <c r="Z16" s="83">
         <f>ROUNDUP(Y16/$B$9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA16" s="82">
         <f>Z16*$B$9</f>
-        <v>597</v>
+        <v>796</v>
       </c>
       <c r="AB16" s="79">
         <f>0.9*AA16*$B$6*(K16-(AA16*$B$6/(0.85*$B$5*(E16*1000)))/2)/1000000</f>
-        <v>73.90552018</v>
+        <v>97.03119664</v>
       </c>
       <c r="AC16" s="84" t="str">
         <f>IF(AB16&gt;=H16,"CUMPLE","REVISAR")</f>
@@ -5565,19 +5085,19 @@
       </c>
       <c r="AL16" s="79">
         <f>1.25*R16*$B$6*(K16-(1.25*R16*$B$6/(0.85*$B$5*(E16*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
+        <v>132.6690274</v>
       </c>
       <c r="AM16" s="79">
         <f>1.25*AA16*$B$6*(K16-(1.25*AA16*$B$6/(0.85*$B$5*(E16*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
+        <v>132.6690274</v>
       </c>
       <c r="AN16" s="79">
         <f>(AL16+AM16)/B16</f>
-        <v>81.17380906</v>
+        <v>94.76359097</v>
       </c>
       <c r="AO16" s="79">
         <f>MAX(I16,AN16)</f>
-        <v>81.17380906</v>
+        <v>94.76359097</v>
       </c>
     </row>
     <row r="17">
@@ -5587,15 +5107,15 @@
         </is>
       </c>
       <c r="B17" s="75" t="n">
-        <v>2.6</v>
+        <v>2.95</v>
       </c>
       <c r="C17" s="76" t="inlineStr">
         <is>
-          <t>Extremo</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D17" s="77" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E17" s="75" t="n">
         <v>0.35</v>
@@ -5604,16 +5124,16 @@
         <v>0.4</v>
       </c>
       <c r="G17" s="78" t="n">
-        <v>97.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="H17" s="78" t="n">
-        <v>86.8</v>
+        <v>32.9</v>
       </c>
       <c r="I17" s="78" t="n">
-        <v>154.3</v>
+        <v>53.5</v>
       </c>
       <c r="J17" s="78" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="K17" s="79">
         <f>F17*1000-$B$7-$B$10-$B$8/2</f>
@@ -5621,15 +5141,15 @@
       </c>
       <c r="L17" s="80">
         <f>G17*1000000/(0.9*(E17*1000)*K17^2)</f>
-        <v>2.62700399</v>
+        <v>2.21036278</v>
       </c>
       <c r="M17" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L17/(0.85*$B$5)))</f>
-        <v>0.006644301483</v>
+        <v>0.005532881244</v>
       </c>
       <c r="N17" s="82">
         <f>M17*(E17*1000)*K17</f>
-        <v>796.6019155</v>
+        <v>663.3509646</v>
       </c>
       <c r="O17" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E17*1000)*K17</f>
@@ -5637,23 +5157,23 @@
       </c>
       <c r="P17" s="82">
         <f>MAX(N17,O17)</f>
-        <v>796.6019155</v>
+        <v>663.3509646</v>
       </c>
       <c r="Q17" s="83">
         <f>ROUNDUP(P17/$B$9,0)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R17" s="82">
         <f>Q17*$B$9</f>
-        <v>995</v>
+        <v>796</v>
       </c>
       <c r="S17" s="79">
         <f>R17*$B$6/(0.85*$B$5*(E17*1000))</f>
-        <v>50.16806723</v>
+        <v>40.13445378</v>
       </c>
       <c r="T17" s="79">
         <f>0.9*R17*$B$6*(K17-S17/2)/1000000</f>
-        <v>119.4021246</v>
+        <v>97.03119664</v>
       </c>
       <c r="U17" s="84" t="str">
         <f>IF(AND(T17&gt;=G17,P17&lt;=0.025*(E17*1000)*K17,P17&gt;=O17),"CUMPLE","REVISAR")</f>
@@ -5661,31 +5181,31 @@
       </c>
       <c r="V17" s="80">
         <f>H17*1000000/(0.9*(E17*1000)*K17^2)</f>
-        <v>2.348341363</v>
+        <v>0.8900971295</v>
       </c>
       <c r="W17" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V17/(0.85*$B$5)))</f>
-        <v>0.005898254285</v>
+        <v>0.002160463612</v>
       </c>
       <c r="X17" s="82">
         <f>W17*(E17*1000)*K17</f>
-        <v>707.1564519</v>
+        <v>259.0233836</v>
       </c>
       <c r="Y17" s="82">
         <f>MAX(X17,O17)</f>
-        <v>707.1564519</v>
+        <v>399.6416667</v>
       </c>
       <c r="Z17" s="83">
         <f>ROUNDUP(Y17/$B$9,0)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA17" s="82">
         <f>Z17*$B$9</f>
-        <v>796</v>
+        <v>597</v>
       </c>
       <c r="AB17" s="79">
         <f>0.9*AA17*$B$6*(K17-(AA17*$B$6/(0.85*$B$5*(E17*1000)))/2)/1000000</f>
-        <v>97.03119664</v>
+        <v>73.90552018</v>
       </c>
       <c r="AC17" s="84" t="str">
         <f>IF(AB17&gt;=H17,"CUMPLE","REVISAR")</f>
@@ -5697,7 +5217,7 @@
       </c>
       <c r="AE17" s="79">
         <f>MAX(I17/0.75-AD17,0)</f>
-        <v>97.88338205</v>
+        <v>0</v>
       </c>
       <c r="AF17" s="83">
         <f>IF(AE17&gt;0,MIN($B$11*$B$6*K17/(AE17*1000),MIN(K17/4,6*$B$8,150)),MIN(K17/4,6*$B$8,150))</f>
@@ -5725,19 +5245,19 @@
       </c>
       <c r="AL17" s="79">
         <f>1.25*R17*$B$6*(K17-(1.25*R17*$B$6/(0.85*$B$5*(E17*1000)))/2)/1000000</f>
-        <v>162.5604662</v>
+        <v>132.6690274</v>
       </c>
       <c r="AM17" s="79">
         <f>1.25*AA17*$B$6*(K17-(1.25*AA17*$B$6/(0.85*$B$5*(E17*1000)))/2)/1000000</f>
-        <v>132.6690274</v>
+        <v>101.4672613</v>
       </c>
       <c r="AN17" s="79">
         <f>(AL17+AM17)/B17</f>
-        <v>113.5498052</v>
+        <v>79.36823345</v>
       </c>
       <c r="AO17" s="79">
         <f>MAX(I17,AN17)</f>
-        <v>154.3</v>
+        <v>79.36823345</v>
       </c>
     </row>
     <row r="18">
@@ -5747,15 +5267,15 @@
         </is>
       </c>
       <c r="B18" s="75" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="C18" s="76" t="inlineStr">
         <is>
-          <t>Interior</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D18" s="77" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="E18" s="75" t="n">
         <v>0.35</v>
@@ -5764,16 +5284,16 @@
         <v>0.4</v>
       </c>
       <c r="G18" s="78" t="n">
-        <v>28.9</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H18" s="78" t="n">
-        <v>14.4</v>
+        <v>82.2</v>
       </c>
       <c r="I18" s="78" t="n">
-        <v>56</v>
+        <v>59.6</v>
       </c>
       <c r="J18" s="78" t="n">
-        <v>6.4</v>
+        <v>1.2</v>
       </c>
       <c r="K18" s="79">
         <f>F18*1000-$B$7-$B$10-$B$8/2</f>
@@ -5781,15 +5301,15 @@
       </c>
       <c r="L18" s="80">
         <f>G18*1000000/(0.9*(E18*1000)*K18^2)</f>
-        <v>0.7818786335</v>
+        <v>2.545840118</v>
       </c>
       <c r="M18" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L18/(0.85*$B$5)))</f>
-        <v>0.001893242565</v>
+        <v>0.006425862723</v>
       </c>
       <c r="N18" s="82">
         <f>M18*(E18*1000)*K18</f>
-        <v>226.9855843</v>
+        <v>770.4127466</v>
       </c>
       <c r="O18" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E18*1000)*K18</f>
@@ -5797,23 +5317,23 @@
       </c>
       <c r="P18" s="82">
         <f>MAX(N18,O18)</f>
-        <v>399.6416667</v>
+        <v>770.4127466</v>
       </c>
       <c r="Q18" s="83">
         <f>ROUNDUP(P18/$B$9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R18" s="82">
         <f>Q18*$B$9</f>
-        <v>597</v>
+        <v>796</v>
       </c>
       <c r="S18" s="79">
         <f>R18*$B$6/(0.85*$B$5*(E18*1000))</f>
-        <v>30.10084034</v>
+        <v>40.13445378</v>
       </c>
       <c r="T18" s="79">
         <f>0.9*R18*$B$6*(K18-S18/2)/1000000</f>
-        <v>73.90552018</v>
+        <v>97.03119664</v>
       </c>
       <c r="U18" s="84" t="str">
         <f>IF(AND(T18&gt;=G18,P18&lt;=0.025*(E18*1000)*K18,P18&gt;=O18),"CUMPLE","REVISAR")</f>
@@ -5821,31 +5341,31 @@
       </c>
       <c r="V18" s="80">
         <f>H18*1000000/(0.9*(E18*1000)*K18^2)</f>
-        <v>0.3895865855</v>
+        <v>2.223890092</v>
       </c>
       <c r="W18" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V18/(0.85*$B$5)))</f>
-        <v>0.0009353059067</v>
+        <v>0.005568586619</v>
       </c>
       <c r="X18" s="82">
         <f>W18*(E18*1000)*K18</f>
-        <v>112.1361634</v>
+        <v>667.6317712</v>
       </c>
       <c r="Y18" s="82">
         <f>MAX(X18,O18)</f>
-        <v>399.6416667</v>
+        <v>667.6317712</v>
       </c>
       <c r="Z18" s="83">
         <f>ROUNDUP(Y18/$B$9,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA18" s="82">
         <f>Z18*$B$9</f>
-        <v>597</v>
+        <v>796</v>
       </c>
       <c r="AB18" s="79">
         <f>0.9*AA18*$B$6*(K18-(AA18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v>73.90552018</v>
+        <v>97.03119664</v>
       </c>
       <c r="AC18" s="84" t="str">
         <f>IF(AB18&gt;=H18,"CUMPLE","REVISAR")</f>
@@ -5877,27 +5397,27 @@
       </c>
       <c r="AJ18" s="85" t="str">
         <f>IF(J18&gt;AI18,"SI - disenar","No - despreciable")</f>
-        <v>SI - disenar</v>
+        <v>No - despreciable</v>
       </c>
       <c r="AK18" s="80">
         <f>IF(J18&gt;AI18,J18*1000000/(0.75*2*0.85*((E18*1000-2*$B$7)*(F18*1000-2*$B$7))*$B$6),0)</f>
-        <v>0.1383269357</v>
+        <v>0</v>
       </c>
       <c r="AL18" s="79">
         <f>1.25*R18*$B$6*(K18-(1.25*R18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
+        <v>132.6690274</v>
       </c>
       <c r="AM18" s="79">
         <f>1.25*AA18*$B$6*(K18-(1.25*AA18*$B$6/(0.85*$B$5*(E18*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
+        <v>132.6690274</v>
       </c>
       <c r="AN18" s="79">
         <f>(AL18+AM18)/B18</f>
-        <v>78.05173948</v>
+        <v>80.40547112</v>
       </c>
       <c r="AO18" s="79">
         <f>MAX(I18,AN18)</f>
-        <v>78.05173948</v>
+        <v>80.40547112</v>
       </c>
     </row>
     <row r="19">
@@ -5907,15 +5427,15 @@
         </is>
       </c>
       <c r="B19" s="75" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="C19" s="76" t="inlineStr">
         <is>
-          <t>Extremo</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D19" s="77" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E19" s="75" t="n">
         <v>0.35</v>
@@ -5924,16 +5444,16 @@
         <v>0.4</v>
       </c>
       <c r="G19" s="78" t="n">
-        <v>81.09999999999999</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="H19" s="78" t="n">
-        <v>42.6</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I19" s="78" t="n">
-        <v>88.7</v>
+        <v>54.5</v>
       </c>
       <c r="J19" s="78" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K19" s="79">
         <f>F19*1000-$B$7-$B$10-$B$8/2</f>
@@ -5941,15 +5461,15 @@
       </c>
       <c r="L19" s="80">
         <f>G19*1000000/(0.9*(E19*1000)*K19^2)</f>
-        <v>2.194130006</v>
+        <v>2.28882119</v>
       </c>
       <c r="M19" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L19/(0.85*$B$5)))</f>
-        <v>0.005490067678</v>
+        <v>0.005740320884</v>
       </c>
       <c r="N19" s="82">
         <f>M19*(E19*1000)*K19</f>
-        <v>658.217939</v>
+        <v>688.2214216</v>
       </c>
       <c r="O19" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E19*1000)*K19</f>
@@ -5957,7 +5477,7 @@
       </c>
       <c r="P19" s="82">
         <f>MAX(N19,O19)</f>
-        <v>658.217939</v>
+        <v>688.2214216</v>
       </c>
       <c r="Q19" s="83">
         <f>ROUNDUP(P19/$B$9,0)</f>
@@ -5981,19 +5501,19 @@
       </c>
       <c r="V19" s="80">
         <f>H19*1000000/(0.9*(E19*1000)*K19^2)</f>
-        <v>1.152526982</v>
+        <v>1.999336713</v>
       </c>
       <c r="W19" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V19/(0.85*$B$5)))</f>
-        <v>0.002813980878</v>
+        <v>0.004979070925</v>
       </c>
       <c r="X19" s="82">
         <f>W19*(E19*1000)*K19</f>
-        <v>337.3752024</v>
+        <v>596.9532609</v>
       </c>
       <c r="Y19" s="82">
         <f>MAX(X19,O19)</f>
-        <v>399.6416667</v>
+        <v>596.9532609</v>
       </c>
       <c r="Z19" s="83">
         <f>ROUNDUP(Y19/$B$9,0)</f>
@@ -6017,7 +5537,7 @@
       </c>
       <c r="AE19" s="79">
         <f>MAX(I19/0.75-AD19,0)</f>
-        <v>10.41671539</v>
+        <v>0</v>
       </c>
       <c r="AF19" s="83">
         <f>IF(AE19&gt;0,MIN($B$11*$B$6*K19/(AE19*1000),MIN(K19/4,6*$B$8,150)),MIN(K19/4,6*$B$8,150))</f>
@@ -6053,11 +5573,11 @@
       </c>
       <c r="AN19" s="79">
         <f>(AL19+AM19)/B19</f>
-        <v>86.71714395</v>
+        <v>64.1469284</v>
       </c>
       <c r="AO19" s="79">
         <f>MAX(I19,AN19)</f>
-        <v>88.7</v>
+        <v>64.1469284</v>
       </c>
     </row>
     <row r="20">
@@ -6067,15 +5587,15 @@
         </is>
       </c>
       <c r="B20" s="75" t="n">
-        <v>2.8</v>
+        <v>4.18</v>
       </c>
       <c r="C20" s="76" t="inlineStr">
         <is>
-          <t>Extremo</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D20" s="77" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E20" s="75" t="n">
         <v>0.35</v>
@@ -6084,16 +5604,16 @@
         <v>0.4</v>
       </c>
       <c r="G20" s="78" t="n">
-        <v>78.8</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H20" s="78" t="n">
-        <v>37.4</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I20" s="78" t="n">
-        <v>85.90000000000001</v>
+        <v>47.3</v>
       </c>
       <c r="J20" s="78" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="79">
         <f>F20*1000-$B$7-$B$10-$B$8/2</f>
@@ -6101,15 +5621,15 @@
       </c>
       <c r="L20" s="80">
         <f>G20*1000000/(0.9*(E20*1000)*K20^2)</f>
-        <v>2.131904371</v>
+        <v>2.180602694</v>
       </c>
       <c r="M20" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L20/(0.85*$B$5)))</f>
-        <v>0.005326279752</v>
+        <v>0.005454417047</v>
       </c>
       <c r="N20" s="82">
         <f>M20*(E20*1000)*K20</f>
-        <v>638.5809952</v>
+        <v>653.9436958</v>
       </c>
       <c r="O20" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E20*1000)*K20</f>
@@ -6117,7 +5637,7 @@
       </c>
       <c r="P20" s="82">
         <f>MAX(N20,O20)</f>
-        <v>638.5809952</v>
+        <v>653.9436958</v>
       </c>
       <c r="Q20" s="83">
         <f>ROUNDUP(P20/$B$9,0)</f>
@@ -6141,19 +5661,19 @@
       </c>
       <c r="V20" s="80">
         <f>H20*1000000/(0.9*(E20*1000)*K20^2)</f>
-        <v>1.011842937</v>
+        <v>1.81536527</v>
       </c>
       <c r="W20" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V20/(0.85*$B$5)))</f>
-        <v>0.002462661944</v>
+        <v>0.004501058826</v>
       </c>
       <c r="X20" s="82">
         <f>W20*(E20*1000)*K20</f>
-        <v>295.2546971</v>
+        <v>539.6431953</v>
       </c>
       <c r="Y20" s="82">
         <f>MAX(X20,O20)</f>
-        <v>399.6416667</v>
+        <v>539.6431953</v>
       </c>
       <c r="Z20" s="83">
         <f>ROUNDUP(Y20/$B$9,0)</f>
@@ -6177,7 +5697,7 @@
       </c>
       <c r="AE20" s="79">
         <f>MAX(I20/0.75-AD20,0)</f>
-        <v>6.683382052</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="83">
         <f>IF(AE20&gt;0,MIN($B$11*$B$6*K20/(AE20*1000),MIN(K20/4,6*$B$8,150)),MIN(K20/4,6*$B$8,150))</f>
@@ -6213,11 +5733,11 @@
       </c>
       <c r="AN20" s="79">
         <f>(AL20+AM20)/B20</f>
-        <v>83.6201031</v>
+        <v>56.01346619</v>
       </c>
       <c r="AO20" s="79">
         <f>MAX(I20,AN20)</f>
-        <v>85.9</v>
+        <v>56.01346619</v>
       </c>
     </row>
     <row r="21">
@@ -6227,15 +5747,15 @@
         </is>
       </c>
       <c r="B21" s="75" t="n">
-        <v>2.95</v>
+        <v>5.5</v>
       </c>
       <c r="C21" s="76" t="inlineStr">
         <is>
-          <t>Extremo</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="D21" s="77" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E21" s="75" t="n">
         <v>0.35</v>
@@ -6244,16 +5764,16 @@
         <v>0.4</v>
       </c>
       <c r="G21" s="78" t="n">
-        <v>56</v>
+        <v>41.2</v>
       </c>
       <c r="H21" s="78" t="n">
-        <v>45.8</v>
+        <v>16.1</v>
       </c>
       <c r="I21" s="78" t="n">
-        <v>95.40000000000001</v>
+        <v>28.7</v>
       </c>
       <c r="J21" s="78" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="K21" s="79">
         <f>F21*1000-$B$7-$B$10-$B$8/2</f>
@@ -6261,15 +5781,15 @@
       </c>
       <c r="L21" s="80">
         <f>G21*1000000/(0.9*(E21*1000)*K21^2)</f>
-        <v>1.515058944</v>
+        <v>1.114650509</v>
       </c>
       <c r="M21" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L21/(0.85*$B$5)))</f>
-        <v>0.003730047188</v>
+        <v>0.002719169946</v>
       </c>
       <c r="N21" s="82">
         <f>M21*(E21*1000)*K21</f>
-        <v>447.2046825</v>
+        <v>326.0080827</v>
       </c>
       <c r="O21" s="82">
         <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E21*1000)*K21</f>
@@ -6277,7 +5797,7 @@
       </c>
       <c r="P21" s="82">
         <f>MAX(N21,O21)</f>
-        <v>447.2046825</v>
+        <v>399.6416667</v>
       </c>
       <c r="Q21" s="83">
         <f>ROUNDUP(P21/$B$9,0)</f>
@@ -6301,15 +5821,15 @@
       </c>
       <c r="V21" s="80">
         <f>H21*1000000/(0.9*(E21*1000)*K21^2)</f>
-        <v>1.239101779</v>
+        <v>0.4355794463</v>
       </c>
       <c r="W21" s="81">
         <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V21/(0.85*$B$5)))</f>
-        <v>0.003031320918</v>
+        <v>0.001046761954</v>
       </c>
       <c r="X21" s="82">
         <f>W21*(E21*1000)*K21</f>
-        <v>363.4326431</v>
+        <v>125.4989076</v>
       </c>
       <c r="Y21" s="82">
         <f>MAX(X21,O21)</f>
@@ -6337,7 +5857,7 @@
       </c>
       <c r="AE21" s="79">
         <f>MAX(I21/0.75-AD21,0)</f>
-        <v>19.35004872</v>
+        <v>0</v>
       </c>
       <c r="AF21" s="83">
         <f>IF(AE21&gt;0,MIN($B$11*$B$6*K21/(AE21*1000),MIN(K21/4,6*$B$8,150)),MIN(K21/4,6*$B$8,150))</f>
@@ -6373,1295 +5893,15 @@
       </c>
       <c r="AN21" s="79">
         <f>(AL21+AM21)/B21</f>
-        <v>68.79136361</v>
+        <v>36.89718594</v>
       </c>
       <c r="AO21" s="79">
         <f>MAX(I21,AN21)</f>
-        <v>95.4</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="72" t="inlineStr">
-        <is>
-          <t>VR-9</t>
-        </is>
-      </c>
-      <c r="B22" s="75" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C22" s="76" t="inlineStr">
-        <is>
-          <t>Extremo</t>
-        </is>
-      </c>
-      <c r="D22" s="77" t="n">
-        <v>6</v>
-      </c>
-      <c r="E22" s="75" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F22" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G22" s="78" t="n">
-        <v>39</v>
-      </c>
-      <c r="H22" s="78" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I22" s="78" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="J22" s="78" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K22" s="79">
-        <f>F22*1000-$B$7-$B$10-$B$8/2</f>
-        <v>342.55</v>
-      </c>
-      <c r="L22" s="80">
-        <f>G22*1000000/(0.9*(E22*1000)*K22^2)</f>
-        <v>1.055130336</v>
-      </c>
-      <c r="M22" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L22/(0.85*$B$5)))</f>
-        <v>0.002570517068</v>
-      </c>
-      <c r="N22" s="82">
-        <f>M22*(E22*1000)*K22</f>
-        <v>308.1857175</v>
-      </c>
-      <c r="O22" s="82">
-        <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E22*1000)*K22</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="P22" s="82">
-        <f>MAX(N22,O22)</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="Q22" s="83">
-        <f>ROUNDUP(P22/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="R22" s="82">
-        <f>Q22*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="S22" s="79">
-        <f>R22*$B$6/(0.85*$B$5*(E22*1000))</f>
-        <v>30.10084034</v>
-      </c>
-      <c r="T22" s="79">
-        <f>0.9*R22*$B$6*(K22-S22/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="U22" s="84" t="str">
-        <f>IF(AND(T22&gt;=G22,P22&lt;=0.025*(E22*1000)*K22,P22&gt;=O22),"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="V22" s="80">
-        <f>H22*1000000/(0.9*(E22*1000)*K22^2)</f>
-        <v>0.4031138975</v>
-      </c>
-      <c r="W22" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V22/(0.85*$B$5)))</f>
-        <v>0.0009680639453</v>
-      </c>
-      <c r="X22" s="82">
-        <f>W22*(E22*1000)*K22</f>
-        <v>116.0636066</v>
-      </c>
-      <c r="Y22" s="82">
-        <f>MAX(X22,O22)</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="Z22" s="83">
-        <f>ROUNDUP(Y22/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA22" s="82">
-        <f>Z22*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="AB22" s="79">
-        <f>0.9*AA22*$B$6*(K22-(AA22*$B$6/(0.85*$B$5*(E22*1000)))/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="AC22" s="84" t="str">
-        <f>IF(AB22&gt;=H22,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AD22" s="79">
-        <f>0.17*SQRT($B$5)*(E22*1000)*K22/1000</f>
-        <v>107.8499513</v>
-      </c>
-      <c r="AE22" s="79">
-        <f>MAX(I22/0.75-AD22,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF22" s="83">
-        <f>IF(AE22&gt;0,MIN($B$11*$B$6*K22/(AE22*1000),MIN(K22/4,6*$B$8,150)),MIN(K22/4,6*$B$8,150))</f>
-        <v>85.6375</v>
-      </c>
-      <c r="AG22" s="79">
-        <f>0.66*SQRT($B$5)*(E22*1000)*K22/1000</f>
-        <v>418.7115756</v>
-      </c>
-      <c r="AH22" s="84" t="str">
-        <f>IF(AE22&lt;=AG22,"CUMPLE","AUMENTAR SECCION")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AI22" s="79">
-        <f>0.75*0.083*SQRT($B$5)*(((E22*1000)*(F22*1000))^2/(2*((E22*1000)+(F22*1000))))/1000000</f>
-        <v>4.304108233</v>
-      </c>
-      <c r="AJ22" s="85" t="str">
-        <f>IF(J22&gt;AI22,"SI - disenar","No - despreciable")</f>
-        <v>No - despreciable</v>
-      </c>
-      <c r="AK22" s="80">
-        <f>IF(J22&gt;AI22,J22*1000000/(0.75*2*0.85*((E22*1000-2*$B$7)*(F22*1000-2*$B$7))*$B$6),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL22" s="79">
-        <f>1.25*R22*$B$6*(K22-(1.25*R22*$B$6/(0.85*$B$5*(E22*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AM22" s="79">
-        <f>1.25*AA22*$B$6*(K22-(1.25*AA22*$B$6/(0.85*$B$5*(E22*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AN22" s="79">
-        <f>(AL22+AM22)/B22</f>
-        <v>61.49530989</v>
-      </c>
-      <c r="AO22" s="79">
-        <f>MAX(I22,AN22)</f>
-        <v>61.49530989</v>
+        <v>36.89718594</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="72" t="inlineStr">
-        <is>
-          <t>VR-10</t>
-        </is>
-      </c>
-      <c r="B23" s="75" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C23" s="76" t="inlineStr">
-        <is>
-          <t>Interior</t>
-        </is>
-      </c>
-      <c r="D23" s="77" t="n">
-        <v>4</v>
-      </c>
-      <c r="E23" s="75" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F23" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G23" s="78" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="H23" s="78" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="I23" s="78" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="J23" s="78" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K23" s="79">
-        <f>F23*1000-$B$7-$B$10-$B$8/2</f>
-        <v>342.55</v>
-      </c>
-      <c r="L23" s="80">
-        <f>G23*1000000/(0.9*(E23*1000)*K23^2)</f>
-        <v>0.9983156254</v>
-      </c>
-      <c r="M23" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L23/(0.85*$B$5)))</f>
-        <v>0.002429001202</v>
-      </c>
-      <c r="N23" s="82">
-        <f>M23*(E23*1000)*K23</f>
-        <v>291.2190266</v>
-      </c>
-      <c r="O23" s="82">
-        <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E23*1000)*K23</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="P23" s="82">
-        <f>MAX(N23,O23)</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="Q23" s="83">
-        <f>ROUNDUP(P23/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="R23" s="82">
-        <f>Q23*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="S23" s="79">
-        <f>R23*$B$6/(0.85*$B$5*(E23*1000))</f>
-        <v>30.10084034</v>
-      </c>
-      <c r="T23" s="79">
-        <f>0.9*R23*$B$6*(K23-S23/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="U23" s="84" t="str">
-        <f>IF(AND(T23&gt;=G23,P23&lt;=0.025*(E23*1000)*K23,P23&gt;=O23),"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="V23" s="80">
-        <f>H23*1000000/(0.9*(E23*1000)*K23^2)</f>
-        <v>0.3977029727</v>
-      </c>
-      <c r="W23" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V23/(0.85*$B$5)))</f>
-        <v>0.0009549584185</v>
-      </c>
-      <c r="X23" s="82">
-        <f>W23*(E23*1000)*K23</f>
-        <v>114.4923522</v>
-      </c>
-      <c r="Y23" s="82">
-        <f>MAX(X23,O23)</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="Z23" s="83">
-        <f>ROUNDUP(Y23/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA23" s="82">
-        <f>Z23*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="AB23" s="79">
-        <f>0.9*AA23*$B$6*(K23-(AA23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="AC23" s="84" t="str">
-        <f>IF(AB23&gt;=H23,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AD23" s="79">
-        <f>0.17*SQRT($B$5)*(E23*1000)*K23/1000</f>
-        <v>107.8499513</v>
-      </c>
-      <c r="AE23" s="79">
-        <f>MAX(I23/0.75-AD23,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF23" s="83">
-        <f>IF(AE23&gt;0,MIN($B$11*$B$6*K23/(AE23*1000),MIN(K23/4,6*$B$8,150)),MIN(K23/4,6*$B$8,150))</f>
-        <v>85.6375</v>
-      </c>
-      <c r="AG23" s="79">
-        <f>0.66*SQRT($B$5)*(E23*1000)*K23/1000</f>
-        <v>418.7115756</v>
-      </c>
-      <c r="AH23" s="84" t="str">
-        <f>IF(AE23&lt;=AG23,"CUMPLE","AUMENTAR SECCION")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AI23" s="79">
-        <f>0.75*0.083*SQRT($B$5)*(((E23*1000)*(F23*1000))^2/(2*((E23*1000)+(F23*1000))))/1000000</f>
-        <v>4.304108233</v>
-      </c>
-      <c r="AJ23" s="85" t="str">
-        <f>IF(J23&gt;AI23,"SI - disenar","No - despreciable")</f>
-        <v>No - despreciable</v>
-      </c>
-      <c r="AK23" s="80">
-        <f>IF(J23&gt;AI23,J23*1000000/(0.75*2*0.85*((E23*1000-2*$B$7)*(F23*1000-2*$B$7))*$B$6),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL23" s="79">
-        <f>1.25*R23*$B$6*(K23-(1.25*R23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AM23" s="79">
-        <f>1.25*AA23*$B$6*(K23-(1.25*AA23*$B$6/(0.85*$B$5*(E23*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AN23" s="79">
-        <f>(AL23+AM23)/B23</f>
-        <v>61.49530989</v>
-      </c>
-      <c r="AO23" s="79">
-        <f>MAX(I23,AN23)</f>
-        <v>61.49530989</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="72" t="inlineStr">
-        <is>
-          <t>VR-11</t>
-        </is>
-      </c>
-      <c r="B24" s="75" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="C24" s="76" t="inlineStr">
-        <is>
-          <t>Extremo</t>
-        </is>
-      </c>
-      <c r="D24" s="77" t="n">
-        <v>12</v>
-      </c>
-      <c r="E24" s="75" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F24" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G24" s="78" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="H24" s="78" t="n">
-        <v>34.6</v>
-      </c>
-      <c r="I24" s="78" t="n">
-        <v>109.7</v>
-      </c>
-      <c r="J24" s="78" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K24" s="79">
-        <f>F24*1000-$B$7-$B$10-$B$8/2</f>
-        <v>342.55</v>
-      </c>
-      <c r="L24" s="80">
-        <f>G24*1000000/(0.9*(E24*1000)*K24^2)</f>
-        <v>1.030781174</v>
-      </c>
-      <c r="M24" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L24/(0.85*$B$5)))</f>
-        <v>0.00250982213</v>
-      </c>
-      <c r="N24" s="82">
-        <f>M24*(E24*1000)*K24</f>
-        <v>300.9088498</v>
-      </c>
-      <c r="O24" s="82">
-        <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E24*1000)*K24</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="P24" s="82">
-        <f>MAX(N24,O24)</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="Q24" s="83">
-        <f>ROUNDUP(P24/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="R24" s="82">
-        <f>Q24*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="S24" s="79">
-        <f>R24*$B$6/(0.85*$B$5*(E24*1000))</f>
-        <v>30.10084034</v>
-      </c>
-      <c r="T24" s="79">
-        <f>0.9*R24*$B$6*(K24-S24/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="U24" s="84" t="str">
-        <f>IF(AND(T24&gt;=G24,P24&lt;=0.025*(E24*1000)*K24,P24&gt;=O24),"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="V24" s="80">
-        <f>H24*1000000/(0.9*(E24*1000)*K24^2)</f>
-        <v>0.9360899903</v>
-      </c>
-      <c r="W24" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V24/(0.85*$B$5)))</f>
-        <v>0.002274430093</v>
-      </c>
-      <c r="X24" s="82">
-        <f>W24*(E24*1000)*K24</f>
-        <v>272.68711</v>
-      </c>
-      <c r="Y24" s="82">
-        <f>MAX(X24,O24)</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="Z24" s="83">
-        <f>ROUNDUP(Y24/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA24" s="82">
-        <f>Z24*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="AB24" s="79">
-        <f>0.9*AA24*$B$6*(K24-(AA24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="AC24" s="84" t="str">
-        <f>IF(AB24&gt;=H24,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AD24" s="79">
-        <f>0.17*SQRT($B$5)*(E24*1000)*K24/1000</f>
-        <v>107.8499513</v>
-      </c>
-      <c r="AE24" s="79">
-        <f>MAX(I24/0.75-AD24,0)</f>
-        <v>38.41671539</v>
-      </c>
-      <c r="AF24" s="83">
-        <f>IF(AE24&gt;0,MIN($B$11*$B$6*K24/(AE24*1000),MIN(K24/4,6*$B$8,150)),MIN(K24/4,6*$B$8,150))</f>
-        <v>85.6375</v>
-      </c>
-      <c r="AG24" s="79">
-        <f>0.66*SQRT($B$5)*(E24*1000)*K24/1000</f>
-        <v>418.7115756</v>
-      </c>
-      <c r="AH24" s="84" t="str">
-        <f>IF(AE24&lt;=AG24,"CUMPLE","AUMENTAR SECCION")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AI24" s="79">
-        <f>0.75*0.083*SQRT($B$5)*(((E24*1000)*(F24*1000))^2/(2*((E24*1000)+(F24*1000))))/1000000</f>
-        <v>4.304108233</v>
-      </c>
-      <c r="AJ24" s="85" t="str">
-        <f>IF(J24&gt;AI24,"SI - disenar","No - despreciable")</f>
-        <v>SI - disenar</v>
-      </c>
-      <c r="AK24" s="80">
-        <f>IF(J24&gt;AI24,J24*1000000/(0.75*2*0.85*((E24*1000-2*$B$7)*(F24*1000-2*$B$7))*$B$6),0)</f>
-        <v>0.1231974271</v>
-      </c>
-      <c r="AL24" s="79">
-        <f>1.25*R24*$B$6*(K24-(1.25*R24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AM24" s="79">
-        <f>1.25*AA24*$B$6*(K24-(1.25*AA24*$B$6/(0.85*$B$5*(E24*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AN24" s="79">
-        <f>(AL24+AM24)/B24</f>
-        <v>55.59849936</v>
-      </c>
-      <c r="AO24" s="79">
-        <f>MAX(I24,AN24)</f>
-        <v>109.7</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="72" t="inlineStr">
-        <is>
-          <t>VR-12</t>
-        </is>
-      </c>
-      <c r="B25" s="75" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="C25" s="76" t="inlineStr">
-        <is>
-          <t>Interior</t>
-        </is>
-      </c>
-      <c r="D25" s="77" t="n">
-        <v>28</v>
-      </c>
-      <c r="E25" s="75" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F25" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G25" s="78" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="H25" s="78" t="n">
-        <v>35</v>
-      </c>
-      <c r="I25" s="78" t="n">
-        <v>110.6</v>
-      </c>
-      <c r="J25" s="78" t="n">
-        <v>6</v>
-      </c>
-      <c r="K25" s="79">
-        <f>F25*1000-$B$7-$B$10-$B$8/2</f>
-        <v>342.55</v>
-      </c>
-      <c r="L25" s="80">
-        <f>G25*1000000/(0.9*(E25*1000)*K25^2)</f>
-        <v>1.263450941</v>
-      </c>
-      <c r="M25" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L25/(0.85*$B$5)))</f>
-        <v>0.003092606666</v>
-      </c>
-      <c r="N25" s="82">
-        <f>M25*(E25*1000)*K25</f>
-        <v>370.7803447</v>
-      </c>
-      <c r="O25" s="82">
-        <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E25*1000)*K25</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="P25" s="82">
-        <f>MAX(N25,O25)</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="Q25" s="83">
-        <f>ROUNDUP(P25/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="R25" s="82">
-        <f>Q25*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="S25" s="79">
-        <f>R25*$B$6/(0.85*$B$5*(E25*1000))</f>
-        <v>30.10084034</v>
-      </c>
-      <c r="T25" s="79">
-        <f>0.9*R25*$B$6*(K25-S25/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="U25" s="84" t="str">
-        <f>IF(AND(T25&gt;=G25,P25&lt;=0.025*(E25*1000)*K25,P25&gt;=O25),"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="V25" s="80">
-        <f>H25*1000000/(0.9*(E25*1000)*K25^2)</f>
-        <v>0.9469118398</v>
-      </c>
-      <c r="W25" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V25/(0.85*$B$5)))</f>
-        <v>0.002301280456</v>
-      </c>
-      <c r="X25" s="82">
-        <f>W25*(E25*1000)*K25</f>
-        <v>275.9062671</v>
-      </c>
-      <c r="Y25" s="82">
-        <f>MAX(X25,O25)</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="Z25" s="83">
-        <f>ROUNDUP(Y25/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA25" s="82">
-        <f>Z25*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="AB25" s="79">
-        <f>0.9*AA25*$B$6*(K25-(AA25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="AC25" s="84" t="str">
-        <f>IF(AB25&gt;=H25,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AD25" s="79">
-        <f>0.17*SQRT($B$5)*(E25*1000)*K25/1000</f>
-        <v>107.8499513</v>
-      </c>
-      <c r="AE25" s="79">
-        <f>MAX(I25/0.75-AD25,0)</f>
-        <v>39.61671539</v>
-      </c>
-      <c r="AF25" s="83">
-        <f>IF(AE25&gt;0,MIN($B$11*$B$6*K25/(AE25*1000),MIN(K25/4,6*$B$8,150)),MIN(K25/4,6*$B$8,150))</f>
-        <v>85.6375</v>
-      </c>
-      <c r="AG25" s="79">
-        <f>0.66*SQRT($B$5)*(E25*1000)*K25/1000</f>
-        <v>418.7115756</v>
-      </c>
-      <c r="AH25" s="84" t="str">
-        <f>IF(AE25&lt;=AG25,"CUMPLE","AUMENTAR SECCION")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AI25" s="79">
-        <f>0.75*0.083*SQRT($B$5)*(((E25*1000)*(F25*1000))^2/(2*((E25*1000)+(F25*1000))))/1000000</f>
-        <v>4.304108233</v>
-      </c>
-      <c r="AJ25" s="85" t="str">
-        <f>IF(J25&gt;AI25,"SI - disenar","No - despreciable")</f>
-        <v>SI - disenar</v>
-      </c>
-      <c r="AK25" s="80">
-        <f>IF(J25&gt;AI25,J25*1000000/(0.75*2*0.85*((E25*1000-2*$B$7)*(F25*1000-2*$B$7))*$B$6),0)</f>
-        <v>0.1296815022</v>
-      </c>
-      <c r="AL25" s="79">
-        <f>1.25*R25*$B$6*(K25-(1.25*R25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AM25" s="79">
-        <f>1.25*AA25*$B$6*(K25-(1.25*AA25*$B$6/(0.85*$B$5*(E25*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AN25" s="79">
-        <f>(AL25+AM25)/B25</f>
-        <v>55.59849936</v>
-      </c>
-      <c r="AO25" s="79">
-        <f>MAX(I25,AN25)</f>
-        <v>110.6</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="72" t="inlineStr">
-        <is>
-          <t>VR-13</t>
-        </is>
-      </c>
-      <c r="B26" s="75" t="n">
-        <v>4</v>
-      </c>
-      <c r="C26" s="76" t="inlineStr">
-        <is>
-          <t>Extremo</t>
-        </is>
-      </c>
-      <c r="D26" s="77" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" s="75" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F26" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G26" s="78" t="n">
-        <v>65.2</v>
-      </c>
-      <c r="H26" s="78" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="I26" s="78" t="n">
-        <v>74</v>
-      </c>
-      <c r="J26" s="78" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K26" s="79">
-        <f>F26*1000-$B$7-$B$10-$B$8/2</f>
-        <v>342.55</v>
-      </c>
-      <c r="L26" s="80">
-        <f>G26*1000000/(0.9*(E26*1000)*K26^2)</f>
-        <v>1.763961485</v>
-      </c>
-      <c r="M26" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L26/(0.85*$B$5)))</f>
-        <v>0.00436827755</v>
-      </c>
-      <c r="N26" s="82">
-        <f>M26*(E26*1000)*K26</f>
-        <v>523.7237162</v>
-      </c>
-      <c r="O26" s="82">
-        <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E26*1000)*K26</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="P26" s="82">
-        <f>MAX(N26,O26)</f>
-        <v>523.7237162</v>
-      </c>
-      <c r="Q26" s="83">
-        <f>ROUNDUP(P26/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="R26" s="82">
-        <f>Q26*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="S26" s="79">
-        <f>R26*$B$6/(0.85*$B$5*(E26*1000))</f>
-        <v>30.10084034</v>
-      </c>
-      <c r="T26" s="79">
-        <f>0.9*R26*$B$6*(K26-S26/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="U26" s="84" t="str">
-        <f>IF(AND(T26&gt;=G26,P26&lt;=0.025*(E26*1000)*K26,P26&gt;=O26),"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="V26" s="80">
-        <f>H26*1000000/(0.9*(E26*1000)*K26^2)</f>
-        <v>0.6168454271</v>
-      </c>
-      <c r="W26" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V26/(0.85*$B$5)))</f>
-        <v>0.001488221982</v>
-      </c>
-      <c r="X26" s="82">
-        <f>W26*(E26*1000)*K26</f>
-        <v>178.426654</v>
-      </c>
-      <c r="Y26" s="82">
-        <f>MAX(X26,O26)</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="Z26" s="83">
-        <f>ROUNDUP(Y26/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA26" s="82">
-        <f>Z26*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="AB26" s="79">
-        <f>0.9*AA26*$B$6*(K26-(AA26*$B$6/(0.85*$B$5*(E26*1000)))/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="AC26" s="84" t="str">
-        <f>IF(AB26&gt;=H26,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AD26" s="79">
-        <f>0.17*SQRT($B$5)*(E26*1000)*K26/1000</f>
-        <v>107.8499513</v>
-      </c>
-      <c r="AE26" s="79">
-        <f>MAX(I26/0.75-AD26,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF26" s="83">
-        <f>IF(AE26&gt;0,MIN($B$11*$B$6*K26/(AE26*1000),MIN(K26/4,6*$B$8,150)),MIN(K26/4,6*$B$8,150))</f>
-        <v>85.6375</v>
-      </c>
-      <c r="AG26" s="79">
-        <f>0.66*SQRT($B$5)*(E26*1000)*K26/1000</f>
-        <v>418.7115756</v>
-      </c>
-      <c r="AH26" s="84" t="str">
-        <f>IF(AE26&lt;=AG26,"CUMPLE","AUMENTAR SECCION")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AI26" s="79">
-        <f>0.75*0.083*SQRT($B$5)*(((E26*1000)*(F26*1000))^2/(2*((E26*1000)+(F26*1000))))/1000000</f>
-        <v>4.304108233</v>
-      </c>
-      <c r="AJ26" s="85" t="str">
-        <f>IF(J26&gt;AI26,"SI - disenar","No - despreciable")</f>
-        <v>No - despreciable</v>
-      </c>
-      <c r="AK26" s="80">
-        <f>IF(J26&gt;AI26,J26*1000000/(0.75*2*0.85*((E26*1000-2*$B$7)*(F26*1000-2*$B$7))*$B$6),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL26" s="79">
-        <f>1.25*R26*$B$6*(K26-(1.25*R26*$B$6/(0.85*$B$5*(E26*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AM26" s="79">
-        <f>1.25*AA26*$B$6*(K26-(1.25*AA26*$B$6/(0.85*$B$5*(E26*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AN26" s="79">
-        <f>(AL26+AM26)/B26</f>
-        <v>50.73363066</v>
-      </c>
-      <c r="AO26" s="79">
-        <f>MAX(I26,AN26)</f>
-        <v>74</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="72" t="inlineStr">
-        <is>
-          <t>VR-14</t>
-        </is>
-      </c>
-      <c r="B27" s="75" t="n">
-        <v>4</v>
-      </c>
-      <c r="C27" s="76" t="inlineStr">
-        <is>
-          <t>Interior</t>
-        </is>
-      </c>
-      <c r="D27" s="77" t="n">
-        <v>22</v>
-      </c>
-      <c r="E27" s="75" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F27" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G27" s="78" t="n">
-        <v>60.9</v>
-      </c>
-      <c r="H27" s="78" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="I27" s="78" t="n">
-        <v>85.2</v>
-      </c>
-      <c r="J27" s="78" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K27" s="79">
-        <f>F27*1000-$B$7-$B$10-$B$8/2</f>
-        <v>342.55</v>
-      </c>
-      <c r="L27" s="80">
-        <f>G27*1000000/(0.9*(E27*1000)*K27^2)</f>
-        <v>1.647626601</v>
-      </c>
-      <c r="M27" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L27/(0.85*$B$5)))</f>
-        <v>0.004069010286</v>
-      </c>
-      <c r="N27" s="82">
-        <f>M27*(E27*1000)*K27</f>
-        <v>487.8438157</v>
-      </c>
-      <c r="O27" s="82">
-        <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E27*1000)*K27</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="P27" s="82">
-        <f>MAX(N27,O27)</f>
-        <v>487.8438157</v>
-      </c>
-      <c r="Q27" s="83">
-        <f>ROUNDUP(P27/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="R27" s="82">
-        <f>Q27*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="S27" s="79">
-        <f>R27*$B$6/(0.85*$B$5*(E27*1000))</f>
-        <v>30.10084034</v>
-      </c>
-      <c r="T27" s="79">
-        <f>0.9*R27*$B$6*(K27-S27/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="U27" s="84" t="str">
-        <f>IF(AND(T27&gt;=G27,P27&lt;=0.025*(E27*1000)*K27,P27&gt;=O27),"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="V27" s="80">
-        <f>H27*1000000/(0.9*(E27*1000)*K27^2)</f>
-        <v>0.7440021599</v>
-      </c>
-      <c r="W27" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V27/(0.85*$B$5)))</f>
-        <v>0.001800022669</v>
-      </c>
-      <c r="X27" s="82">
-        <f>W27*(E27*1000)*K27</f>
-        <v>215.8092179</v>
-      </c>
-      <c r="Y27" s="82">
-        <f>MAX(X27,O27)</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="Z27" s="83">
-        <f>ROUNDUP(Y27/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA27" s="82">
-        <f>Z27*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="AB27" s="79">
-        <f>0.9*AA27*$B$6*(K27-(AA27*$B$6/(0.85*$B$5*(E27*1000)))/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="AC27" s="84" t="str">
-        <f>IF(AB27&gt;=H27,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AD27" s="79">
-        <f>0.17*SQRT($B$5)*(E27*1000)*K27/1000</f>
-        <v>107.8499513</v>
-      </c>
-      <c r="AE27" s="79">
-        <f>MAX(I27/0.75-AD27,0)</f>
-        <v>5.750048719</v>
-      </c>
-      <c r="AF27" s="83">
-        <f>IF(AE27&gt;0,MIN($B$11*$B$6*K27/(AE27*1000),MIN(K27/4,6*$B$8,150)),MIN(K27/4,6*$B$8,150))</f>
-        <v>85.6375</v>
-      </c>
-      <c r="AG27" s="79">
-        <f>0.66*SQRT($B$5)*(E27*1000)*K27/1000</f>
-        <v>418.7115756</v>
-      </c>
-      <c r="AH27" s="84" t="str">
-        <f>IF(AE27&lt;=AG27,"CUMPLE","AUMENTAR SECCION")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AI27" s="79">
-        <f>0.75*0.083*SQRT($B$5)*(((E27*1000)*(F27*1000))^2/(2*((E27*1000)+(F27*1000))))/1000000</f>
-        <v>4.304108233</v>
-      </c>
-      <c r="AJ27" s="85" t="str">
-        <f>IF(J27&gt;AI27,"SI - disenar","No - despreciable")</f>
-        <v>SI - disenar</v>
-      </c>
-      <c r="AK27" s="80">
-        <f>IF(J27&gt;AI27,J27*1000000/(0.75*2*0.85*((E27*1000-2*$B$7)*(F27*1000-2*$B$7))*$B$6),0)</f>
-        <v>0.1188747104</v>
-      </c>
-      <c r="AL27" s="79">
-        <f>1.25*R27*$B$6*(K27-(1.25*R27*$B$6/(0.85*$B$5*(E27*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AM27" s="79">
-        <f>1.25*AA27*$B$6*(K27-(1.25*AA27*$B$6/(0.85*$B$5*(E27*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AN27" s="79">
-        <f>(AL27+AM27)/B27</f>
-        <v>50.73363066</v>
-      </c>
-      <c r="AO27" s="79">
-        <f>MAX(I27,AN27)</f>
-        <v>85.2</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="72" t="inlineStr">
-        <is>
-          <t>VR-15</t>
-        </is>
-      </c>
-      <c r="B28" s="75" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="C28" s="76" t="inlineStr">
-        <is>
-          <t>Interior</t>
-        </is>
-      </c>
-      <c r="D28" s="77" t="n">
-        <v>20</v>
-      </c>
-      <c r="E28" s="75" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F28" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G28" s="78" t="n">
-        <v>78</v>
-      </c>
-      <c r="H28" s="78" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="I28" s="78" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="J28" s="78" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K28" s="79">
-        <f>F28*1000-$B$7-$B$10-$B$8/2</f>
-        <v>342.55</v>
-      </c>
-      <c r="L28" s="80">
-        <f>G28*1000000/(0.9*(E28*1000)*K28^2)</f>
-        <v>2.110260672</v>
-      </c>
-      <c r="M28" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L28/(0.85*$B$5)))</f>
-        <v>0.005269432385</v>
-      </c>
-      <c r="N28" s="82">
-        <f>M28*(E28*1000)*K28</f>
-        <v>631.7654223</v>
-      </c>
-      <c r="O28" s="82">
-        <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E28*1000)*K28</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="P28" s="82">
-        <f>MAX(N28,O28)</f>
-        <v>631.7654223</v>
-      </c>
-      <c r="Q28" s="83">
-        <f>ROUNDUP(P28/$B$9,0)</f>
-        <v>4</v>
-      </c>
-      <c r="R28" s="82">
-        <f>Q28*$B$9</f>
-        <v>796</v>
-      </c>
-      <c r="S28" s="79">
-        <f>R28*$B$6/(0.85*$B$5*(E28*1000))</f>
-        <v>40.13445378</v>
-      </c>
-      <c r="T28" s="79">
-        <f>0.9*R28*$B$6*(K28-S28/2)/1000000</f>
-        <v>97.03119664</v>
-      </c>
-      <c r="U28" s="84" t="str">
-        <f>IF(AND(T28&gt;=G28,P28&lt;=0.025*(E28*1000)*K28,P28&gt;=O28),"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="V28" s="80">
-        <f>H28*1000000/(0.9*(E28*1000)*K28^2)</f>
-        <v>0.7088311487</v>
-      </c>
-      <c r="W28" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V28/(0.85*$B$5)))</f>
-        <v>0.001713602932</v>
-      </c>
-      <c r="X28" s="82">
-        <f>W28*(E28*1000)*K28</f>
-        <v>205.4481395</v>
-      </c>
-      <c r="Y28" s="82">
-        <f>MAX(X28,O28)</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="Z28" s="83">
-        <f>ROUNDUP(Y28/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA28" s="82">
-        <f>Z28*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="AB28" s="79">
-        <f>0.9*AA28*$B$6*(K28-(AA28*$B$6/(0.85*$B$5*(E28*1000)))/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="AC28" s="84" t="str">
-        <f>IF(AB28&gt;=H28,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AD28" s="79">
-        <f>0.17*SQRT($B$5)*(E28*1000)*K28/1000</f>
-        <v>107.8499513</v>
-      </c>
-      <c r="AE28" s="79">
-        <f>MAX(I28/0.75-AD28,0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF28" s="83">
-        <f>IF(AE28&gt;0,MIN($B$11*$B$6*K28/(AE28*1000),MIN(K28/4,6*$B$8,150)),MIN(K28/4,6*$B$8,150))</f>
-        <v>85.6375</v>
-      </c>
-      <c r="AG28" s="79">
-        <f>0.66*SQRT($B$5)*(E28*1000)*K28/1000</f>
-        <v>418.7115756</v>
-      </c>
-      <c r="AH28" s="84" t="str">
-        <f>IF(AE28&lt;=AG28,"CUMPLE","AUMENTAR SECCION")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AI28" s="79">
-        <f>0.75*0.083*SQRT($B$5)*(((E28*1000)*(F28*1000))^2/(2*((E28*1000)+(F28*1000))))/1000000</f>
-        <v>4.304108233</v>
-      </c>
-      <c r="AJ28" s="85" t="str">
-        <f>IF(J28&gt;AI28,"SI - disenar","No - despreciable")</f>
-        <v>No - despreciable</v>
-      </c>
-      <c r="AK28" s="80">
-        <f>IF(J28&gt;AI28,J28*1000000/(0.75*2*0.85*((E28*1000-2*$B$7)*(F28*1000-2*$B$7))*$B$6),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL28" s="79">
-        <f>1.25*R28*$B$6*(K28-(1.25*R28*$B$6/(0.85*$B$5*(E28*1000)))/2)/1000000</f>
-        <v>132.6690274</v>
-      </c>
-      <c r="AM28" s="79">
-        <f>1.25*AA28*$B$6*(K28-(1.25*AA28*$B$6/(0.85*$B$5*(E28*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AN28" s="79">
-        <f>(AL28+AM28)/B28</f>
-        <v>56.01346619</v>
-      </c>
-      <c r="AO28" s="79">
-        <f>MAX(I28,AN28)</f>
-        <v>79.2</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="72" t="inlineStr">
-        <is>
-          <t>VR-16</t>
-        </is>
-      </c>
-      <c r="B29" s="75" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C29" s="76" t="inlineStr">
-        <is>
-          <t>Interior</t>
-        </is>
-      </c>
-      <c r="D29" s="77" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="75" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F29" s="75" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G29" s="78" t="n">
-        <v>103.8</v>
-      </c>
-      <c r="H29" s="78" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="I29" s="78" t="n">
-        <v>113.3</v>
-      </c>
-      <c r="J29" s="78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="79">
-        <f>F29*1000-$B$7-$B$10-$B$8/2</f>
-        <v>342.55</v>
-      </c>
-      <c r="L29" s="80">
-        <f>G29*1000000/(0.9*(E29*1000)*K29^2)</f>
-        <v>2.808269971</v>
-      </c>
-      <c r="M29" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*L29/(0.85*$B$5)))</f>
-        <v>0.007135626135</v>
-      </c>
-      <c r="N29" s="82">
-        <f>M29*(E29*1000)*K29</f>
-        <v>855.5080564</v>
-      </c>
-      <c r="O29" s="82">
-        <f>MAX(0.25*SQRT($B$5)/$B$6,1.4/$B$6)*(E29*1000)*K29</f>
-        <v>399.6416667</v>
-      </c>
-      <c r="P29" s="82">
-        <f>MAX(N29,O29)</f>
-        <v>855.5080564</v>
-      </c>
-      <c r="Q29" s="83">
-        <f>ROUNDUP(P29/$B$9,0)</f>
-        <v>5</v>
-      </c>
-      <c r="R29" s="82">
-        <f>Q29*$B$9</f>
-        <v>995</v>
-      </c>
-      <c r="S29" s="79">
-        <f>R29*$B$6/(0.85*$B$5*(E29*1000))</f>
-        <v>50.16806723</v>
-      </c>
-      <c r="T29" s="79">
-        <f>0.9*R29*$B$6*(K29-S29/2)/1000000</f>
-        <v>119.4021246</v>
-      </c>
-      <c r="U29" s="84" t="str">
-        <f>IF(AND(T29&gt;=G29,P29&lt;=0.025*(E29*1000)*K29,P29&gt;=O29),"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="V29" s="80">
-        <f>H29*1000000/(0.9*(E29*1000)*K29^2)</f>
-        <v>1.368963974</v>
-      </c>
-      <c r="W29" s="81">
-        <f>(0.85*$B$5/$B$6)*(1-SQRT(1-2*V29/(0.85*$B$5)))</f>
-        <v>0.003358992417</v>
-      </c>
-      <c r="X29" s="82">
-        <f>W29*(E29*1000)*K29</f>
-        <v>402.7179983</v>
-      </c>
-      <c r="Y29" s="82">
-        <f>MAX(X29,O29)</f>
-        <v>402.7179983</v>
-      </c>
-      <c r="Z29" s="83">
-        <f>ROUNDUP(Y29/$B$9,0)</f>
-        <v>3</v>
-      </c>
-      <c r="AA29" s="82">
-        <f>Z29*$B$9</f>
-        <v>597</v>
-      </c>
-      <c r="AB29" s="79">
-        <f>0.9*AA29*$B$6*(K29-(AA29*$B$6/(0.85*$B$5*(E29*1000)))/2)/1000000</f>
-        <v>73.90552018</v>
-      </c>
-      <c r="AC29" s="84" t="str">
-        <f>IF(AB29&gt;=H29,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AD29" s="79">
-        <f>0.17*SQRT($B$5)*(E29*1000)*K29/1000</f>
-        <v>107.8499513</v>
-      </c>
-      <c r="AE29" s="79">
-        <f>MAX(I29/0.75-AD29,0)</f>
-        <v>43.21671539</v>
-      </c>
-      <c r="AF29" s="83">
-        <f>IF(AE29&gt;0,MIN($B$11*$B$6*K29/(AE29*1000),MIN(K29/4,6*$B$8,150)),MIN(K29/4,6*$B$8,150))</f>
-        <v>85.6375</v>
-      </c>
-      <c r="AG29" s="79">
-        <f>0.66*SQRT($B$5)*(E29*1000)*K29/1000</f>
-        <v>418.7115756</v>
-      </c>
-      <c r="AH29" s="84" t="str">
-        <f>IF(AE29&lt;=AG29,"CUMPLE","AUMENTAR SECCION")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="AI29" s="79">
-        <f>0.75*0.083*SQRT($B$5)*(((E29*1000)*(F29*1000))^2/(2*((E29*1000)+(F29*1000))))/1000000</f>
-        <v>4.304108233</v>
-      </c>
-      <c r="AJ29" s="85" t="str">
-        <f>IF(J29&gt;AI29,"SI - disenar","No - despreciable")</f>
-        <v>No - despreciable</v>
-      </c>
-      <c r="AK29" s="80">
-        <f>IF(J29&gt;AI29,J29*1000000/(0.75*2*0.85*((E29*1000-2*$B$7)*(F29*1000-2*$B$7))*$B$6),0)</f>
-        <v>0</v>
-      </c>
-      <c r="AL29" s="79">
-        <f>1.25*R29*$B$6*(K29-(1.25*R29*$B$6/(0.85*$B$5*(E29*1000)))/2)/1000000</f>
-        <v>162.5604662</v>
-      </c>
-      <c r="AM29" s="79">
-        <f>1.25*AA29*$B$6*(K29-(1.25*AA29*$B$6/(0.85*$B$5*(E29*1000)))/2)/1000000</f>
-        <v>101.4672613</v>
-      </c>
-      <c r="AN29" s="79">
-        <f>(AL29+AM29)/B29</f>
-        <v>48.00504136</v>
-      </c>
-      <c r="AO29" s="79">
-        <f>MAX(I29,AN29)</f>
-        <v>113.3</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="71" t="inlineStr">
+      <c r="A23" s="71" t="inlineStr">
         <is>
           <t>Nota: 'CUMPLE' verifica phiMn&gt;=Mu, cuantia&lt;=0.025 y As&gt;=As_min. El cortante por capacidad (DMO, C.21) toma V diseno=max(Vu,Ve) con Ve=(Mpr-+Mpr+)/Ln. En los apoyos se colocan las barras superiores (As-) y en el centro las inferiores (As+); estribos #3 a la separacion 's estribo' en zona de confinamiento (2h) y d/2 en el resto.</t>
         </is>
@@ -7833,7 +6073,7 @@
       </c>
       <c r="C16" s="19">
         <f>C8*1000-C11*1000-C12/2</f>
-        <v>303.65</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -7844,7 +6084,7 @@
       </c>
       <c r="C17" s="19">
         <f>(1.2*C14+1.6*C15)*C10</f>
-        <v>9.0624</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -7855,7 +6095,7 @@
       </c>
       <c r="C18" s="21">
         <f>MAX(0.25*SQRT(C5)/C6,1.4/C6)*C7*1000*C16</f>
-        <v>151.825</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -7866,7 +6106,7 @@
       </c>
       <c r="C19" s="21">
         <f>0.17*SQRT(C5)*C7*1000*C16/1000</f>
-        <v>40.97250167</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -7877,7 +6117,7 @@
       </c>
       <c r="C20" s="21">
         <f>0.75*1.1*C19</f>
-        <v>33.80231387</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -7945,19 +6185,19 @@
       </c>
       <c r="C25" s="19">
         <f>MIN(C24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v>462.5</v>
+        <v/>
       </c>
       <c r="D25" s="19">
         <f>MIN(D24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v>800</v>
+        <v/>
       </c>
       <c r="E25" s="19">
         <f>MIN(E24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v>800</v>
+        <v/>
       </c>
       <c r="F25" s="19">
         <f>MIN(F24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v>800</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -7968,19 +6208,19 @@
       </c>
       <c r="C26" s="19">
         <f>$C$17*C24^2/10</f>
-        <v>3.1016064</v>
+        <v/>
       </c>
       <c r="D26" s="19">
         <f>$C$17*D24^2/10</f>
-        <v>9.57216</v>
+        <v/>
       </c>
       <c r="E26" s="19">
         <f>$C$17*E24^2/10</f>
-        <v>17.9458176</v>
+        <v/>
       </c>
       <c r="F26" s="19">
         <f>$C$17*F24^2/10</f>
-        <v>20.8797696</v>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -7991,19 +6231,19 @@
       </c>
       <c r="C27" s="19">
         <f>$C$17*C24^2/14</f>
-        <v>2.215433143</v>
+        <v/>
       </c>
       <c r="D27" s="19">
         <f>$C$17*D24^2/14</f>
-        <v>6.837257143</v>
+        <v/>
       </c>
       <c r="E27" s="19">
         <f>$C$17*E24^2/14</f>
-        <v>12.81844114</v>
+        <v/>
       </c>
       <c r="F27" s="19">
         <f>$C$17*F24^2/14</f>
-        <v>14.91412114</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -8014,19 +6254,19 @@
       </c>
       <c r="C28" s="19">
         <f>1.15*$C$17*C24/2</f>
-        <v>9.640128</v>
+        <v/>
       </c>
       <c r="D28" s="19">
         <f>1.15*$C$17*D24/2</f>
-        <v>16.93536</v>
+        <v/>
       </c>
       <c r="E28" s="19">
         <f>1.15*$C$17*E24/2</f>
-        <v>23.188416</v>
+        <v/>
       </c>
       <c r="F28" s="19">
         <f>1.15*$C$17*F24/2</f>
-        <v>25.012224</v>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -8048,19 +6288,19 @@
       </c>
       <c r="C30" s="16">
         <f>C27*1000000/(0.9*C25*$C$16^2)</f>
-        <v>0.05772418781</v>
+        <v/>
       </c>
       <c r="D30" s="16">
         <f>D27*1000000/(0.9*D25*$C$16^2)</f>
-        <v>0.1029918469</v>
+        <v/>
       </c>
       <c r="E30" s="16">
         <f>E27*1000000/(0.9*E25*$C$16^2)</f>
-        <v>0.1930883833</v>
+        <v/>
       </c>
       <c r="F30" s="16">
         <f>F27*1000000/(0.9*F25*$C$16^2)</f>
-        <v>0.2246562985</v>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -8071,19 +6311,19 @@
       </c>
       <c r="C31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C30/(0.85*$C$5)))</f>
-        <v>0.0001376056186</v>
+        <v/>
       </c>
       <c r="D31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D30/(0.85*$C$5)))</f>
-        <v>0.0002457515699</v>
+        <v/>
       </c>
       <c r="E31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E30/(0.85*$C$5)))</f>
-        <v>0.0004616144332</v>
+        <v/>
       </c>
       <c r="F31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F30/(0.85*$C$5)))</f>
-        <v>0.0005374445961</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -8094,19 +6334,19 @@
       </c>
       <c r="C32" s="16">
         <f>C31*C25*$C$16</f>
-        <v>19.32507507</v>
+        <v/>
       </c>
       <c r="D32" s="16">
         <f>D31*D25*$C$16</f>
-        <v>59.69797136</v>
+        <v/>
       </c>
       <c r="E32" s="16">
         <f>E31*E25*$C$16</f>
-        <v>112.1353781</v>
+        <v/>
       </c>
       <c r="F32" s="16">
         <f>F31*F25*$C$16</f>
-        <v>130.5560413</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -8117,19 +6357,19 @@
       </c>
       <c r="C33" s="16">
         <f>C32*$C$6/(0.85*$C$5*C25)</f>
-        <v>0.7373637547</v>
+        <v/>
       </c>
       <c r="D33" s="16">
         <f>D32*$C$6/(0.85*$C$5*D25)</f>
-        <v>1.316867015</v>
+        <v/>
       </c>
       <c r="E33" s="16">
         <f>E32*$C$6/(0.85*$C$5*E25)</f>
-        <v>2.473574517</v>
+        <v/>
       </c>
       <c r="F33" s="16">
         <f>F32*$C$6/(0.85*$C$5*F25)</f>
-        <v>2.879912676</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -8138,21 +6378,21 @@
           <t>a &lt;= hf ? (viga T)</t>
         </is>
       </c>
-      <c r="C34" s="18" t="str">
+      <c r="C34" s="18">
         <f>IF(C33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v>Si (T)</v>
-      </c>
-      <c r="D34" s="18" t="str">
+        <v/>
+      </c>
+      <c r="D34" s="18">
         <f>IF(D33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v>Si (T)</v>
-      </c>
-      <c r="E34" s="18" t="str">
+        <v/>
+      </c>
+      <c r="E34" s="18">
         <f>IF(E33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v>Si (T)</v>
-      </c>
-      <c r="F34" s="18" t="str">
+        <v/>
+      </c>
+      <c r="F34" s="18">
         <f>IF(F33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v>Si (T)</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -8163,19 +6403,19 @@
       </c>
       <c r="C35" s="19">
         <f>MAX(C32,$C$18)</f>
-        <v>151.825</v>
+        <v/>
       </c>
       <c r="D35" s="19">
         <f>MAX(D32,$C$18)</f>
-        <v>151.825</v>
+        <v/>
       </c>
       <c r="E35" s="19">
         <f>MAX(E32,$C$18)</f>
-        <v>151.825</v>
+        <v/>
       </c>
       <c r="F35" s="19">
         <f>MAX(F32,$C$18)</f>
-        <v>151.825</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -8186,19 +6426,19 @@
       </c>
       <c r="C36" s="19">
         <f>ROUNDUP(C35/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="D36" s="19">
         <f>ROUNDUP(D35/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="E36" s="19">
         <f>ROUNDUP(E35/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="F36" s="19">
         <f>ROUNDUP(F35/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -8220,19 +6460,19 @@
       </c>
       <c r="C38" s="16">
         <f>C26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v>0.2491760774</v>
+        <v/>
       </c>
       <c r="D38" s="16">
         <f>D26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v>0.7690057903</v>
+        <v/>
       </c>
       <c r="E38" s="16">
         <f>E26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v>1.441726595</v>
+        <v/>
       </c>
       <c r="F38" s="16">
         <f>F26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v>1.677433696</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -8243,19 +6483,19 @@
       </c>
       <c r="C39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C38/(0.85*$C$5)))</f>
-        <v>0.0005964149999</v>
+        <v/>
       </c>
       <c r="D39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D38/(0.85*$C$5)))</f>
-        <v>0.001861542708</v>
+        <v/>
       </c>
       <c r="E39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E38/(0.85*$C$5)))</f>
-        <v>0.003543472336</v>
+        <v/>
       </c>
       <c r="F39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F38/(0.85*$C$5)))</f>
-        <v>0.00414552547</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -8266,19 +6506,19 @@
       </c>
       <c r="C40" s="16">
         <f>C39*$C$7*1000*$C$16</f>
-        <v>27.16521221</v>
+        <v/>
       </c>
       <c r="D40" s="16">
         <f>D39*$C$7*1000*$C$16</f>
-        <v>84.78861649</v>
+        <v/>
       </c>
       <c r="E40" s="16">
         <f>E39*$C$7*1000*$C$16</f>
-        <v>161.3963062</v>
+        <v/>
       </c>
       <c r="F40" s="16">
         <f>F39*$C$7*1000*$C$16</f>
-        <v>188.8183213</v>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -8289,19 +6529,19 @@
       </c>
       <c r="C41" s="19">
         <f>MAX(C40,$C$18)</f>
-        <v>151.825</v>
+        <v/>
       </c>
       <c r="D41" s="19">
         <f>MAX(D40,$C$18)</f>
-        <v>151.825</v>
+        <v/>
       </c>
       <c r="E41" s="19">
         <f>MAX(E40,$C$18)</f>
-        <v>161.3963062</v>
+        <v/>
       </c>
       <c r="F41" s="19">
         <f>MAX(F40,$C$18)</f>
-        <v>188.8183213</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -8312,19 +6552,19 @@
       </c>
       <c r="C42" s="19">
         <f>ROUNDUP(C41/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="D42" s="19">
         <f>ROUNDUP(D41/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="E42" s="19">
         <f>ROUNDUP(E41/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="F42" s="19">
         <f>ROUNDUP(F41/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -8344,21 +6584,21 @@
           <t>Vu &lt;= phi 1.1 Vc ?</t>
         </is>
       </c>
-      <c r="C44" s="18" t="str">
+      <c r="C44" s="18">
         <f>IF(C28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v>Si - sin estribos</v>
-      </c>
-      <c r="D44" s="18" t="str">
+        <v/>
+      </c>
+      <c r="D44" s="18">
         <f>IF(D28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v>Si - sin estribos</v>
-      </c>
-      <c r="E44" s="18" t="str">
+        <v/>
+      </c>
+      <c r="E44" s="18">
         <f>IF(E28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v>Si - sin estribos</v>
-      </c>
-      <c r="F44" s="18" t="str">
+        <v/>
+      </c>
+      <c r="F44" s="18">
         <f>IF(F28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v>Si - sin estribos</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -8367,21 +6607,21 @@
           <t>CHECK deflexion (h&gt;=Ln/18.5)</t>
         </is>
       </c>
-      <c r="C45" s="18" t="str">
+      <c r="C45" s="18">
         <f>IF($C$8&gt;=C24/18.5,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="D45" s="18" t="str">
+        <v/>
+      </c>
+      <c r="D45" s="18">
         <f>IF($C$8&gt;=D24/18.5,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="E45" s="18" t="str">
+        <v/>
+      </c>
+      <c r="E45" s="18">
         <f>IF($C$8&gt;=E24/18.5,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="F45" s="18" t="str">
+        <v/>
+      </c>
+      <c r="F45" s="18">
         <f>IF($C$8&gt;=F24/18.5,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -8554,7 +6794,7 @@
       </c>
       <c r="C16" s="19">
         <f>C8*1000-C11*1000-C12/2</f>
-        <v>303.65</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -8565,7 +6805,7 @@
       </c>
       <c r="C17" s="19">
         <f>(1.2*C14+1.6*C15)*C10</f>
-        <v>10.60096</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -8576,7 +6816,7 @@
       </c>
       <c r="C18" s="21">
         <f>MAX(0.25*SQRT(C5)/C6,1.4/C6)*C7*1000*C16</f>
-        <v>151.825</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -8587,7 +6827,7 @@
       </c>
       <c r="C19" s="21">
         <f>0.17*SQRT(C5)*C7*1000*C16/1000</f>
-        <v>40.97250167</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -8598,7 +6838,7 @@
       </c>
       <c r="C20" s="21">
         <f>0.75*1.1*C19</f>
-        <v>33.80231387</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -8666,19 +6906,19 @@
       </c>
       <c r="C25" s="19">
         <f>MIN(C24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v>462.5</v>
+        <v/>
       </c>
       <c r="D25" s="19">
         <f>MIN(D24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v>800</v>
+        <v/>
       </c>
       <c r="E25" s="19">
         <f>MIN(E24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v>800</v>
+        <v/>
       </c>
       <c r="F25" s="19">
         <f>MIN(F24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v>800</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -8689,19 +6929,19 @@
       </c>
       <c r="C26" s="19">
         <f>$C$17*C24^2/10</f>
-        <v>3.62817856</v>
+        <v/>
       </c>
       <c r="D26" s="19">
         <f>$C$17*D24^2/10</f>
-        <v>11.197264</v>
+        <v/>
       </c>
       <c r="E26" s="19">
         <f>$C$17*E24^2/10</f>
-        <v>20.99255104</v>
+        <v/>
       </c>
       <c r="F26" s="19">
         <f>$C$17*F24^2/10</f>
-        <v>24.42461184</v>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -8712,19 +6952,19 @@
       </c>
       <c r="C27" s="19">
         <f>$C$17*C24^2/14</f>
-        <v>2.591556114</v>
+        <v/>
       </c>
       <c r="D27" s="19">
         <f>$C$17*D24^2/14</f>
-        <v>7.998045714</v>
+        <v/>
       </c>
       <c r="E27" s="19">
         <f>$C$17*E24^2/14</f>
-        <v>14.99467931</v>
+        <v/>
       </c>
       <c r="F27" s="19">
         <f>$C$17*F24^2/14</f>
-        <v>17.44615131</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -8735,19 +6975,19 @@
       </c>
       <c r="C28" s="19">
         <f>1.15*$C$17*C24/2</f>
-        <v>11.2767712</v>
+        <v/>
       </c>
       <c r="D28" s="19">
         <f>1.15*$C$17*D24/2</f>
-        <v>19.810544</v>
+        <v/>
       </c>
       <c r="E28" s="19">
         <f>1.15*$C$17*E24/2</f>
-        <v>27.1252064</v>
+        <v/>
       </c>
       <c r="F28" s="19">
         <f>1.15*$C$17*F24/2</f>
-        <v>29.2586496</v>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -8769,19 +7009,19 @@
       </c>
       <c r="C30" s="16">
         <f>C27*1000000/(0.9*C25*$C$16^2)</f>
-        <v>0.06752425472</v>
+        <v/>
       </c>
       <c r="D30" s="16">
         <f>D27*1000000/(0.9*D25*$C$16^2)</f>
-        <v>0.1204771859</v>
+        <v/>
       </c>
       <c r="E30" s="16">
         <f>E27*1000000/(0.9*E25*$C$16^2)</f>
-        <v>0.2258697727</v>
+        <v/>
       </c>
       <c r="F30" s="16">
         <f>F27*1000000/(0.9*F25*$C$16^2)</f>
-        <v>0.2627970995</v>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -8792,19 +7032,19 @@
       </c>
       <c r="C31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C30/(0.85*$C$5)))</f>
-        <v>0.0001610007519</v>
+        <v/>
       </c>
       <c r="D31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D30/(0.85*$C$5)))</f>
-        <v>0.0002875801693</v>
+        <v/>
       </c>
       <c r="E31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E30/(0.85*$C$5)))</f>
-        <v>0.0005403615608</v>
+        <v/>
       </c>
       <c r="F31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F30/(0.85*$C$5)))</f>
-        <v>0.0006292005562</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -8815,19 +7055,19 @@
       </c>
       <c r="C32" s="16">
         <f>C31*C25*$C$16</f>
-        <v>22.61064372</v>
+        <v/>
       </c>
       <c r="D32" s="16">
         <f>D31*D25*$C$16</f>
-        <v>69.85897472</v>
+        <v/>
       </c>
       <c r="E32" s="16">
         <f>E31*E25*$C$16</f>
-        <v>131.2646304</v>
+        <v/>
       </c>
       <c r="F32" s="16">
         <f>F31*F25*$C$16</f>
-        <v>152.8453991</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -8838,19 +7078,19 @@
       </c>
       <c r="C33" s="16">
         <f>C32*$C$6/(0.85*$C$5*C25)</f>
-        <v>0.8627272644</v>
+        <v/>
       </c>
       <c r="D33" s="16">
         <f>D32*$C$6/(0.85*$C$5*D25)</f>
-        <v>1.541006795</v>
+        <v/>
       </c>
       <c r="E33" s="16">
         <f>E32*$C$6/(0.85*$C$5*E25)</f>
-        <v>2.895543317</v>
+        <v/>
       </c>
       <c r="F33" s="16">
         <f>F32*$C$6/(0.85*$C$5*F25)</f>
-        <v>3.371589686</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -8859,21 +7099,21 @@
           <t>a &lt;= hf ? (viga T)</t>
         </is>
       </c>
-      <c r="C34" s="18" t="str">
+      <c r="C34" s="18">
         <f>IF(C33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v>Si (T)</v>
-      </c>
-      <c r="D34" s="18" t="str">
+        <v/>
+      </c>
+      <c r="D34" s="18">
         <f>IF(D33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v>Si (T)</v>
-      </c>
-      <c r="E34" s="18" t="str">
+        <v/>
+      </c>
+      <c r="E34" s="18">
         <f>IF(E33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v>Si (T)</v>
-      </c>
-      <c r="F34" s="18" t="str">
+        <v/>
+      </c>
+      <c r="F34" s="18">
         <f>IF(F33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v>Si (T)</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -8884,19 +7124,19 @@
       </c>
       <c r="C35" s="19">
         <f>MAX(C32,$C$18)</f>
-        <v>151.825</v>
+        <v/>
       </c>
       <c r="D35" s="19">
         <f>MAX(D32,$C$18)</f>
-        <v>151.825</v>
+        <v/>
       </c>
       <c r="E35" s="19">
         <f>MAX(E32,$C$18)</f>
-        <v>151.825</v>
+        <v/>
       </c>
       <c r="F35" s="19">
         <f>MAX(F32,$C$18)</f>
-        <v>152.8453991</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -8907,19 +7147,19 @@
       </c>
       <c r="C36" s="19">
         <f>ROUNDUP(C35/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="D36" s="19">
         <f>ROUNDUP(D35/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="E36" s="19">
         <f>ROUNDUP(E35/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="F36" s="19">
         <f>ROUNDUP(F35/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -8941,19 +7181,19 @@
       </c>
       <c r="C38" s="16">
         <f>C26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v>0.2914796996</v>
+        <v/>
       </c>
       <c r="D38" s="16">
         <f>D26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v>0.8995629881</v>
+        <v/>
       </c>
       <c r="E38" s="16">
         <f>E26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v>1.686494303</v>
+        <v/>
       </c>
       <c r="F38" s="16">
         <f>F26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v>1.962218343</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -8964,19 +7204,19 @@
       </c>
       <c r="C39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C38/(0.85*$C$5)))</f>
-        <v>0.0006983018625</v>
+        <v/>
       </c>
       <c r="D39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D38/(0.85*$C$5)))</f>
-        <v>0.002183899739</v>
+        <v/>
       </c>
       <c r="E39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E38/(0.85*$C$5)))</f>
-        <v>0.004168806263</v>
+        <v/>
       </c>
       <c r="F39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F38/(0.85*$C$5)))</f>
-        <v>0.004882271123</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -8987,19 +7227,19 @@
       </c>
       <c r="C40" s="16">
         <f>C39*$C$7*1000*$C$16</f>
-        <v>31.80590408</v>
+        <v/>
       </c>
       <c r="D40" s="16">
         <f>D39*$C$7*1000*$C$16</f>
-        <v>99.47117335</v>
+        <v/>
       </c>
       <c r="E40" s="16">
         <f>E39*$C$7*1000*$C$16</f>
-        <v>189.8787033</v>
+        <v/>
       </c>
       <c r="F40" s="16">
         <f>F39*$C$7*1000*$C$16</f>
-        <v>222.375244</v>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -9010,19 +7250,19 @@
       </c>
       <c r="C41" s="19">
         <f>MAX(C40,$C$18)</f>
-        <v>151.825</v>
+        <v/>
       </c>
       <c r="D41" s="19">
         <f>MAX(D40,$C$18)</f>
-        <v>151.825</v>
+        <v/>
       </c>
       <c r="E41" s="19">
         <f>MAX(E40,$C$18)</f>
-        <v>189.8787033</v>
+        <v/>
       </c>
       <c r="F41" s="19">
         <f>MAX(F40,$C$18)</f>
-        <v>222.375244</v>
+        <v/>
       </c>
     </row>
     <row r="42">
@@ -9033,19 +7273,19 @@
       </c>
       <c r="C42" s="19">
         <f>ROUNDUP(C41/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="D42" s="19">
         <f>ROUNDUP(D41/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="E42" s="19">
         <f>ROUNDUP(E41/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="F42" s="19">
         <f>ROUNDUP(F41/$C$13,0)</f>
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="43">
@@ -9065,21 +7305,21 @@
           <t>Vu &lt;= phi 1.1 Vc ?</t>
         </is>
       </c>
-      <c r="C44" s="18" t="str">
+      <c r="C44" s="18">
         <f>IF(C28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v>Si - sin estribos</v>
-      </c>
-      <c r="D44" s="18" t="str">
+        <v/>
+      </c>
+      <c r="D44" s="18">
         <f>IF(D28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v>Si - sin estribos</v>
-      </c>
-      <c r="E44" s="18" t="str">
+        <v/>
+      </c>
+      <c r="E44" s="18">
         <f>IF(E28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v>Si - sin estribos</v>
-      </c>
-      <c r="F44" s="18" t="str">
+        <v/>
+      </c>
+      <c r="F44" s="18">
         <f>IF(F28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v>Si - sin estribos</v>
+        <v/>
       </c>
     </row>
     <row r="45">
@@ -9088,21 +7328,21 @@
           <t>CHECK deflexion (h&gt;=Ln/18.5)</t>
         </is>
       </c>
-      <c r="C45" s="18" t="str">
+      <c r="C45" s="18">
         <f>IF($C$8&gt;=C24/18.5,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="D45" s="18" t="str">
+        <v/>
+      </c>
+      <c r="D45" s="18">
         <f>IF($C$8&gt;=D24/18.5,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="E45" s="18" t="str">
+        <v/>
+      </c>
+      <c r="E45" s="18">
         <f>IF($C$8&gt;=E24/18.5,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
-      </c>
-      <c r="F45" s="18" t="str">
+        <v/>
+      </c>
+      <c r="F45" s="18">
         <f>IF($C$8&gt;=F24/18.5,"CUMPLE","REVISAR")</f>
-        <v>CUMPLE</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -10015,27 +8255,27 @@
       </c>
       <c r="D10" s="16">
         <f>($E$5*1*0.8)/(1.1*SQRT($C$5)*2.5)*C10</f>
-        <v>219.356836</v>
+        <v/>
       </c>
       <c r="E10" s="16">
         <f>($E$5*1.3*0.8)/(1.1*SQRT($C$5)*2.5)*C10</f>
-        <v>285.1638868</v>
+        <v/>
       </c>
       <c r="F10" s="19">
         <f>MAX(0.24*$E$5/SQRT($C$5)*C10,8*C10,150)</f>
-        <v>180.9693897</v>
+        <v/>
       </c>
       <c r="G10" s="16">
         <f>12*C10</f>
-        <v>114</v>
+        <v/>
       </c>
       <c r="H10" s="16">
         <f>MAX(6*C10,75)</f>
-        <v>75</v>
+        <v/>
       </c>
       <c r="I10" s="16">
         <f>6*C10</f>
-        <v>57</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -10049,27 +8289,27 @@
       </c>
       <c r="D11" s="16">
         <f>($E$5*1*0.8)/(1.1*SQRT($C$5)*2.5)*C11</f>
-        <v>293.2454544</v>
+        <v/>
       </c>
       <c r="E11" s="16">
         <f>($E$5*1.3*0.8)/(1.1*SQRT($C$5)*2.5)*C11</f>
-        <v>381.2190907</v>
+        <v/>
       </c>
       <c r="F11" s="19">
         <f>MAX(0.24*$E$5/SQRT($C$5)*C11,8*C11,150)</f>
-        <v>241.9274999</v>
+        <v/>
       </c>
       <c r="G11" s="16">
         <f>12*C11</f>
-        <v>152.4</v>
+        <v/>
       </c>
       <c r="H11" s="16">
         <f>MAX(6*C11,75)</f>
-        <v>76.2</v>
+        <v/>
       </c>
       <c r="I11" s="16">
         <f>6*C11</f>
-        <v>76.2</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -10083,27 +8323,27 @@
       </c>
       <c r="D12" s="16">
         <f>($E$5*1*0.8)/(1.1*SQRT($C$5)*2.5)*C12</f>
-        <v>367.1340728</v>
+        <v/>
       </c>
       <c r="E12" s="16">
         <f>($E$5*1.3*0.8)/(1.1*SQRT($C$5)*2.5)*C12</f>
-        <v>477.2742947</v>
+        <v/>
       </c>
       <c r="F12" s="19">
         <f>MAX(0.24*$E$5/SQRT($C$5)*C12,8*C12,150)</f>
-        <v>302.8856101</v>
+        <v/>
       </c>
       <c r="G12" s="16">
         <f>12*C12</f>
-        <v>190.8</v>
+        <v/>
       </c>
       <c r="H12" s="16">
         <f>MAX(6*C12,75)</f>
-        <v>95.4</v>
+        <v/>
       </c>
       <c r="I12" s="16">
         <f>6*C12</f>
-        <v>95.4</v>
+        <v/>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="33">
@@ -10175,7 +8415,7 @@
       </c>
       <c r="E17" s="16">
         <f>F11</f>
-        <v>241.9274999</v>
+        <v/>
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
@@ -10184,7 +8424,7 @@
       </c>
       <c r="G17" s="19">
         <f>(D17/4*1000+E17)/1000</f>
-        <v>1.5169275</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -10203,7 +8443,7 @@
       </c>
       <c r="E18" s="16">
         <f>F12</f>
-        <v>302.8856101</v>
+        <v/>
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
@@ -10212,7 +8452,7 @@
       </c>
       <c r="G18" s="19">
         <f>(D18*1000+2*E18)/1000</f>
-        <v>5.70577122</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -10231,7 +8471,7 @@
       </c>
       <c r="E19" s="16">
         <f>F10</f>
-        <v>180.9693897</v>
+        <v/>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -10240,7 +8480,7 @@
       </c>
       <c r="G19" s="19">
         <f>(D19/4*1000+E19)/1000</f>
-        <v>1.45596939</v>
+        <v/>
       </c>
     </row>
     <row r="20" ht="27.95" customHeight="1" s="33">
@@ -10259,7 +8499,7 @@
       </c>
       <c r="E20" s="16">
         <f>F10</f>
-        <v>180.9693897</v>
+        <v/>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -10268,7 +8508,7 @@
       </c>
       <c r="G20" s="19">
         <f>(D20*1000+2*E20)/1000</f>
-        <v>5.461938779</v>
+        <v/>
       </c>
     </row>
     <row r="22" ht="60" customHeight="1" s="33">
@@ -10337,19 +8577,19 @@
       </c>
       <c r="F24" s="16">
         <f>2*D24</f>
-        <v>800</v>
+        <v/>
       </c>
       <c r="G24" s="19">
         <f>MIN(E24/4,6*15.9,150)</f>
-        <v>85.65</v>
+        <v/>
       </c>
       <c r="H24" s="19">
         <f>E24/2</f>
-        <v>171.3</v>
+        <v/>
       </c>
       <c r="I24" s="16">
         <f>2*((C24-2*$G$5)+(D24-2*$G$5))+2*MAX(10*9.5,75)</f>
-        <v>1270</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -10369,19 +8609,19 @@
       </c>
       <c r="F25" s="16">
         <f>2*D25</f>
-        <v>800</v>
+        <v/>
       </c>
       <c r="G25" s="19">
         <f>MIN(E25/4,6*15.9,150)</f>
-        <v>85.65</v>
+        <v/>
       </c>
       <c r="H25" s="19">
         <f>E25/2</f>
-        <v>171.3</v>
+        <v/>
       </c>
       <c r="I25" s="16">
         <f>2*((C25-2*$G$5)+(D25-2*$G$5))+2*MAX(10*9.5,75)</f>
-        <v>1370</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -10401,19 +8641,19 @@
       </c>
       <c r="F26" s="16">
         <f>2*D26</f>
-        <v>680</v>
+        <v/>
       </c>
       <c r="G26" s="19">
         <f>MIN(E26/4,6*15.9,150)</f>
-        <v>76</v>
+        <v/>
       </c>
       <c r="H26" s="19">
         <f>E26/2</f>
-        <v>152</v>
+        <v/>
       </c>
       <c r="I26" s="16">
         <f>2*((C26-2*$G$5)+(D26-2*$G$5))+2*MAX(10*9.5,75)</f>
-        <v>850</v>
+        <v/>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" s="33">

--- a/Proyectos/Diseno-Estructural/DISENO-VIGAS-VIGUETAS-FINAL-v2.xlsx
+++ b/Proyectos/Diseno-Estructural/DISENO-VIGAS-VIGUETAS-FINAL-v2.xlsx
@@ -8255,27 +8255,27 @@
       </c>
       <c r="D10" s="16">
         <f>($E$5*1*0.8)/(1.1*SQRT($C$5)*2.5)*C10</f>
-        <v/>
+        <v>219.356836</v>
       </c>
       <c r="E10" s="16">
         <f>($E$5*1.3*0.8)/(1.1*SQRT($C$5)*2.5)*C10</f>
-        <v/>
+        <v>285.1638868</v>
       </c>
       <c r="F10" s="19">
         <f>MAX(0.24*$E$5/SQRT($C$5)*C10,8*C10,150)</f>
-        <v/>
+        <v>180.9693897</v>
       </c>
       <c r="G10" s="16">
         <f>12*C10</f>
-        <v/>
+        <v>114</v>
       </c>
       <c r="H10" s="16">
         <f>MAX(6*C10,75)</f>
-        <v/>
+        <v>75</v>
       </c>
       <c r="I10" s="16">
         <f>6*C10</f>
-        <v/>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -8289,27 +8289,27 @@
       </c>
       <c r="D11" s="16">
         <f>($E$5*1*0.8)/(1.1*SQRT($C$5)*2.5)*C11</f>
-        <v/>
+        <v>293.2454544</v>
       </c>
       <c r="E11" s="16">
         <f>($E$5*1.3*0.8)/(1.1*SQRT($C$5)*2.5)*C11</f>
-        <v/>
+        <v>381.2190907</v>
       </c>
       <c r="F11" s="19">
         <f>MAX(0.24*$E$5/SQRT($C$5)*C11,8*C11,150)</f>
-        <v/>
+        <v>241.9274999</v>
       </c>
       <c r="G11" s="16">
         <f>12*C11</f>
-        <v/>
+        <v>152.4</v>
       </c>
       <c r="H11" s="16">
         <f>MAX(6*C11,75)</f>
-        <v/>
+        <v>76.2</v>
       </c>
       <c r="I11" s="16">
         <f>6*C11</f>
-        <v/>
+        <v>76.2</v>
       </c>
     </row>
     <row r="12">
@@ -8323,27 +8323,27 @@
       </c>
       <c r="D12" s="16">
         <f>($E$5*1*0.8)/(1.1*SQRT($C$5)*2.5)*C12</f>
-        <v/>
+        <v>367.1340728</v>
       </c>
       <c r="E12" s="16">
         <f>($E$5*1.3*0.8)/(1.1*SQRT($C$5)*2.5)*C12</f>
-        <v/>
+        <v>477.2742947</v>
       </c>
       <c r="F12" s="19">
         <f>MAX(0.24*$E$5/SQRT($C$5)*C12,8*C12,150)</f>
-        <v/>
+        <v>302.8856101</v>
       </c>
       <c r="G12" s="16">
         <f>12*C12</f>
-        <v/>
+        <v>190.8</v>
       </c>
       <c r="H12" s="16">
         <f>MAX(6*C12,75)</f>
-        <v/>
+        <v>95.4</v>
       </c>
       <c r="I12" s="16">
         <f>6*C12</f>
-        <v/>
+        <v>95.4</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" s="33">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="E17" s="16">
         <f>F11</f>
-        <v/>
+        <v>241.9274999</v>
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="G17" s="19">
         <f>(D17/4*1000+E17)/1000</f>
-        <v/>
+        <v>1.5169275</v>
       </c>
     </row>
     <row r="18">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="E18" s="16">
         <f>F12</f>
-        <v/>
+        <v>302.8856101</v>
       </c>
       <c r="F18" s="21" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
       </c>
       <c r="G18" s="19">
         <f>(D18*1000+2*E18)/1000</f>
-        <v/>
+        <v>5.70577122</v>
       </c>
     </row>
     <row r="19">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="E19" s="16">
         <f>F10</f>
-        <v/>
+        <v>180.9693897</v>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="G19" s="19">
         <f>(D19/4*1000+E19)/1000</f>
-        <v/>
+        <v>1.45596939</v>
       </c>
     </row>
     <row r="20" ht="27.95" customHeight="1" s="33">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="E20" s="16">
         <f>F10</f>
-        <v/>
+        <v>180.9693897</v>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="G20" s="19">
         <f>(D20*1000+2*E20)/1000</f>
-        <v/>
+        <v>5.461938779</v>
       </c>
     </row>
     <row r="22" ht="60" customHeight="1" s="33">
@@ -8577,19 +8577,19 @@
       </c>
       <c r="F24" s="16">
         <f>2*D24</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="G24" s="19">
         <f>MIN(E24/4,6*15.9,150)</f>
-        <v/>
+        <v>85.65</v>
       </c>
       <c r="H24" s="19">
         <f>E24/2</f>
-        <v/>
+        <v>171.3</v>
       </c>
       <c r="I24" s="16">
         <f>2*((C24-2*$G$5)+(D24-2*$G$5))+2*MAX(10*9.5,75)</f>
-        <v/>
+        <v>1270</v>
       </c>
     </row>
     <row r="25">
@@ -8609,19 +8609,19 @@
       </c>
       <c r="F25" s="16">
         <f>2*D25</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="G25" s="19">
         <f>MIN(E25/4,6*15.9,150)</f>
-        <v/>
+        <v>85.65</v>
       </c>
       <c r="H25" s="19">
         <f>E25/2</f>
-        <v/>
+        <v>171.3</v>
       </c>
       <c r="I25" s="16">
         <f>2*((C25-2*$G$5)+(D25-2*$G$5))+2*MAX(10*9.5,75)</f>
-        <v/>
+        <v>1370</v>
       </c>
     </row>
     <row r="26">
@@ -8641,19 +8641,19 @@
       </c>
       <c r="F26" s="16">
         <f>2*D26</f>
-        <v/>
+        <v>680</v>
       </c>
       <c r="G26" s="19">
         <f>MIN(E26/4,6*15.9,150)</f>
-        <v/>
+        <v>76</v>
       </c>
       <c r="H26" s="19">
         <f>E26/2</f>
-        <v/>
+        <v>152</v>
       </c>
       <c r="I26" s="16">
         <f>2*((C26-2*$G$5)+(D26-2*$G$5))+2*MAX(10*9.5,75)</f>
-        <v/>
+        <v>850</v>
       </c>
     </row>
     <row r="28" ht="27.95" customHeight="1" s="33">

--- a/Proyectos/Diseno-Estructural/DISENO-VIGAS-VIGUETAS-FINAL-v2.xlsx
+++ b/Proyectos/Diseno-Estructural/DISENO-VIGAS-VIGUETAS-FINAL-v2.xlsx
@@ -1397,20 +1397,20 @@
       </c>
       <c r="D18" s="7">
         <f>MAX(E68:E72,H68:H72)</f>
-        <v/>
+        <v>1.023571884</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
           <t>1.20 / 1.40</t>
         </is>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="7" t="str">
         <f>IF(D18&gt;1.4,"Extrema",IF(D18&gt;1.2,"Si","No"))</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="G18" s="8">
         <f>IF(D18&gt;1.4,0.8,IF(D18&gt;1.2,0.9,1))</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J18" s="32" t="inlineStr">
         <is>
@@ -1431,20 +1431,20 @@
       </c>
       <c r="D19" s="7">
         <f>MAX(C42/C40,C43/C41)</f>
-        <v/>
+        <v>0.1657285804</v>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="7" t="str">
         <f>IF(AND(C42/C40&gt;0.15,C43/C41&gt;0.15),"Si","No")</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="G19" s="8">
         <f>IF(AND(C42/C40&gt;0.15,C43/C41&gt;0.15),0.9,1)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1460,19 +1460,19 @@
       </c>
       <c r="D20" s="7">
         <f>C45</f>
-        <v/>
+        <v>27.03</v>
       </c>
       <c r="E20" s="7">
         <f>0.5*C40*C41</f>
-        <v/>
-      </c>
-      <c r="F20" s="7">
+        <v>292.617</v>
+      </c>
+      <c r="F20" s="7" t="str">
         <f>IF(C45&gt;0.5*C40*C41,"Si","No")</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="G20" s="8">
         <f>IF(C45&gt;0.5*C40*C41,0.9,1)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="G23" s="9">
         <f>MIN(G18:G22)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="33">
@@ -1603,20 +1603,20 @@
       </c>
       <c r="D27" s="7">
         <f>MIN(G52:G55)</f>
-        <v/>
+        <v>1.064936106</v>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
           <t>0.70 / 0.60</t>
         </is>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="7" t="str">
         <f>IF(D27&lt;0.6,"Extrema",IF(D27&lt;0.7,"Si","No"))</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="G27" s="8">
         <f>IF(D27&lt;0.6,0.8,IF(D27&lt;0.7,0.9,1))</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="33">
@@ -1632,20 +1632,20 @@
       </c>
       <c r="D28" s="7">
         <f>MAX(H60:H63)</f>
-        <v/>
+        <v>1.323326017</v>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="7" t="str">
         <f>IF(D28&gt;1.5,"Si","No")</f>
-        <v/>
+        <v>No</v>
       </c>
       <c r="G28" s="8">
         <f>IF(D28&gt;1.5,0.9,1)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="G32" s="9">
         <f>MIN(G27:G31)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="34" ht="31.5" customHeight="1" s="33">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="C36" s="9">
         <f>IF(E35="Si",1,0.75)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="38" ht="31.5" customHeight="1" s="33">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="C44" s="7">
         <f>C40*C41</f>
-        <v/>
+        <v>585.234</v>
       </c>
     </row>
     <row r="45">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C46" s="10">
         <f>C13*G32*G23*C36</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="47" ht="57.95" customHeight="1" s="33">
@@ -1938,18 +1938,18 @@
       </c>
       <c r="D52" s="7">
         <f>SUM(C52:C56)</f>
-        <v/>
+        <v>15128.72</v>
       </c>
       <c r="E52" s="7" t="n">
         <v>0.022</v>
       </c>
       <c r="F52" s="7">
         <f>D52/E52</f>
-        <v/>
+        <v>687669.0909</v>
       </c>
       <c r="G52" s="7">
         <f>F52/F53</f>
-        <v/>
+        <v>1.410636191</v>
       </c>
     </row>
     <row r="53">
@@ -1961,18 +1961,18 @@
       </c>
       <c r="D53" s="7">
         <f>SUM(C53:C56)</f>
-        <v/>
+        <v>14137.17</v>
       </c>
       <c r="E53" s="7" t="n">
         <v>0.029</v>
       </c>
       <c r="F53" s="7">
         <f>D53/E53</f>
-        <v/>
+        <v>487488.6207</v>
       </c>
       <c r="G53" s="7">
         <f>F53/F54</f>
-        <v/>
+        <v>1.087083105</v>
       </c>
     </row>
     <row r="54">
@@ -1984,18 +1984,18 @@
       </c>
       <c r="D54" s="7">
         <f>SUM(C54:C56)</f>
-        <v/>
+        <v>11659.37</v>
       </c>
       <c r="E54" s="7" t="n">
         <v>0.026</v>
       </c>
       <c r="F54" s="7">
         <f>D54/E54</f>
-        <v/>
+        <v>448437.3077</v>
       </c>
       <c r="G54" s="7">
         <f>F54/F55</f>
-        <v/>
+        <v>1.064936106</v>
       </c>
     </row>
     <row r="55">
@@ -2007,18 +2007,18 @@
       </c>
       <c r="D55" s="7">
         <f>SUM(C55:C56)</f>
-        <v/>
+        <v>8000.77</v>
       </c>
       <c r="E55" s="7" t="n">
         <v>0.019</v>
       </c>
       <c r="F55" s="7">
         <f>D55/E55</f>
-        <v/>
+        <v>421093.1579</v>
       </c>
       <c r="G55" s="7">
         <f>F55/F56</f>
-        <v/>
+        <v>1.870865889</v>
       </c>
     </row>
     <row r="56">
@@ -2030,14 +2030,14 @@
       </c>
       <c r="D56" s="7">
         <f>SUM(C56:C56)</f>
-        <v/>
+        <v>3151.11</v>
       </c>
       <c r="E56" s="7" t="n">
         <v>0.014</v>
       </c>
       <c r="F56" s="7">
         <f>D56/E56</f>
-        <v/>
+        <v>225079.2857</v>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
@@ -2093,11 +2093,11 @@
       </c>
       <c r="E60" s="7">
         <f>C60/C61</f>
-        <v/>
+        <v>0.7556716842</v>
       </c>
       <c r="H60" s="7">
         <f>E60</f>
-        <v/>
+        <v>0.7556716842</v>
       </c>
     </row>
     <row r="61">
@@ -2109,15 +2109,15 @@
       </c>
       <c r="D61" s="7">
         <f>C61/C60</f>
-        <v/>
+        <v>1.323326017</v>
       </c>
       <c r="E61" s="7">
         <f>C61/C62</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H61" s="7">
         <f>MAX(D61,E61)</f>
-        <v/>
+        <v>1.323326017</v>
       </c>
     </row>
     <row r="62">
@@ -2129,15 +2129,15 @@
       </c>
       <c r="D62" s="7">
         <f>C62/C61</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E62" s="7">
         <f>C62/C63</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H62" s="7">
         <f>MAX(D62,E62)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="D63" s="7">
         <f>C63/C62</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="H63" s="7">
         <f>D63</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E68" s="7">
         <f>C68/((C68+D68)/2)</f>
-        <v/>
+        <v>1.023571884</v>
       </c>
       <c r="F68" s="7" t="n">
         <v>0.02097</v>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="H68" s="7">
         <f>F68/((F68+G68)/2)</f>
-        <v/>
+        <v>1.013288234</v>
       </c>
     </row>
     <row r="69">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E69" s="7">
         <f>C69/((C69+D69)/2)</f>
-        <v/>
+        <v>1.022820801</v>
       </c>
       <c r="F69" s="7" t="n">
         <v>0.04338</v>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="H69" s="7">
         <f>F69/((F69+G69)/2)</f>
-        <v/>
+        <v>1.014143776</v>
       </c>
     </row>
     <row r="70">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="E70" s="7">
         <f>C70/((C70+D70)/2)</f>
-        <v/>
+        <v>1.022321985</v>
       </c>
       <c r="F70" s="7" t="n">
         <v>0.0625</v>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="H70" s="7">
         <f>F70/((F70+G70)/2)</f>
-        <v/>
+        <v>1.014363386</v>
       </c>
     </row>
     <row r="71">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="E71" s="7">
         <f>C71/((C71+D71)/2)</f>
-        <v/>
+        <v>1.022007838</v>
       </c>
       <c r="F71" s="7" t="n">
         <v>0.07592</v>
@@ -2312,7 +2312,7 @@
       </c>
       <c r="H71" s="7">
         <f>F71/((F71+G71)/2)</f>
-        <v/>
+        <v>1.014498564</v>
       </c>
     </row>
     <row r="72">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E72" s="7">
         <f>C72/((C72+D72)/2)</f>
-        <v/>
+        <v>1.021769631</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>0.08278000000000001</v>
@@ -2337,7 +2337,7 @@
       </c>
       <c r="H72" s="7">
         <f>F72/((F72+G72)/2)</f>
-        <v/>
+        <v>1.014522949</v>
       </c>
     </row>
   </sheetData>
@@ -6073,7 +6073,7 @@
       </c>
       <c r="C16" s="19">
         <f>C8*1000-C11*1000-C12/2</f>
-        <v/>
+        <v>303.65</v>
       </c>
     </row>
     <row r="17">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="C17" s="19">
         <f>(1.2*C14+1.6*C15)*C10</f>
-        <v/>
+        <v>9.0624</v>
       </c>
     </row>
     <row r="18">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="C18" s="21">
         <f>MAX(0.25*SQRT(C5)/C6,1.4/C6)*C7*1000*C16</f>
-        <v/>
+        <v>151.825</v>
       </c>
     </row>
     <row r="19">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="C19" s="21">
         <f>0.17*SQRT(C5)*C7*1000*C16/1000</f>
-        <v/>
+        <v>40.97250167</v>
       </c>
     </row>
     <row r="20">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="C20" s="21">
         <f>0.75*1.1*C19</f>
-        <v/>
+        <v>33.80231387</v>
       </c>
     </row>
     <row r="22">
@@ -6185,19 +6185,19 @@
       </c>
       <c r="C25" s="19">
         <f>MIN(C24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>462.5</v>
       </c>
       <c r="D25" s="19">
         <f>MIN(D24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="E25" s="19">
         <f>MIN(E24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="F25" s="19">
         <f>MIN(F24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
     </row>
     <row r="26">
@@ -6208,19 +6208,19 @@
       </c>
       <c r="C26" s="19">
         <f>$C$17*C24^2/10</f>
-        <v/>
+        <v>3.1016064</v>
       </c>
       <c r="D26" s="19">
         <f>$C$17*D24^2/10</f>
-        <v/>
+        <v>9.57216</v>
       </c>
       <c r="E26" s="19">
         <f>$C$17*E24^2/10</f>
-        <v/>
+        <v>17.9458176</v>
       </c>
       <c r="F26" s="19">
         <f>$C$17*F24^2/10</f>
-        <v/>
+        <v>20.8797696</v>
       </c>
     </row>
     <row r="27">
@@ -6231,19 +6231,19 @@
       </c>
       <c r="C27" s="19">
         <f>$C$17*C24^2/14</f>
-        <v/>
+        <v>2.215433143</v>
       </c>
       <c r="D27" s="19">
         <f>$C$17*D24^2/14</f>
-        <v/>
+        <v>6.837257143</v>
       </c>
       <c r="E27" s="19">
         <f>$C$17*E24^2/14</f>
-        <v/>
+        <v>12.81844114</v>
       </c>
       <c r="F27" s="19">
         <f>$C$17*F24^2/14</f>
-        <v/>
+        <v>14.91412114</v>
       </c>
     </row>
     <row r="28">
@@ -6254,19 +6254,19 @@
       </c>
       <c r="C28" s="19">
         <f>1.15*$C$17*C24/2</f>
-        <v/>
+        <v>9.640128</v>
       </c>
       <c r="D28" s="19">
         <f>1.15*$C$17*D24/2</f>
-        <v/>
+        <v>16.93536</v>
       </c>
       <c r="E28" s="19">
         <f>1.15*$C$17*E24/2</f>
-        <v/>
+        <v>23.188416</v>
       </c>
       <c r="F28" s="19">
         <f>1.15*$C$17*F24/2</f>
-        <v/>
+        <v>25.012224</v>
       </c>
     </row>
     <row r="29">
@@ -6288,19 +6288,19 @@
       </c>
       <c r="C30" s="16">
         <f>C27*1000000/(0.9*C25*$C$16^2)</f>
-        <v/>
+        <v>0.05772418781</v>
       </c>
       <c r="D30" s="16">
         <f>D27*1000000/(0.9*D25*$C$16^2)</f>
-        <v/>
+        <v>0.1029918469</v>
       </c>
       <c r="E30" s="16">
         <f>E27*1000000/(0.9*E25*$C$16^2)</f>
-        <v/>
+        <v>0.1930883833</v>
       </c>
       <c r="F30" s="16">
         <f>F27*1000000/(0.9*F25*$C$16^2)</f>
-        <v/>
+        <v>0.2246562985</v>
       </c>
     </row>
     <row r="31">
@@ -6311,19 +6311,19 @@
       </c>
       <c r="C31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0001376056186</v>
       </c>
       <c r="D31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0002457515699</v>
       </c>
       <c r="E31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0004616144332</v>
       </c>
       <c r="F31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0005374445961</v>
       </c>
     </row>
     <row r="32">
@@ -6334,19 +6334,19 @@
       </c>
       <c r="C32" s="16">
         <f>C31*C25*$C$16</f>
-        <v/>
+        <v>19.32507507</v>
       </c>
       <c r="D32" s="16">
         <f>D31*D25*$C$16</f>
-        <v/>
+        <v>59.69797136</v>
       </c>
       <c r="E32" s="16">
         <f>E31*E25*$C$16</f>
-        <v/>
+        <v>112.1353781</v>
       </c>
       <c r="F32" s="16">
         <f>F31*F25*$C$16</f>
-        <v/>
+        <v>130.5560413</v>
       </c>
     </row>
     <row r="33">
@@ -6357,19 +6357,19 @@
       </c>
       <c r="C33" s="16">
         <f>C32*$C$6/(0.85*$C$5*C25)</f>
-        <v/>
+        <v>0.7373637547</v>
       </c>
       <c r="D33" s="16">
         <f>D32*$C$6/(0.85*$C$5*D25)</f>
-        <v/>
+        <v>1.316867015</v>
       </c>
       <c r="E33" s="16">
         <f>E32*$C$6/(0.85*$C$5*E25)</f>
-        <v/>
+        <v>2.473574517</v>
       </c>
       <c r="F33" s="16">
         <f>F32*$C$6/(0.85*$C$5*F25)</f>
-        <v/>
+        <v>2.879912676</v>
       </c>
     </row>
     <row r="34">
@@ -6378,21 +6378,21 @@
           <t>a &lt;= hf ? (viga T)</t>
         </is>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="18" t="str">
         <f>IF(C33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="D34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="D34" s="18" t="str">
         <f>IF(D33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="E34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="E34" s="18" t="str">
         <f>IF(E33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="F34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="F34" s="18" t="str">
         <f>IF(F33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
+        <v>Si (T)</v>
       </c>
     </row>
     <row r="35">
@@ -6403,19 +6403,19 @@
       </c>
       <c r="C35" s="19">
         <f>MAX(C32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="D35" s="19">
         <f>MAX(D32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="E35" s="19">
         <f>MAX(E32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="F35" s="19">
         <f>MAX(F32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
     </row>
     <row r="36">
@@ -6426,19 +6426,19 @@
       </c>
       <c r="C36" s="19">
         <f>ROUNDUP(C35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D36" s="19">
         <f>ROUNDUP(D35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E36" s="19">
         <f>ROUNDUP(E35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F36" s="19">
         <f>ROUNDUP(F35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -6460,19 +6460,19 @@
       </c>
       <c r="C38" s="16">
         <f>C26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>0.2491760774</v>
       </c>
       <c r="D38" s="16">
         <f>D26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>0.7690057903</v>
       </c>
       <c r="E38" s="16">
         <f>E26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>1.441726595</v>
       </c>
       <c r="F38" s="16">
         <f>F26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>1.677433696</v>
       </c>
     </row>
     <row r="39">
@@ -6483,19 +6483,19 @@
       </c>
       <c r="C39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0005964149999</v>
       </c>
       <c r="D39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.001861542708</v>
       </c>
       <c r="E39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.003543472336</v>
       </c>
       <c r="F39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.00414552547</v>
       </c>
     </row>
     <row r="40">
@@ -6506,19 +6506,19 @@
       </c>
       <c r="C40" s="16">
         <f>C39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>27.16521221</v>
       </c>
       <c r="D40" s="16">
         <f>D39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>84.78861649</v>
       </c>
       <c r="E40" s="16">
         <f>E39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>161.3963062</v>
       </c>
       <c r="F40" s="16">
         <f>F39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>188.8183213</v>
       </c>
     </row>
     <row r="41">
@@ -6529,19 +6529,19 @@
       </c>
       <c r="C41" s="19">
         <f>MAX(C40,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="D41" s="19">
         <f>MAX(D40,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="E41" s="19">
         <f>MAX(E40,$C$18)</f>
-        <v/>
+        <v>161.3963062</v>
       </c>
       <c r="F41" s="19">
         <f>MAX(F40,$C$18)</f>
-        <v/>
+        <v>188.8183213</v>
       </c>
     </row>
     <row r="42">
@@ -6552,19 +6552,19 @@
       </c>
       <c r="C42" s="19">
         <f>ROUNDUP(C41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D42" s="19">
         <f>ROUNDUP(D41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E42" s="19">
         <f>ROUNDUP(E41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F42" s="19">
         <f>ROUNDUP(F41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -6584,21 +6584,21 @@
           <t>Vu &lt;= phi 1.1 Vc ?</t>
         </is>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="18" t="str">
         <f>IF(C28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="D44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="D44" s="18" t="str">
         <f>IF(D28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="E44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="E44" s="18" t="str">
         <f>IF(E28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="F44" s="18" t="str">
         <f>IF(F28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
+        <v>Si - sin estribos</v>
       </c>
     </row>
     <row r="45">
@@ -6607,21 +6607,21 @@
           <t>CHECK deflexion (h&gt;=Ln/18.5)</t>
         </is>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="18" t="str">
         <f>IF($C$8&gt;=C24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="D45" s="18" t="str">
         <f>IF($C$8&gt;=D24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="E45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="E45" s="18" t="str">
         <f>IF($C$8&gt;=E24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="F45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="F45" s="18" t="str">
         <f>IF($C$8&gt;=F24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
     </row>
   </sheetData>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="C16" s="19">
         <f>C8*1000-C11*1000-C12/2</f>
-        <v/>
+        <v>303.65</v>
       </c>
     </row>
     <row r="17">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="C17" s="19">
         <f>(1.2*C14+1.6*C15)*C10</f>
-        <v/>
+        <v>10.60096</v>
       </c>
     </row>
     <row r="18">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="C18" s="21">
         <f>MAX(0.25*SQRT(C5)/C6,1.4/C6)*C7*1000*C16</f>
-        <v/>
+        <v>151.825</v>
       </c>
     </row>
     <row r="19">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="C19" s="21">
         <f>0.17*SQRT(C5)*C7*1000*C16/1000</f>
-        <v/>
+        <v>40.97250167</v>
       </c>
     </row>
     <row r="20">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="C20" s="21">
         <f>0.75*1.1*C19</f>
-        <v/>
+        <v>33.80231387</v>
       </c>
     </row>
     <row r="22">
@@ -6906,19 +6906,19 @@
       </c>
       <c r="C25" s="19">
         <f>MIN(C24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>462.5</v>
       </c>
       <c r="D25" s="19">
         <f>MIN(D24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="E25" s="19">
         <f>MIN(E24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
       <c r="F25" s="19">
         <f>MIN(F24*1000/4,$C$7*1000+16*$C$9*1000,$C$10*1000)</f>
-        <v/>
+        <v>800</v>
       </c>
     </row>
     <row r="26">
@@ -6929,19 +6929,19 @@
       </c>
       <c r="C26" s="19">
         <f>$C$17*C24^2/10</f>
-        <v/>
+        <v>3.62817856</v>
       </c>
       <c r="D26" s="19">
         <f>$C$17*D24^2/10</f>
-        <v/>
+        <v>11.197264</v>
       </c>
       <c r="E26" s="19">
         <f>$C$17*E24^2/10</f>
-        <v/>
+        <v>20.99255104</v>
       </c>
       <c r="F26" s="19">
         <f>$C$17*F24^2/10</f>
-        <v/>
+        <v>24.42461184</v>
       </c>
     </row>
     <row r="27">
@@ -6952,19 +6952,19 @@
       </c>
       <c r="C27" s="19">
         <f>$C$17*C24^2/14</f>
-        <v/>
+        <v>2.591556114</v>
       </c>
       <c r="D27" s="19">
         <f>$C$17*D24^2/14</f>
-        <v/>
+        <v>7.998045714</v>
       </c>
       <c r="E27" s="19">
         <f>$C$17*E24^2/14</f>
-        <v/>
+        <v>14.99467931</v>
       </c>
       <c r="F27" s="19">
         <f>$C$17*F24^2/14</f>
-        <v/>
+        <v>17.44615131</v>
       </c>
     </row>
     <row r="28">
@@ -6975,19 +6975,19 @@
       </c>
       <c r="C28" s="19">
         <f>1.15*$C$17*C24/2</f>
-        <v/>
+        <v>11.2767712</v>
       </c>
       <c r="D28" s="19">
         <f>1.15*$C$17*D24/2</f>
-        <v/>
+        <v>19.810544</v>
       </c>
       <c r="E28" s="19">
         <f>1.15*$C$17*E24/2</f>
-        <v/>
+        <v>27.1252064</v>
       </c>
       <c r="F28" s="19">
         <f>1.15*$C$17*F24/2</f>
-        <v/>
+        <v>29.2586496</v>
       </c>
     </row>
     <row r="29">
@@ -7009,19 +7009,19 @@
       </c>
       <c r="C30" s="16">
         <f>C27*1000000/(0.9*C25*$C$16^2)</f>
-        <v/>
+        <v>0.06752425472</v>
       </c>
       <c r="D30" s="16">
         <f>D27*1000000/(0.9*D25*$C$16^2)</f>
-        <v/>
+        <v>0.1204771859</v>
       </c>
       <c r="E30" s="16">
         <f>E27*1000000/(0.9*E25*$C$16^2)</f>
-        <v/>
+        <v>0.2258697727</v>
       </c>
       <c r="F30" s="16">
         <f>F27*1000000/(0.9*F25*$C$16^2)</f>
-        <v/>
+        <v>0.2627970995</v>
       </c>
     </row>
     <row r="31">
@@ -7032,19 +7032,19 @@
       </c>
       <c r="C31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0001610007519</v>
       </c>
       <c r="D31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0002875801693</v>
       </c>
       <c r="E31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0005403615608</v>
       </c>
       <c r="F31" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F30/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0006292005562</v>
       </c>
     </row>
     <row r="32">
@@ -7055,19 +7055,19 @@
       </c>
       <c r="C32" s="16">
         <f>C31*C25*$C$16</f>
-        <v/>
+        <v>22.61064372</v>
       </c>
       <c r="D32" s="16">
         <f>D31*D25*$C$16</f>
-        <v/>
+        <v>69.85897472</v>
       </c>
       <c r="E32" s="16">
         <f>E31*E25*$C$16</f>
-        <v/>
+        <v>131.2646304</v>
       </c>
       <c r="F32" s="16">
         <f>F31*F25*$C$16</f>
-        <v/>
+        <v>152.8453991</v>
       </c>
     </row>
     <row r="33">
@@ -7078,19 +7078,19 @@
       </c>
       <c r="C33" s="16">
         <f>C32*$C$6/(0.85*$C$5*C25)</f>
-        <v/>
+        <v>0.8627272644</v>
       </c>
       <c r="D33" s="16">
         <f>D32*$C$6/(0.85*$C$5*D25)</f>
-        <v/>
+        <v>1.541006795</v>
       </c>
       <c r="E33" s="16">
         <f>E32*$C$6/(0.85*$C$5*E25)</f>
-        <v/>
+        <v>2.895543317</v>
       </c>
       <c r="F33" s="16">
         <f>F32*$C$6/(0.85*$C$5*F25)</f>
-        <v/>
+        <v>3.371589686</v>
       </c>
     </row>
     <row r="34">
@@ -7099,21 +7099,21 @@
           <t>a &lt;= hf ? (viga T)</t>
         </is>
       </c>
-      <c r="C34" s="18">
+      <c r="C34" s="18" t="str">
         <f>IF(C33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="D34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="D34" s="18" t="str">
         <f>IF(D33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="E34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="E34" s="18" t="str">
         <f>IF(E33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
-      </c>
-      <c r="F34" s="18">
+        <v>Si (T)</v>
+      </c>
+      <c r="F34" s="18" t="str">
         <f>IF(F33&lt;=$C$9*1000,"Si (T)","revisar")</f>
-        <v/>
+        <v>Si (T)</v>
       </c>
     </row>
     <row r="35">
@@ -7124,19 +7124,19 @@
       </c>
       <c r="C35" s="19">
         <f>MAX(C32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="D35" s="19">
         <f>MAX(D32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="E35" s="19">
         <f>MAX(E32,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="F35" s="19">
         <f>MAX(F32,$C$18)</f>
-        <v/>
+        <v>152.8453991</v>
       </c>
     </row>
     <row r="36">
@@ -7147,19 +7147,19 @@
       </c>
       <c r="C36" s="19">
         <f>ROUNDUP(C35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D36" s="19">
         <f>ROUNDUP(D35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E36" s="19">
         <f>ROUNDUP(E35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F36" s="19">
         <f>ROUNDUP(F35/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -7181,19 +7181,19 @@
       </c>
       <c r="C38" s="16">
         <f>C26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>0.2914796996</v>
       </c>
       <c r="D38" s="16">
         <f>D26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>0.8995629881</v>
       </c>
       <c r="E38" s="16">
         <f>E26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>1.686494303</v>
       </c>
       <c r="F38" s="16">
         <f>F26*1000000/(0.9*$C$7*1000*$C$16^2)</f>
-        <v/>
+        <v>1.962218343</v>
       </c>
     </row>
     <row r="39">
@@ -7204,19 +7204,19 @@
       </c>
       <c r="C39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*C38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.0006983018625</v>
       </c>
       <c r="D39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*D38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.002183899739</v>
       </c>
       <c r="E39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*E38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.004168806263</v>
       </c>
       <c r="F39" s="16">
         <f>(0.85*$C$5/$C$6)*(1-SQRT(1-2*F38/(0.85*$C$5)))</f>
-        <v/>
+        <v>0.004882271123</v>
       </c>
     </row>
     <row r="40">
@@ -7227,19 +7227,19 @@
       </c>
       <c r="C40" s="16">
         <f>C39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>31.80590408</v>
       </c>
       <c r="D40" s="16">
         <f>D39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>99.47117335</v>
       </c>
       <c r="E40" s="16">
         <f>E39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>189.8787033</v>
       </c>
       <c r="F40" s="16">
         <f>F39*$C$7*1000*$C$16</f>
-        <v/>
+        <v>222.375244</v>
       </c>
     </row>
     <row r="41">
@@ -7250,19 +7250,19 @@
       </c>
       <c r="C41" s="19">
         <f>MAX(C40,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="D41" s="19">
         <f>MAX(D40,$C$18)</f>
-        <v/>
+        <v>151.825</v>
       </c>
       <c r="E41" s="19">
         <f>MAX(E40,$C$18)</f>
-        <v/>
+        <v>189.8787033</v>
       </c>
       <c r="F41" s="19">
         <f>MAX(F40,$C$18)</f>
-        <v/>
+        <v>222.375244</v>
       </c>
     </row>
     <row r="42">
@@ -7273,19 +7273,19 @@
       </c>
       <c r="C42" s="19">
         <f>ROUNDUP(C41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="D42" s="19">
         <f>ROUNDUP(D41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E42" s="19">
         <f>ROUNDUP(E41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="F42" s="19">
         <f>ROUNDUP(F41/$C$13,0)</f>
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -7305,21 +7305,21 @@
           <t>Vu &lt;= phi 1.1 Vc ?</t>
         </is>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="18" t="str">
         <f>IF(C28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="D44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="D44" s="18" t="str">
         <f>IF(D28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="E44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="E44" s="18" t="str">
         <f>IF(E28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
-      </c>
-      <c r="F44" s="18">
+        <v>Si - sin estribos</v>
+      </c>
+      <c r="F44" s="18" t="str">
         <f>IF(F28&lt;=$C$20,"Si - sin estribos","Requiere estribos")</f>
-        <v/>
+        <v>Si - sin estribos</v>
       </c>
     </row>
     <row r="45">
@@ -7328,21 +7328,21 @@
           <t>CHECK deflexion (h&gt;=Ln/18.5)</t>
         </is>
       </c>
-      <c r="C45" s="18">
+      <c r="C45" s="18" t="str">
         <f>IF($C$8&gt;=C24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="D45" s="18" t="str">
         <f>IF($C$8&gt;=D24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="E45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="E45" s="18" t="str">
         <f>IF($C$8&gt;=E24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="F45" s="18">
+        <v>CUMPLE</v>
+      </c>
+      <c r="F45" s="18" t="str">
         <f>IF($C$8&gt;=F24/18.5,"CUMPLE","REVISAR")</f>
-        <v/>
+        <v>CUMPLE</v>
       </c>
     </row>
   </sheetData>
